--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F09E7061-5B05-4A41-835F-D3EBF3DC2D77}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D1DBC7B-C8BC-4EDD-9338-3BD1990E7D7B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7383" uniqueCount="3180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7386" uniqueCount="3181">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -13981,6 +13981,9 @@
   </si>
   <si>
     <t>5/1/26, 6/5/26, 7/26, 8/26</t>
+  </si>
+  <si>
+    <t>Scudetto Logistics</t>
   </si>
 </sst>
 </file>
@@ -16858,10 +16861,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17476,7 +17475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -17807,6 +17806,23 @@
       </c>
       <c r="E19" s="48">
         <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="60" t="s">
+        <v>3180</v>
+      </c>
+      <c r="B20" s="60" t="s">
+        <v>2590</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="50">
+        <v>46156</v>
+      </c>
+      <c r="E20" s="49">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D1DBC7B-C8BC-4EDD-9338-3BD1990E7D7B}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB07AC7C-55A2-4AB3-84BA-1DC9DE8ADA15}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7386" uniqueCount="3181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7390" uniqueCount="3183">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -13984,6 +13984,12 @@
   </si>
   <si>
     <t>Scudetto Logistics</t>
+  </si>
+  <si>
+    <t>Imperia Foods</t>
+  </si>
+  <si>
+    <t>5/22/26 and 9/1/26</t>
   </si>
 </sst>
 </file>
@@ -16861,6 +16867,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17475,7 +17485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -17823,6 +17833,23 @@
       </c>
       <c r="E20" s="49">
         <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="31.2">
+      <c r="A21" s="48" t="s">
+        <v>3181</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>3039</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>3182</v>
+      </c>
+      <c r="E21" s="48">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB07AC7C-55A2-4AB3-84BA-1DC9DE8ADA15}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2E04359-CDD9-4EA1-81AB-3C27E28520EF}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7390" uniqueCount="3183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7393" uniqueCount="3183">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -17485,7 +17485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -17850,6 +17850,23 @@
       </c>
       <c r="E21" s="48">
         <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="60" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B22" s="60" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="50">
+        <v>46161</v>
+      </c>
+      <c r="E22" s="49">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2E04359-CDD9-4EA1-81AB-3C27E28520EF}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC44903E-8094-4BA9-8C51-E6009DDFD1A8}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7393" uniqueCount="3183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7401" uniqueCount="3186">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -13990,6 +13990,15 @@
   </si>
   <si>
     <t>5/22/26 and 9/1/26</t>
+  </si>
+  <si>
+    <t>5/21/26, 6/19/26, 7/16/26, 7/31/26, 10/23/26, 12/17/26, 12/31/26</t>
+  </si>
+  <si>
+    <t>Cigna Evernorth Services</t>
+  </si>
+  <si>
+    <t>4/29/26, 5/3/26, 5/20/26</t>
   </si>
 </sst>
 </file>
@@ -14115,7 +14124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -14206,12 +14215,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="thin">
+        <color theme="6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -14391,6 +14413,15 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -17485,13 +17516,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.21875" style="41" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17867,6 +17898,40 @@
       </c>
       <c r="E22" s="49">
         <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="62.4">
+      <c r="A23" s="63" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>2968</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="65" t="s">
+        <v>3183</v>
+      </c>
+      <c r="E23" s="63">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="31.2">
+      <c r="A24" s="48" t="s">
+        <v>3184</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>2596</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="50" t="s">
+        <v>3185</v>
+      </c>
+      <c r="E24" s="48">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC44903E-8094-4BA9-8C51-E6009DDFD1A8}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AC822F1-28B8-41BC-9C12-6CD932E172B3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7401" uniqueCount="3186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7408" uniqueCount="3188">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -13999,6 +13999,12 @@
   </si>
   <si>
     <t>4/29/26, 5/3/26, 5/20/26</t>
+  </si>
+  <si>
+    <t>5/21/26, 5/27/26, 6/2/26, 6/6/26, 6/7/26, 6/14/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macy's  </t>
   </si>
 </sst>
 </file>
@@ -17516,7 +17522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -17577,7 +17583,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5">
       <c r="A4" s="60" t="s">
         <v>3153</v>
       </c>
@@ -17628,7 +17634,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="78">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17764,7 +17770,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="46.8">
+    <row r="15" spans="1:5">
       <c r="A15" s="60" t="s">
         <v>3174</v>
       </c>
@@ -17781,7 +17787,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="31.2">
+    <row r="16" spans="1:5">
       <c r="A16" s="60" t="s">
         <v>3176</v>
       </c>
@@ -17832,7 +17838,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="46.8">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -17866,7 +17872,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="31.2">
+    <row r="21" spans="1:5">
       <c r="A21" s="48" t="s">
         <v>3181</v>
       </c>
@@ -17932,6 +17938,40 @@
       </c>
       <c r="E24" s="48">
         <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="46.8">
+      <c r="A25" s="60" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B25" s="60" t="s">
+        <v>3168</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>3186</v>
+      </c>
+      <c r="E25" s="49">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="60" t="s">
+        <v>3187</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>3168</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="50">
+        <v>46088</v>
+      </c>
+      <c r="E26" s="49">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AC822F1-28B8-41BC-9C12-6CD932E172B3}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD190953-756E-4133-AFAE-27BBFE1EFBED}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7408" uniqueCount="3188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7414" uniqueCount="3190">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14005,6 +14005,12 @@
   </si>
   <si>
     <t xml:space="preserve">Macy's  </t>
+  </si>
+  <si>
+    <t>IPIC Theaters</t>
+  </si>
+  <si>
+    <t>MarketSource</t>
   </si>
 </sst>
 </file>
@@ -17522,7 +17528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -17972,6 +17978,40 @@
       </c>
       <c r="E26" s="49">
         <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="48" t="s">
+        <v>3188</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C27" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="50">
+        <v>46170</v>
+      </c>
+      <c r="E27" s="48">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="48" t="s">
+        <v>3189</v>
+      </c>
+      <c r="B28" s="48" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="50">
+        <v>46172</v>
+      </c>
+      <c r="E28" s="48">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD190953-756E-4133-AFAE-27BBFE1EFBED}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76E5E4D2-51A4-4886-80D3-C974FC8782ED}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7414" uniqueCount="3190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7418" uniqueCount="3193">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14011,6 +14011,15 @@
   </si>
   <si>
     <t>MarketSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compass Inc. </t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>1/9/26 - 8/14/26</t>
   </si>
 </sst>
 </file>
@@ -17528,7 +17537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18012,6 +18021,23 @@
       </c>
       <c r="E28" s="48">
         <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="48" t="s">
+        <v>3190</v>
+      </c>
+      <c r="B29" s="48" t="s">
+        <v>3191</v>
+      </c>
+      <c r="C29" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>3192</v>
+      </c>
+      <c r="E29" s="48">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76E5E4D2-51A4-4886-80D3-C974FC8782ED}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44B3792F-7B97-4784-9557-706929561D31}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7418" uniqueCount="3193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7421" uniqueCount="3194">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14020,6 +14020,9 @@
   </si>
   <si>
     <t>1/9/26 - 8/14/26</t>
+  </si>
+  <si>
+    <t>Luna Foods dba Joey's Fine Foods</t>
   </si>
 </sst>
 </file>
@@ -17537,7 +17540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18038,6 +18041,23 @@
       </c>
       <c r="E29" s="48">
         <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="31.2">
+      <c r="A30" s="60" t="s">
+        <v>3193</v>
+      </c>
+      <c r="B30" s="60" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="50">
+        <v>46178</v>
+      </c>
+      <c r="E30" s="49">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -56241,7 +56261,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="20" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="18" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44B3792F-7B97-4784-9557-706929561D31}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F23C162-27D9-4132-AB41-2034699249E6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7421" uniqueCount="3194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7425" uniqueCount="3196">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14023,6 +14023,12 @@
   </si>
   <si>
     <t>Luna Foods dba Joey's Fine Foods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prudential </t>
+  </si>
+  <si>
+    <t>5/7/26 - 6/7/26</t>
   </si>
 </sst>
 </file>
@@ -17540,7 +17546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18058,6 +18064,23 @@
       </c>
       <c r="E30" s="49">
         <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="48" t="s">
+        <v>3194</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>3195</v>
+      </c>
+      <c r="E31" s="48">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F23C162-27D9-4132-AB41-2034699249E6}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4312EBEE-542B-444A-8593-45F67E7FD681}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7425" uniqueCount="3196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7437" uniqueCount="3200">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14029,6 +14029,18 @@
   </si>
   <si>
     <t>5/7/26 - 6/7/26</t>
+  </si>
+  <si>
+    <t>Reckitt Benckiser</t>
+  </si>
+  <si>
+    <t>3/2/26 - 8/31/26</t>
+  </si>
+  <si>
+    <t>RB Health</t>
+  </si>
+  <si>
+    <t>Mead Johnson</t>
   </si>
 </sst>
 </file>
@@ -17546,7 +17558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18081,6 +18093,57 @@
       </c>
       <c r="E31" s="48">
         <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="63" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B32" s="63" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C32" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="65" t="s">
+        <v>3197</v>
+      </c>
+      <c r="E32" s="63">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="63" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B33" s="63" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C33" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="65" t="s">
+        <v>3197</v>
+      </c>
+      <c r="E33" s="63">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="48" t="s">
+        <v>3199</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C34" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="50" t="s">
+        <v>3197</v>
+      </c>
+      <c r="E34" s="48">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4312EBEE-542B-444A-8593-45F67E7FD681}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B944FC44-7D1E-49E1-B26E-7851F68FE090}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7437" uniqueCount="3200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7440" uniqueCount="3200">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -17558,7 +17558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18144,6 +18144,23 @@
       </c>
       <c r="E34" s="48">
         <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="48" t="s">
+        <v>3114</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C35" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="50">
+        <v>46097</v>
+      </c>
+      <c r="E35" s="48">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B944FC44-7D1E-49E1-B26E-7851F68FE090}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDE656FD-6565-4229-B0B3-8638CB98A934}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7440" uniqueCount="3200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7444" uniqueCount="3203">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14041,6 +14041,15 @@
   </si>
   <si>
     <t>Mead Johnson</t>
+  </si>
+  <si>
+    <t>Fiserv Solutions LLC</t>
+  </si>
+  <si>
+    <t>Berkeley Heights</t>
+  </si>
+  <si>
+    <t>3/31/26 - 5/31/26</t>
   </si>
 </sst>
 </file>
@@ -16940,10 +16949,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17558,7 +17563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18161,6 +18166,23 @@
       </c>
       <c r="E35" s="48">
         <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="60" t="s">
+        <v>3200</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>3201</v>
+      </c>
+      <c r="C36" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="50" t="s">
+        <v>3202</v>
+      </c>
+      <c r="E36" s="49">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDE656FD-6565-4229-B0B3-8638CB98A934}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D9BCC62-ECB9-4918-8DC9-0015A882B601}"/>
   <bookViews>
-    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7444" uniqueCount="3203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7454" uniqueCount="3206">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14050,6 +14050,15 @@
   </si>
   <si>
     <t>3/31/26 - 5/31/26</t>
+  </si>
+  <si>
+    <t>OTB Hospitality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBS </t>
+  </si>
+  <si>
+    <t>3/24/26 - 3/26/26</t>
   </si>
 </sst>
 </file>
@@ -16949,6 +16958,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17563,7 +17576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18183,6 +18196,57 @@
       </c>
       <c r="E36" s="49">
         <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="48" t="s">
+        <v>3203</v>
+      </c>
+      <c r="B37" s="48" t="s">
+        <v>378</v>
+      </c>
+      <c r="C37" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="50">
+        <v>46094</v>
+      </c>
+      <c r="E37" s="48">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="63" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B38" s="63" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C38" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="65" t="s">
+        <v>3205</v>
+      </c>
+      <c r="E38" s="63">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="48" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B39" s="48" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C39" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="50">
+        <v>46193</v>
+      </c>
+      <c r="E39" s="48">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D9BCC62-ECB9-4918-8DC9-0015A882B601}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C164C6AB-BDD8-4355-8D43-6C0036EB69A7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -14058,7 +14058,7 @@
     <t xml:space="preserve">UBS </t>
   </si>
   <si>
-    <t>3/24/26 - 3/26/26</t>
+    <t>6/22/26 - 6/24/26</t>
   </si>
 </sst>
 </file>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C164C6AB-BDD8-4355-8D43-6C0036EB69A7}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DC9FD53-D273-4DE2-A6BB-EF1C9C64D737}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7454" uniqueCount="3206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7462" uniqueCount="3210">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14059,6 +14059,18 @@
   </si>
   <si>
     <t>6/22/26 - 6/24/26</t>
+  </si>
+  <si>
+    <t>Labcorp Raritan</t>
+  </si>
+  <si>
+    <t>Raritan</t>
+  </si>
+  <si>
+    <t>7/3/26 - 7/17/26</t>
+  </si>
+  <si>
+    <t>6/26/26 - 11/27/26</t>
   </si>
 </sst>
 </file>
@@ -16958,10 +16970,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17576,7 +17584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18247,6 +18255,40 @@
       </c>
       <c r="E39" s="48">
         <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="60" t="s">
+        <v>3206</v>
+      </c>
+      <c r="B40" s="60" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="50" t="s">
+        <v>3208</v>
+      </c>
+      <c r="E40" s="49">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="60" t="s">
+        <v>2992</v>
+      </c>
+      <c r="B41" s="60" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C41" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="50" t="s">
+        <v>3209</v>
+      </c>
+      <c r="E41" s="49">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DC9FD53-D273-4DE2-A6BB-EF1C9C64D737}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01C4D5DA-6E02-4CF0-B239-02D251B1E8F0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7462" uniqueCount="3210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7465" uniqueCount="3211">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14071,6 +14071,9 @@
   </si>
   <si>
     <t>6/26/26 - 11/27/26</t>
+  </si>
+  <si>
+    <t>O.C.E.A.N Inc.</t>
   </si>
 </sst>
 </file>
@@ -17584,7 +17587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18289,6 +18292,23 @@
       </c>
       <c r="E41" s="49">
         <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="48" t="s">
+        <v>3210</v>
+      </c>
+      <c r="B42" s="48" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C42" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="50">
+        <v>46204</v>
+      </c>
+      <c r="E42" s="48">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/4.2.26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01C4D5DA-6E02-4CF0-B239-02D251B1E8F0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B1AC58D-8F16-4F12-B923-C793E5250E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7465" uniqueCount="3211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7468" uniqueCount="3212">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -13980,9 +13980,6 @@
     <t>Arrow Fastener</t>
   </si>
   <si>
-    <t>5/1/26, 6/5/26, 7/26, 8/26</t>
-  </si>
-  <si>
     <t>Scudetto Logistics</t>
   </si>
   <si>
@@ -14074,6 +14071,12 @@
   </si>
   <si>
     <t>O.C.E.A.N Inc.</t>
+  </si>
+  <si>
+    <t>Bayonne University Hospital</t>
+  </si>
+  <si>
+    <t>5/1/2026, 6/5/2026, 7/2026, 8/2026, 9/4/26</t>
   </si>
 </sst>
 </file>
@@ -17587,13 +17590,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E42"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17631,7 +17637,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17682,7 +17688,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17699,7 +17705,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17716,7 +17722,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17733,7 +17739,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17750,7 +17756,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17801,7 +17807,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17818,7 +17824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17903,7 +17909,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -17914,15 +17920,15 @@
         <v>64</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>3179</v>
+        <v>3211</v>
       </c>
       <c r="E19" s="48">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="60" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="B20" s="60" t="s">
         <v>2590</v>
@@ -17939,7 +17945,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="48" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="B21" s="48" t="s">
         <v>3039</v>
@@ -17948,7 +17954,7 @@
         <v>64</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="E21" s="48">
         <v>82</v>
@@ -17971,7 +17977,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -17982,15 +17988,15 @@
         <v>64</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="E23" s="63">
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="B24" s="48" t="s">
         <v>2596</v>
@@ -17999,13 +18005,13 @@
         <v>64</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E24" s="48">
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18016,7 +18022,7 @@
         <v>64</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="E25" s="49">
         <v>141</v>
@@ -18024,7 +18030,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="60" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="B26" s="60" t="s">
         <v>3168</v>
@@ -18041,7 +18047,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="48" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="B27" s="48" t="s">
         <v>1464</v>
@@ -18058,7 +18064,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="48" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="B28" s="48" t="s">
         <v>1526</v>
@@ -18075,24 +18081,24 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="48" t="s">
+        <v>3189</v>
+      </c>
+      <c r="B29" s="48" t="s">
         <v>3190</v>
-      </c>
-      <c r="B29" s="48" t="s">
-        <v>3191</v>
       </c>
       <c r="C29" s="49" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="E29" s="48">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="B30" s="60" t="s">
         <v>1441</v>
@@ -18109,7 +18115,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="48" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="B31" s="48" t="s">
         <v>1441</v>
@@ -18118,7 +18124,7 @@
         <v>65</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="E31" s="48">
         <v>54</v>
@@ -18126,7 +18132,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="63" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="B32" s="63" t="s">
         <v>2036</v>
@@ -18135,7 +18141,7 @@
         <v>65</v>
       </c>
       <c r="D32" s="65" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="E32" s="63">
         <v>62</v>
@@ -18143,7 +18149,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="63" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="B33" s="63" t="s">
         <v>2036</v>
@@ -18152,7 +18158,7 @@
         <v>65</v>
       </c>
       <c r="D33" s="65" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="E33" s="63">
         <v>14</v>
@@ -18160,7 +18166,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="48" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="B34" s="48" t="s">
         <v>2036</v>
@@ -18169,13 +18175,13 @@
         <v>65</v>
       </c>
       <c r="D34" s="50" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="E34" s="48">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18194,16 +18200,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="60" t="s">
+        <v>3199</v>
+      </c>
+      <c r="B36" s="60" t="s">
         <v>3200</v>
-      </c>
-      <c r="B36" s="60" t="s">
-        <v>3201</v>
       </c>
       <c r="C36" s="58" t="s">
         <v>65</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="E36" s="49">
         <v>118</v>
@@ -18211,7 +18217,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="48" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="B37" s="48" t="s">
         <v>378</v>
@@ -18228,7 +18234,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="63" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B38" s="63" t="s">
         <v>2694</v>
@@ -18237,7 +18243,7 @@
         <v>65</v>
       </c>
       <c r="D38" s="65" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="E38" s="63">
         <v>103</v>
@@ -18262,16 +18268,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="60" t="s">
+        <v>3205</v>
+      </c>
+      <c r="B40" s="60" t="s">
         <v>3206</v>
-      </c>
-      <c r="B40" s="60" t="s">
-        <v>3207</v>
       </c>
       <c r="C40" s="58" t="s">
         <v>65</v>
       </c>
       <c r="D40" s="50" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="E40" s="49">
         <v>83</v>
@@ -18288,7 +18294,7 @@
         <v>65</v>
       </c>
       <c r="D41" s="50" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="E41" s="49">
         <v>114</v>
@@ -18296,7 +18302,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="48" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="B42" s="48" t="s">
         <v>1498</v>
@@ -18311,8 +18317,30 @@
         <v>79</v>
       </c>
     </row>
+    <row r="43" spans="1:5" ht="31.5">
+      <c r="A43" s="60" t="s">
+        <v>3210</v>
+      </c>
+      <c r="B43" s="60" t="s">
+        <v>2922</v>
+      </c>
+      <c r="C43" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="50">
+        <v>46202</v>
+      </c>
+      <c r="E43" s="49">
+        <v>967</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="6" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -18322,12 +18350,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19282,7 +19310,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19401,7 +19429,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -19812,12 +19840,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19854,7 +19882,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -19888,7 +19916,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20007,7 +20035,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20075,7 +20103,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20109,7 +20137,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -20551,7 +20579,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -20809,12 +20837,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20919,7 +20947,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -20987,7 +21015,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21038,7 +21066,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21106,7 +21134,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -21480,7 +21508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -21548,7 +21576,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -21718,7 +21746,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -21973,7 +22001,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22364,7 +22392,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22432,7 +22460,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -22534,7 +22562,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -22551,7 +22579,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -22602,7 +22630,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -22670,7 +22698,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -22704,7 +22732,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -22772,7 +22800,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -22806,7 +22834,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -22823,7 +22851,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -22891,7 +22919,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23027,7 +23055,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23197,7 +23225,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23384,7 +23412,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -23727,13 +23755,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -24790,7 +24818,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -24824,7 +24852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -24943,7 +24971,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -24977,7 +25005,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25232,7 +25260,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25300,7 +25328,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -25609,13 +25637,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25737,7 +25765,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26162,7 +26190,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -26570,7 +26598,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -26913,13 +26941,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27413,7 +27441,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -27787,7 +27815,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28008,7 +28036,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28042,7 +28070,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -28521,13 +28549,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28547,7 +28575,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -28615,7 +28643,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -28666,7 +28694,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -28785,7 +28813,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -28921,7 +28949,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29023,7 +29051,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29040,7 +29068,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29057,7 +29085,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29159,7 +29187,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29227,7 +29255,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29397,7 +29425,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29448,7 +29476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -29720,7 +29748,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -29907,7 +29935,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30233,13 +30261,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30344,7 +30372,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32047,13 +32075,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33178,7 +33206,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33195,7 +33223,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34249,7 +34277,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34308,13 +34336,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -36718,16 +36746,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -36744,7 +36772,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -36761,7 +36789,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -36778,7 +36806,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -36795,7 +36823,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -36812,7 +36840,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -36829,7 +36857,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -36846,7 +36874,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -36863,7 +36891,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -36880,7 +36908,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -36897,7 +36925,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -36914,7 +36942,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -36931,7 +36959,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -36948,7 +36976,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -36965,7 +36993,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -36982,7 +37010,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -36999,7 +37027,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37016,7 +37044,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37033,7 +37061,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37050,7 +37078,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37067,7 +37095,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37084,7 +37112,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37101,7 +37129,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37118,7 +37146,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37135,7 +37163,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37152,7 +37180,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37169,7 +37197,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37186,7 +37214,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37203,7 +37231,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37220,7 +37248,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37237,7 +37265,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37254,7 +37282,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37271,7 +37299,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37288,7 +37316,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37305,7 +37333,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37322,7 +37350,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37339,7 +37367,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37356,7 +37384,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37373,7 +37401,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37390,7 +37418,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37407,7 +37435,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37424,7 +37452,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37441,7 +37469,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37458,7 +37486,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -37475,7 +37503,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -37492,7 +37520,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -37509,7 +37537,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -37526,7 +37554,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -37543,7 +37571,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -37560,7 +37588,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37577,7 +37605,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -37594,7 +37622,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37611,7 +37639,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -37628,7 +37656,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -37645,7 +37673,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -37662,7 +37690,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -37679,7 +37707,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -37696,7 +37724,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -37713,7 +37741,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -37730,7 +37758,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -37747,7 +37775,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37764,7 +37792,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -37781,7 +37809,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -37798,7 +37826,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -37815,7 +37843,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -37832,7 +37860,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -37849,7 +37877,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -37866,7 +37894,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -37883,7 +37911,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37900,7 +37928,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37917,7 +37945,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -37934,7 +37962,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -37951,7 +37979,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -37968,7 +37996,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -37985,7 +38013,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38002,7 +38030,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38019,7 +38047,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38036,7 +38064,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38053,7 +38081,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38070,7 +38098,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38087,7 +38115,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38104,7 +38132,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38121,7 +38149,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38138,7 +38166,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38155,7 +38183,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38172,7 +38200,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38189,7 +38217,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38206,7 +38234,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38223,7 +38251,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38240,7 +38268,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38257,7 +38285,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38274,7 +38302,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38291,7 +38319,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38308,7 +38336,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38325,7 +38353,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38342,7 +38370,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38359,7 +38387,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38376,7 +38404,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38393,7 +38421,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38410,7 +38438,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38427,7 +38455,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38444,7 +38472,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38461,7 +38489,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -38478,7 +38506,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -38495,7 +38523,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -38512,7 +38540,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -38529,7 +38557,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -38546,7 +38574,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -38563,7 +38591,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -38580,7 +38608,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -38616,14 +38644,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40228,14 +40256,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40865,7 +40893,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -41948,14 +41976,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -43687,13 +43715,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45431,14 +45459,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45577,7 +45605,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -45594,7 +45622,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -45645,7 +45673,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -45713,7 +45741,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -45764,7 +45792,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -45798,7 +45826,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46019,7 +46047,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46087,7 +46115,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46155,7 +46183,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46359,7 +46387,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -46597,7 +46625,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46665,7 +46693,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -46911,7 +46939,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47013,7 +47041,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47030,7 +47058,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47064,7 +47092,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47081,7 +47109,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47132,7 +47160,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47251,7 +47279,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47322,14 +47350,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -48573,7 +48601,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -48862,7 +48890,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49100,7 +49128,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49117,7 +49145,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49151,7 +49179,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49272,14 +49300,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50029,14 +50057,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50430,7 +50458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -50617,7 +50645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -50913,13 +50941,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51007,7 +51035,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51245,7 +51273,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -51568,7 +51596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -51585,7 +51613,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -51602,7 +51630,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -51619,7 +51647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -51653,7 +51681,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -51891,7 +51919,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -51908,7 +51936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52078,7 +52106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52163,7 +52191,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52316,7 +52344,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -52503,7 +52531,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -52605,7 +52633,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -52622,7 +52650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -52775,7 +52803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -52792,7 +52820,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -52877,7 +52905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -52928,7 +52956,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53200,7 +53228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53353,7 +53381,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53421,7 +53449,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53455,7 +53483,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -53472,7 +53500,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -53727,7 +53755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -53897,7 +53925,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -53948,7 +53976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54033,7 +54061,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54118,7 +54146,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -54696,7 +54724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55056,12 +55084,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55200,7 +55228,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -55727,7 +55755,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56067,7 +56095,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56084,7 +56112,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56101,7 +56129,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56186,7 +56214,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56339,7 +56367,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56356,7 +56384,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56407,7 +56435,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -56529,12 +56557,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57013,7 +57041,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57438,7 +57466,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/4.2.26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B1AC58D-8F16-4F12-B923-C793E5250E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B7BEA8E-3058-4C39-903F-44C5DEE62960}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -13980,6 +13980,9 @@
     <t>Arrow Fastener</t>
   </si>
   <si>
+    <t>5/1/26, 6/5/26, 7/26, 8/26</t>
+  </si>
+  <si>
     <t>Scudetto Logistics</t>
   </si>
   <si>
@@ -14073,10 +14076,7 @@
     <t>O.C.E.A.N Inc.</t>
   </si>
   <si>
-    <t>Bayonne University Hospital</t>
-  </si>
-  <si>
-    <t>5/1/2026, 6/5/2026, 7/2026, 8/2026, 9/4/26</t>
+    <t xml:space="preserve">Alan Ritchey, Inc. </t>
   </si>
 </sst>
 </file>
@@ -17590,16 +17590,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17637,7 +17634,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17688,7 +17685,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17705,7 +17702,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17722,7 +17719,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17739,7 +17736,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17756,7 +17753,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17807,7 +17804,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17824,7 +17821,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17909,7 +17906,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -17920,15 +17917,15 @@
         <v>64</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>3211</v>
+        <v>3179</v>
       </c>
       <c r="E19" s="48">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="60" t="s">
-        <v>3179</v>
+        <v>3180</v>
       </c>
       <c r="B20" s="60" t="s">
         <v>2590</v>
@@ -17945,7 +17942,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="48" t="s">
-        <v>3180</v>
+        <v>3181</v>
       </c>
       <c r="B21" s="48" t="s">
         <v>3039</v>
@@ -17954,7 +17951,7 @@
         <v>64</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>3181</v>
+        <v>3182</v>
       </c>
       <c r="E21" s="48">
         <v>82</v>
@@ -17977,7 +17974,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -17988,15 +17985,15 @@
         <v>64</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>3182</v>
+        <v>3183</v>
       </c>
       <c r="E23" s="63">
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
-        <v>3183</v>
+        <v>3184</v>
       </c>
       <c r="B24" s="48" t="s">
         <v>2596</v>
@@ -18005,13 +18002,13 @@
         <v>64</v>
       </c>
       <c r="D24" s="50" t="s">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="E24" s="48">
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18022,7 +18019,7 @@
         <v>64</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>3185</v>
+        <v>3186</v>
       </c>
       <c r="E25" s="49">
         <v>141</v>
@@ -18030,7 +18027,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="60" t="s">
-        <v>3186</v>
+        <v>3187</v>
       </c>
       <c r="B26" s="60" t="s">
         <v>3168</v>
@@ -18047,7 +18044,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="48" t="s">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="B27" s="48" t="s">
         <v>1464</v>
@@ -18064,7 +18061,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="48" t="s">
-        <v>3188</v>
+        <v>3189</v>
       </c>
       <c r="B28" s="48" t="s">
         <v>1526</v>
@@ -18081,24 +18078,24 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="48" t="s">
-        <v>3189</v>
+        <v>3190</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>3190</v>
+        <v>3191</v>
       </c>
       <c r="C29" s="49" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="E29" s="48">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="B30" s="60" t="s">
         <v>1441</v>
@@ -18115,7 +18112,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="48" t="s">
-        <v>3193</v>
+        <v>3194</v>
       </c>
       <c r="B31" s="48" t="s">
         <v>1441</v>
@@ -18124,7 +18121,7 @@
         <v>65</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>3194</v>
+        <v>3195</v>
       </c>
       <c r="E31" s="48">
         <v>54</v>
@@ -18132,7 +18129,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="63" t="s">
-        <v>3195</v>
+        <v>3196</v>
       </c>
       <c r="B32" s="63" t="s">
         <v>2036</v>
@@ -18141,7 +18138,7 @@
         <v>65</v>
       </c>
       <c r="D32" s="65" t="s">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="E32" s="63">
         <v>62</v>
@@ -18149,7 +18146,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="63" t="s">
-        <v>3197</v>
+        <v>3198</v>
       </c>
       <c r="B33" s="63" t="s">
         <v>2036</v>
@@ -18158,7 +18155,7 @@
         <v>65</v>
       </c>
       <c r="D33" s="65" t="s">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="E33" s="63">
         <v>14</v>
@@ -18166,7 +18163,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="48" t="s">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="B34" s="48" t="s">
         <v>2036</v>
@@ -18175,13 +18172,13 @@
         <v>65</v>
       </c>
       <c r="D34" s="50" t="s">
-        <v>3196</v>
+        <v>3197</v>
       </c>
       <c r="E34" s="48">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18200,16 +18197,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="60" t="s">
-        <v>3199</v>
+        <v>3200</v>
       </c>
       <c r="B36" s="60" t="s">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="C36" s="58" t="s">
         <v>65</v>
       </c>
       <c r="D36" s="50" t="s">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="E36" s="49">
         <v>118</v>
@@ -18217,7 +18214,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="48" t="s">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="B37" s="48" t="s">
         <v>378</v>
@@ -18234,7 +18231,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="63" t="s">
-        <v>3203</v>
+        <v>3204</v>
       </c>
       <c r="B38" s="63" t="s">
         <v>2694</v>
@@ -18243,7 +18240,7 @@
         <v>65</v>
       </c>
       <c r="D38" s="65" t="s">
-        <v>3204</v>
+        <v>3205</v>
       </c>
       <c r="E38" s="63">
         <v>103</v>
@@ -18268,16 +18265,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="60" t="s">
-        <v>3205</v>
+        <v>3206</v>
       </c>
       <c r="B40" s="60" t="s">
-        <v>3206</v>
+        <v>3207</v>
       </c>
       <c r="C40" s="58" t="s">
         <v>65</v>
       </c>
       <c r="D40" s="50" t="s">
-        <v>3207</v>
+        <v>3208</v>
       </c>
       <c r="E40" s="49">
         <v>83</v>
@@ -18294,7 +18291,7 @@
         <v>65</v>
       </c>
       <c r="D41" s="50" t="s">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="E41" s="49">
         <v>114</v>
@@ -18302,7 +18299,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="48" t="s">
-        <v>3209</v>
+        <v>3210</v>
       </c>
       <c r="B42" s="48" t="s">
         <v>1498</v>
@@ -18317,30 +18314,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5">
       <c r="A43" s="60" t="s">
-        <v>3210</v>
+        <v>3211</v>
       </c>
       <c r="B43" s="60" t="s">
-        <v>2922</v>
+        <v>2963</v>
       </c>
       <c r="C43" s="58" t="s">
         <v>66</v>
       </c>
       <c r="D43" s="50">
-        <v>46202</v>
+        <v>46220</v>
       </c>
       <c r="E43" s="49">
-        <v>967</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="6" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
-    <oddFooter>&amp;CPage &amp;P</oddFooter>
-  </headerFooter>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18350,12 +18343,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19310,7 +19303,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19429,7 +19422,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -19840,12 +19833,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19882,7 +19875,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -19916,7 +19909,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20035,7 +20028,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20103,7 +20096,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20137,7 +20130,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -20579,7 +20572,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -20837,12 +20830,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20947,7 +20940,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21015,7 +21008,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21066,7 +21059,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21134,7 +21127,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -21508,7 +21501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -21576,7 +21569,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -21746,7 +21739,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22001,7 +21994,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22392,7 +22385,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22460,7 +22453,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -22562,7 +22555,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -22579,7 +22572,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -22630,7 +22623,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -22698,7 +22691,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -22732,7 +22725,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -22800,7 +22793,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -22834,7 +22827,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -22851,7 +22844,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -22919,7 +22912,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23055,7 +23048,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23225,7 +23218,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23412,7 +23405,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -23755,13 +23748,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -24818,7 +24811,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -24852,7 +24845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -24971,7 +24964,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25005,7 +24998,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25260,7 +25253,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25328,7 +25321,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -25637,13 +25630,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25765,7 +25758,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26190,7 +26183,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -26598,7 +26591,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -26941,13 +26934,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27441,7 +27434,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -27815,7 +27808,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28036,7 +28029,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28070,7 +28063,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -28549,13 +28542,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28575,7 +28568,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -28643,7 +28636,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -28694,7 +28687,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -28813,7 +28806,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -28949,7 +28942,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29051,7 +29044,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29068,7 +29061,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29085,7 +29078,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29187,7 +29180,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29255,7 +29248,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29425,7 +29418,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29476,7 +29469,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -29748,7 +29741,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -29935,7 +29928,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30261,13 +30254,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30372,7 +30365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32075,13 +32068,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33206,7 +33199,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33223,7 +33216,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34277,7 +34270,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34336,13 +34329,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -36746,16 +36739,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -36772,7 +36765,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -36789,7 +36782,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -36806,7 +36799,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -36823,7 +36816,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -36840,7 +36833,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -36857,7 +36850,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -36874,7 +36867,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -36891,7 +36884,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -36908,7 +36901,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -36925,7 +36918,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -36942,7 +36935,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -36959,7 +36952,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -36976,7 +36969,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -36993,7 +36986,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37010,7 +37003,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37027,7 +37020,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37044,7 +37037,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37061,7 +37054,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37078,7 +37071,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37095,7 +37088,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37112,7 +37105,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37129,7 +37122,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37146,7 +37139,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37163,7 +37156,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37180,7 +37173,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37197,7 +37190,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37214,7 +37207,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37231,7 +37224,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37248,7 +37241,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37265,7 +37258,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37282,7 +37275,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37299,7 +37292,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37316,7 +37309,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37333,7 +37326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37350,7 +37343,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37367,7 +37360,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37384,7 +37377,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37401,7 +37394,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37418,7 +37411,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37435,7 +37428,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37452,7 +37445,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37469,7 +37462,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37486,7 +37479,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -37503,7 +37496,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -37520,7 +37513,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -37537,7 +37530,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -37554,7 +37547,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -37571,7 +37564,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -37588,7 +37581,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37605,7 +37598,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -37622,7 +37615,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37639,7 +37632,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -37656,7 +37649,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -37673,7 +37666,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -37690,7 +37683,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -37707,7 +37700,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -37724,7 +37717,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -37741,7 +37734,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -37758,7 +37751,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -37775,7 +37768,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37792,7 +37785,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -37809,7 +37802,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -37826,7 +37819,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -37843,7 +37836,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -37860,7 +37853,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -37877,7 +37870,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -37894,7 +37887,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -37911,7 +37904,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37928,7 +37921,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37945,7 +37938,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -37962,7 +37955,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -37979,7 +37972,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -37996,7 +37989,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38013,7 +38006,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38030,7 +38023,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38047,7 +38040,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38064,7 +38057,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38081,7 +38074,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38098,7 +38091,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38115,7 +38108,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38132,7 +38125,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38149,7 +38142,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38166,7 +38159,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38183,7 +38176,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38200,7 +38193,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38217,7 +38210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38234,7 +38227,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38251,7 +38244,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38268,7 +38261,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38285,7 +38278,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38302,7 +38295,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38319,7 +38312,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38336,7 +38329,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38353,7 +38346,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38370,7 +38363,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38387,7 +38380,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38404,7 +38397,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38421,7 +38414,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38438,7 +38431,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38455,7 +38448,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38472,7 +38465,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38489,7 +38482,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -38506,7 +38499,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -38523,7 +38516,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -38540,7 +38533,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -38557,7 +38550,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -38574,7 +38567,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -38591,7 +38584,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -38608,7 +38601,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -38644,14 +38637,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40256,14 +40249,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40893,7 +40886,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -41976,14 +41969,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -43715,13 +43708,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45459,14 +45452,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45605,7 +45598,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -45622,7 +45615,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -45673,7 +45666,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -45741,7 +45734,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -45792,7 +45785,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -45826,7 +45819,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46047,7 +46040,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46115,7 +46108,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46183,7 +46176,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46387,7 +46380,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -46625,7 +46618,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46693,7 +46686,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -46939,7 +46932,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47041,7 +47034,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47058,7 +47051,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47092,7 +47085,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47109,7 +47102,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47160,7 +47153,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47279,7 +47272,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47350,14 +47343,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -48601,7 +48594,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -48890,7 +48883,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49128,7 +49121,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49145,7 +49138,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49179,7 +49172,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49300,14 +49293,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50057,14 +50050,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50458,7 +50451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -50645,7 +50638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -50941,13 +50934,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51035,7 +51028,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51273,7 +51266,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -51596,7 +51589,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -51613,7 +51606,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -51630,7 +51623,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -51647,7 +51640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -51681,7 +51674,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -51919,7 +51912,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -51936,7 +51929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52106,7 +52099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52191,7 +52184,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52344,7 +52337,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -52531,7 +52524,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -52633,7 +52626,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -52650,7 +52643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -52803,7 +52796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -52820,7 +52813,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -52905,7 +52898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -52956,7 +52949,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53228,7 +53221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53381,7 +53374,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53449,7 +53442,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53483,7 +53476,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -53500,7 +53493,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -53755,7 +53748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -53925,7 +53918,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -53976,7 +53969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54061,7 +54054,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54146,7 +54139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -54724,7 +54717,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55084,12 +55077,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55228,7 +55221,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -55755,7 +55748,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56095,7 +56088,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56112,7 +56105,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56129,7 +56122,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56214,7 +56207,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56367,7 +56360,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56384,7 +56377,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56435,7 +56428,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -56540,7 +56533,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="18" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="40" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -56557,12 +56550,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57041,7 +57034,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57466,7 +57459,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B7BEA8E-3058-4C39-903F-44C5DEE62960}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9675EB3-C94C-41DD-9EEF-EDFB943E1A0A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7468" uniqueCount="3212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7472" uniqueCount="3213">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14077,6 +14077,9 @@
   </si>
   <si>
     <t xml:space="preserve">Alan Ritchey, Inc. </t>
+  </si>
+  <si>
+    <t>7/16/26 - 12/31/26</t>
   </si>
 </sst>
 </file>
@@ -16976,6 +16979,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17590,7 +17597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18329,6 +18336,23 @@
       </c>
       <c r="E43" s="49">
         <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="48" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B44" s="48" t="s">
+        <v>2968</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" s="50" t="s">
+        <v>3212</v>
+      </c>
+      <c r="E44" s="48">
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9675EB3-C94C-41DD-9EEF-EDFB943E1A0A}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{121C0FEC-C282-475C-AD0F-36C24B637D9D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7472" uniqueCount="3213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7476" uniqueCount="3214">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14080,6 +14080,9 @@
   </si>
   <si>
     <t>7/16/26 - 12/31/26</t>
+  </si>
+  <si>
+    <t>5/4/26 and 5/19/26</t>
   </si>
 </sst>
 </file>
@@ -16979,10 +16982,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17597,7 +17596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18353,6 +18352,23 @@
       </c>
       <c r="E44" s="48">
         <v>206</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="60" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B45" s="60" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C45" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>3213</v>
+      </c>
+      <c r="E45" s="49">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/4.22.26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{121C0FEC-C282-475C-AD0F-36C24B637D9D}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{914FEAB3-B71C-4C6D-8C6B-7679DA6B2D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1291CDF5-AC74-4224-8386-EF0A9EB7A119}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7476" uniqueCount="3214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7479" uniqueCount="3215">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14083,6 +14083,9 @@
   </si>
   <si>
     <t>5/4/26 and 5/19/26</t>
+  </si>
+  <si>
+    <t>Sandy Alexander</t>
   </si>
 </sst>
 </file>
@@ -17596,13 +17599,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E45"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17640,7 +17643,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17691,7 +17694,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17708,7 +17711,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17725,7 +17728,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17742,7 +17745,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17759,7 +17762,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17810,7 +17813,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17827,7 +17830,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17912,7 +17915,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -17980,7 +17983,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -17997,7 +18000,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18014,7 +18017,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18099,7 +18102,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18184,7 +18187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18371,9 +18374,30 @@
         <v>87</v>
       </c>
     </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="48" t="s">
+        <v>3214</v>
+      </c>
+      <c r="B46" s="48" t="s">
+        <v>2587</v>
+      </c>
+      <c r="C46" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" s="50">
+        <v>46222</v>
+      </c>
+      <c r="E46" s="48">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="landscape" verticalDpi="1200" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -18383,12 +18407,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19343,7 +19367,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19462,7 +19486,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -19873,12 +19897,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19915,7 +19939,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -19949,7 +19973,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20068,7 +20092,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20136,7 +20160,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20170,7 +20194,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -20612,7 +20636,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -20870,12 +20894,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20980,7 +21004,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21048,7 +21072,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21099,7 +21123,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21167,7 +21191,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -21541,7 +21565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -21609,7 +21633,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -21779,7 +21803,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22034,7 +22058,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22425,7 +22449,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22493,7 +22517,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -22595,7 +22619,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -22612,7 +22636,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -22663,7 +22687,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -22731,7 +22755,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -22765,7 +22789,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -22833,7 +22857,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -22867,7 +22891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -22884,7 +22908,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -22952,7 +22976,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23088,7 +23112,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23258,7 +23282,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23445,7 +23469,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -23788,13 +23812,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -24851,7 +24875,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -24885,7 +24909,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25004,7 +25028,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25038,7 +25062,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25293,7 +25317,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25361,7 +25385,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -25670,13 +25694,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25798,7 +25822,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26223,7 +26247,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -26631,7 +26655,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -26974,13 +26998,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27474,7 +27498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -27848,7 +27872,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28069,7 +28093,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28103,7 +28127,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -28582,13 +28606,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28608,7 +28632,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -28676,7 +28700,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -28727,7 +28751,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -28846,7 +28870,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -28982,7 +29006,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29084,7 +29108,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29101,7 +29125,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29118,7 +29142,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29220,7 +29244,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29288,7 +29312,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29458,7 +29482,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29509,7 +29533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -29781,7 +29805,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -29968,7 +29992,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30294,13 +30318,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30405,7 +30429,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32108,13 +32132,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33239,7 +33263,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33256,7 +33280,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34310,7 +34334,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34369,13 +34393,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -36779,16 +36803,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -36805,7 +36829,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -36822,7 +36846,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -36839,7 +36863,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -36856,7 +36880,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -36873,7 +36897,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -36890,7 +36914,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -36907,7 +36931,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -36924,7 +36948,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -36941,7 +36965,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -36958,7 +36982,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -36975,7 +36999,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -36992,7 +37016,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37009,7 +37033,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37026,7 +37050,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37043,7 +37067,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37060,7 +37084,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37077,7 +37101,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37094,7 +37118,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37111,7 +37135,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37128,7 +37152,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37145,7 +37169,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37162,7 +37186,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37179,7 +37203,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37196,7 +37220,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37213,7 +37237,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37230,7 +37254,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37247,7 +37271,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37264,7 +37288,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37281,7 +37305,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37298,7 +37322,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37315,7 +37339,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37332,7 +37356,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37349,7 +37373,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37366,7 +37390,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37383,7 +37407,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37400,7 +37424,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37417,7 +37441,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37434,7 +37458,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37451,7 +37475,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37468,7 +37492,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37485,7 +37509,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37502,7 +37526,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37519,7 +37543,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -37536,7 +37560,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -37553,7 +37577,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -37570,7 +37594,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -37587,7 +37611,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -37604,7 +37628,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -37621,7 +37645,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37638,7 +37662,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -37655,7 +37679,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37672,7 +37696,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -37689,7 +37713,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -37706,7 +37730,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -37723,7 +37747,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -37740,7 +37764,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -37757,7 +37781,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -37774,7 +37798,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -37791,7 +37815,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -37808,7 +37832,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37825,7 +37849,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -37842,7 +37866,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -37859,7 +37883,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -37876,7 +37900,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -37893,7 +37917,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -37910,7 +37934,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -37927,7 +37951,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -37944,7 +37968,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37961,7 +37985,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37978,7 +38002,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -37995,7 +38019,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38012,7 +38036,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38029,7 +38053,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38046,7 +38070,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38063,7 +38087,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38080,7 +38104,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38097,7 +38121,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38114,7 +38138,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38131,7 +38155,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38148,7 +38172,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38165,7 +38189,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38182,7 +38206,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38199,7 +38223,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38216,7 +38240,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38233,7 +38257,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38250,7 +38274,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38267,7 +38291,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38284,7 +38308,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38301,7 +38325,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38318,7 +38342,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38335,7 +38359,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38352,7 +38376,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38369,7 +38393,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38386,7 +38410,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38403,7 +38427,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38420,7 +38444,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38437,7 +38461,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38454,7 +38478,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38471,7 +38495,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38488,7 +38512,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38505,7 +38529,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38522,7 +38546,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -38539,7 +38563,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -38556,7 +38580,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -38573,7 +38597,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -38590,7 +38614,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -38607,7 +38631,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -38624,7 +38648,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -38641,7 +38665,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -38677,14 +38701,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40289,14 +40313,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40926,7 +40950,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42009,14 +42033,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -43748,13 +43772,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45492,14 +45516,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45638,7 +45662,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -45655,7 +45679,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -45706,7 +45730,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -45774,7 +45798,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -45825,7 +45849,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -45859,7 +45883,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46080,7 +46104,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46148,7 +46172,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46216,7 +46240,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46420,7 +46444,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -46658,7 +46682,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46726,7 +46750,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -46972,7 +46996,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47074,7 +47098,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47091,7 +47115,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47125,7 +47149,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47142,7 +47166,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47193,7 +47217,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47312,7 +47336,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47383,14 +47407,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -48634,7 +48658,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -48923,7 +48947,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49161,7 +49185,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49178,7 +49202,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49212,7 +49236,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49333,14 +49357,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50090,14 +50114,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50491,7 +50515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -50678,7 +50702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -50974,13 +50998,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51068,7 +51092,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51306,7 +51330,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -51629,7 +51653,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -51646,7 +51670,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -51663,7 +51687,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -51680,7 +51704,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -51714,7 +51738,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -51952,7 +51976,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -51969,7 +51993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52139,7 +52163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52224,7 +52248,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52377,7 +52401,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -52564,7 +52588,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -52666,7 +52690,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -52683,7 +52707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -52836,7 +52860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -52853,7 +52877,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -52938,7 +52962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -52989,7 +53013,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53261,7 +53285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53414,7 +53438,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53482,7 +53506,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53516,7 +53540,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -53533,7 +53557,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -53788,7 +53812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -53958,7 +53982,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54009,7 +54033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54094,7 +54118,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54179,7 +54203,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -54757,7 +54781,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55117,12 +55141,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55261,7 +55285,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -55788,7 +55812,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56128,7 +56152,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56145,7 +56169,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56162,7 +56186,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56247,7 +56271,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56400,7 +56424,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56417,7 +56441,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56468,7 +56492,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -56590,12 +56614,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57074,7 +57098,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57499,7 +57523,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/4.22.26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/4.23.26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{914FEAB3-B71C-4C6D-8C6B-7679DA6B2D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1291CDF5-AC74-4224-8386-EF0A9EB7A119}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC1E971F-6BD0-4AEE-AA26-1CE8D60738F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7479" uniqueCount="3215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7482" uniqueCount="3216">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14086,6 +14086,9 @@
   </si>
   <si>
     <t>Sandy Alexander</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lakewood Public Schools </t>
   </si>
 </sst>
 </file>
@@ -17599,7 +17602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18389,6 +18392,23 @@
       </c>
       <c r="E46" s="48">
         <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="48" t="s">
+        <v>3215</v>
+      </c>
+      <c r="B47" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" s="50">
+        <v>46203</v>
+      </c>
+      <c r="E47" s="48">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/4.23.26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC1E971F-6BD0-4AEE-AA26-1CE8D60738F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB908FED-2474-4F69-BDB1-ED1BCFC45F25}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7482" uniqueCount="3216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7480" uniqueCount="3215">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14085,10 +14085,7 @@
     <t>5/4/26 and 5/19/26</t>
   </si>
   <si>
-    <t>Sandy Alexander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lakewood Public Schools </t>
+    <t>7/24/26 - 11/20/26</t>
   </si>
 </sst>
 </file>
@@ -17602,7 +17599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18190,7 +18187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18378,46 +18375,25 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="48" t="s">
+      <c r="A46" s="60" t="s">
+        <v>2992</v>
+      </c>
+      <c r="B46" s="60" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C46" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" s="50" t="s">
         <v>3214</v>
       </c>
-      <c r="B46" s="48" t="s">
-        <v>2587</v>
-      </c>
-      <c r="C46" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="D46" s="50">
-        <v>46222</v>
-      </c>
-      <c r="E46" s="48">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="48" t="s">
-        <v>3215</v>
-      </c>
-      <c r="B47" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="C47" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="D47" s="50">
-        <v>46203</v>
-      </c>
-      <c r="E47" s="48">
-        <v>164</v>
+      <c r="E46" s="49">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" verticalDpi="1200" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
-    <oddFooter>Page &amp;P</oddFooter>
-  </headerFooter>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -37546,7 +37522,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38668,7 +38644,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="195" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB908FED-2474-4F69-BDB1-ED1BCFC45F25}"/>
+  <xr:revisionPtr revIDLastSave="196" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77341FAD-28D5-45BD-83F2-36E1E26DC934}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7480" uniqueCount="3215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7484" uniqueCount="3218">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14086,6 +14086,15 @@
   </si>
   <si>
     <t>7/24/26 - 11/20/26</t>
+  </si>
+  <si>
+    <t>FreshRealm</t>
+  </si>
+  <si>
+    <t>Linden</t>
+  </si>
+  <si>
+    <t>6/27/26 - 727/26</t>
   </si>
 </sst>
 </file>
@@ -16985,6 +16994,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17599,13 +17612,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17643,7 +17656,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17694,7 +17707,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17711,7 +17724,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17728,7 +17741,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17745,7 +17758,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17762,7 +17775,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17813,7 +17826,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17830,7 +17843,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17915,7 +17928,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -17983,7 +17996,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18000,7 +18013,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18017,7 +18030,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18102,7 +18115,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18389,6 +18402,23 @@
       </c>
       <c r="E46" s="49">
         <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="48" t="s">
+        <v>3215</v>
+      </c>
+      <c r="B47" s="48" t="s">
+        <v>3216</v>
+      </c>
+      <c r="C47" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" s="50" t="s">
+        <v>3217</v>
+      </c>
+      <c r="E47" s="48">
+        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -18403,12 +18433,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19363,7 +19393,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19482,7 +19512,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -19893,12 +19923,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19935,7 +19965,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -19969,7 +19999,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20088,7 +20118,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20156,7 +20186,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20190,7 +20220,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -20632,7 +20662,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -20890,12 +20920,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21000,7 +21030,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21068,7 +21098,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21119,7 +21149,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21187,7 +21217,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -21561,7 +21591,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -21629,7 +21659,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -21799,7 +21829,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22054,7 +22084,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22445,7 +22475,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22513,7 +22543,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -22615,7 +22645,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -22632,7 +22662,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -22683,7 +22713,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -22751,7 +22781,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -22785,7 +22815,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -22853,7 +22883,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -22887,7 +22917,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -22904,7 +22934,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -22972,7 +23002,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23108,7 +23138,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23278,7 +23308,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23465,7 +23495,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -23808,13 +23838,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -24871,7 +24901,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -24905,7 +24935,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25024,7 +25054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25058,7 +25088,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25313,7 +25343,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25381,7 +25411,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -25690,13 +25720,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25818,7 +25848,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26243,7 +26273,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -26651,7 +26681,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -26994,13 +27024,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27494,7 +27524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -27868,7 +27898,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28089,7 +28119,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28123,7 +28153,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -28602,13 +28632,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28628,7 +28658,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -28696,7 +28726,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -28747,7 +28777,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -28866,7 +28896,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29002,7 +29032,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29104,7 +29134,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29121,7 +29151,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29138,7 +29168,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29240,7 +29270,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29308,7 +29338,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29478,7 +29508,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29529,7 +29559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -29801,7 +29831,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -29988,7 +30018,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30314,13 +30344,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30425,7 +30455,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32128,13 +32158,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33259,7 +33289,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33276,7 +33306,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34330,7 +34360,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34389,13 +34419,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -36799,16 +36829,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -36825,7 +36855,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -36842,7 +36872,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -36859,7 +36889,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -36876,7 +36906,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -36893,7 +36923,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -36910,7 +36940,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -36927,7 +36957,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -36944,7 +36974,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -36961,7 +36991,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -36978,7 +37008,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -36995,7 +37025,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37012,7 +37042,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37029,7 +37059,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37046,7 +37076,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37063,7 +37093,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37080,7 +37110,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37097,7 +37127,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37114,7 +37144,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37131,7 +37161,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37148,7 +37178,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37165,7 +37195,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37182,7 +37212,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37199,7 +37229,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37216,7 +37246,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37233,7 +37263,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37250,7 +37280,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37267,7 +37297,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37284,7 +37314,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37301,7 +37331,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37318,7 +37348,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37335,7 +37365,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37352,7 +37382,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37369,7 +37399,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37386,7 +37416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37403,7 +37433,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37420,7 +37450,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37437,7 +37467,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37454,7 +37484,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37471,7 +37501,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37488,7 +37518,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37505,7 +37535,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37522,7 +37552,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37539,7 +37569,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -37556,7 +37586,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -37573,7 +37603,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -37590,7 +37620,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -37607,7 +37637,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -37624,7 +37654,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -37641,7 +37671,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37658,7 +37688,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -37675,7 +37705,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37692,7 +37722,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -37709,7 +37739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -37726,7 +37756,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -37743,7 +37773,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -37760,7 +37790,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -37777,7 +37807,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -37794,7 +37824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -37811,7 +37841,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -37828,7 +37858,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37845,7 +37875,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -37862,7 +37892,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -37879,7 +37909,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -37896,7 +37926,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -37913,7 +37943,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -37930,7 +37960,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -37947,7 +37977,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -37964,7 +37994,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37981,7 +38011,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37998,7 +38028,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38015,7 +38045,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38032,7 +38062,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38049,7 +38079,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38066,7 +38096,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38083,7 +38113,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38100,7 +38130,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38117,7 +38147,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38134,7 +38164,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38151,7 +38181,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38168,7 +38198,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38185,7 +38215,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38202,7 +38232,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38219,7 +38249,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38236,7 +38266,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38253,7 +38283,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38270,7 +38300,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38287,7 +38317,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38304,7 +38334,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38321,7 +38351,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38338,7 +38368,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38355,7 +38385,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38372,7 +38402,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38389,7 +38419,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38406,7 +38436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38423,7 +38453,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38440,7 +38470,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38457,7 +38487,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38474,7 +38504,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38491,7 +38521,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38508,7 +38538,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38525,7 +38555,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38542,7 +38572,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -38559,7 +38589,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -38576,7 +38606,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -38593,7 +38623,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -38610,7 +38640,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -38627,7 +38657,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -38644,7 +38674,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -38661,7 +38691,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -38697,14 +38727,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40309,14 +40339,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40946,7 +40976,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42029,14 +42059,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -43768,13 +43798,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45512,14 +45542,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45658,7 +45688,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -45675,7 +45705,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -45726,7 +45756,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -45794,7 +45824,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -45845,7 +45875,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -45879,7 +45909,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46100,7 +46130,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46168,7 +46198,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46236,7 +46266,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46440,7 +46470,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -46678,7 +46708,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46746,7 +46776,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -46992,7 +47022,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47094,7 +47124,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47111,7 +47141,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47145,7 +47175,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47162,7 +47192,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47213,7 +47243,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47332,7 +47362,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47403,14 +47433,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -48654,7 +48684,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -48943,7 +48973,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49181,7 +49211,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49198,7 +49228,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49232,7 +49262,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49353,14 +49383,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50110,14 +50140,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50511,7 +50541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -50698,7 +50728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -50994,13 +51024,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51088,7 +51118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51326,7 +51356,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -51649,7 +51679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -51666,7 +51696,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -51683,7 +51713,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -51700,7 +51730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -51734,7 +51764,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -51972,7 +52002,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -51989,7 +52019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52159,7 +52189,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52244,7 +52274,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52397,7 +52427,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -52584,7 +52614,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -52686,7 +52716,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -52703,7 +52733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -52856,7 +52886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -52873,7 +52903,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -52958,7 +52988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53009,7 +53039,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53281,7 +53311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53434,7 +53464,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53502,7 +53532,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53536,7 +53566,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -53553,7 +53583,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -53808,7 +53838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -53978,7 +54008,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54029,7 +54059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54114,7 +54144,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54199,7 +54229,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -54777,7 +54807,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55137,12 +55167,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55281,7 +55311,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -55808,7 +55838,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56148,7 +56178,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56165,7 +56195,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56182,7 +56212,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56267,7 +56297,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56420,7 +56450,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56437,7 +56467,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56488,7 +56518,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -56610,12 +56640,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57094,7 +57124,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57519,7 +57549,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77341FAD-28D5-45BD-83F2-36E1E26DC934}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25B22611-2454-41E2-896A-FC13DFB19399}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7484" uniqueCount="3218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7488" uniqueCount="3220">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14095,6 +14095,12 @@
   </si>
   <si>
     <t>6/27/26 - 727/26</t>
+  </si>
+  <si>
+    <t>Reckitt Benckiser LLC</t>
+  </si>
+  <si>
+    <t>3/2/26 - 3/18/27</t>
   </si>
 </sst>
 </file>
@@ -17612,7 +17618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18419,6 +18425,23 @@
       </c>
       <c r="E47" s="48">
         <v>637</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="58" t="s">
+        <v>3218</v>
+      </c>
+      <c r="B48" s="60" t="s">
+        <v>2980</v>
+      </c>
+      <c r="C48" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="50" t="s">
+        <v>3219</v>
+      </c>
+      <c r="E48" s="49">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25B22611-2454-41E2-896A-FC13DFB19399}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{600E1F22-5ED8-42C6-8CD9-DFAACCAE58EE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7488" uniqueCount="3220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7491" uniqueCount="3221">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14101,6 +14101,9 @@
   </si>
   <si>
     <t>3/2/26 - 3/18/27</t>
+  </si>
+  <si>
+    <t>Federal Express Corporation</t>
   </si>
 </sst>
 </file>
@@ -17618,7 +17621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18442,6 +18445,23 @@
       </c>
       <c r="E48" s="49">
         <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="31.2">
+      <c r="A49" s="48" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B49" s="48" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="50">
+        <v>46237</v>
+      </c>
+      <c r="E49" s="48">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{600E1F22-5ED8-42C6-8CD9-DFAACCAE58EE}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13156083-E00A-4755-8A5A-D3A26A65F0B1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7491" uniqueCount="3221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7495" uniqueCount="3222">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14104,6 +14104,9 @@
   </si>
   <si>
     <t>Federal Express Corporation</t>
+  </si>
+  <si>
+    <t>7/31/26 and 10/2/26</t>
   </si>
 </sst>
 </file>
@@ -17003,10 +17006,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17621,7 +17620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18462,6 +18461,23 @@
       </c>
       <c r="E49" s="48">
         <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="48" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B50" s="48" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C50" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="50" t="s">
+        <v>3221</v>
+      </c>
+      <c r="E50" s="48">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13156083-E00A-4755-8A5A-D3A26A65F0B1}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{304E161D-64EF-4006-B45E-95B6CB4A1B94}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7495" uniqueCount="3222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7492" uniqueCount="3221">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14071,9 +14071,6 @@
   </si>
   <si>
     <t>6/26/26 - 11/27/26</t>
-  </si>
-  <si>
-    <t>O.C.E.A.N Inc.</t>
   </si>
   <si>
     <t xml:space="preserve">Alan Ritchey, Inc. </t>
@@ -17006,6 +17003,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17620,7 +17621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18328,62 +18329,62 @@
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="48" t="s">
+      <c r="A42" s="60" t="s">
         <v>3210</v>
       </c>
-      <c r="B42" s="48" t="s">
-        <v>1498</v>
-      </c>
-      <c r="C42" s="49" t="s">
-        <v>65</v>
+      <c r="B42" s="60" t="s">
+        <v>2963</v>
+      </c>
+      <c r="C42" s="58" t="s">
+        <v>66</v>
       </c>
       <c r="D42" s="50">
-        <v>46204</v>
-      </c>
-      <c r="E42" s="48">
-        <v>79</v>
+        <v>46220</v>
+      </c>
+      <c r="E42" s="49">
+        <v>176</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="60" t="s">
+      <c r="A43" s="48" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B43" s="48" t="s">
+        <v>2968</v>
+      </c>
+      <c r="C43" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="50" t="s">
         <v>3211</v>
       </c>
-      <c r="B43" s="60" t="s">
-        <v>2963</v>
-      </c>
-      <c r="C43" s="58" t="s">
-        <v>66</v>
-      </c>
-      <c r="D43" s="50">
-        <v>46220</v>
-      </c>
-      <c r="E43" s="49">
-        <v>176</v>
+      <c r="E43" s="48">
+        <v>206</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="48" t="s">
-        <v>2870</v>
-      </c>
-      <c r="B44" s="48" t="s">
-        <v>2968</v>
-      </c>
-      <c r="C44" s="49" t="s">
+      <c r="A44" s="60" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B44" s="60" t="s">
+        <v>2911</v>
+      </c>
+      <c r="C44" s="58" t="s">
         <v>66</v>
       </c>
       <c r="D44" s="50" t="s">
         <v>3212</v>
       </c>
-      <c r="E44" s="48">
-        <v>206</v>
+      <c r="E44" s="49">
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="60" t="s">
-        <v>2910</v>
+        <v>2992</v>
       </c>
       <c r="B45" s="60" t="s">
-        <v>2911</v>
+        <v>1519</v>
       </c>
       <c r="C45" s="58" t="s">
         <v>66</v>
@@ -18392,91 +18393,74 @@
         <v>3213</v>
       </c>
       <c r="E45" s="49">
-        <v>87</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="60" t="s">
-        <v>2992</v>
-      </c>
-      <c r="B46" s="60" t="s">
-        <v>1519</v>
-      </c>
-      <c r="C46" s="58" t="s">
+      <c r="A46" s="48" t="s">
+        <v>3214</v>
+      </c>
+      <c r="B46" s="48" t="s">
+        <v>3215</v>
+      </c>
+      <c r="C46" s="49" t="s">
         <v>66</v>
       </c>
       <c r="D46" s="50" t="s">
-        <v>3214</v>
-      </c>
-      <c r="E46" s="49">
-        <v>60</v>
+        <v>3216</v>
+      </c>
+      <c r="E46" s="48">
+        <v>637</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="48" t="s">
-        <v>3215</v>
-      </c>
-      <c r="B47" s="48" t="s">
-        <v>3216</v>
-      </c>
-      <c r="C47" s="49" t="s">
+      <c r="A47" s="58" t="s">
+        <v>3217</v>
+      </c>
+      <c r="B47" s="60" t="s">
+        <v>2980</v>
+      </c>
+      <c r="C47" s="58" t="s">
         <v>66</v>
       </c>
       <c r="D47" s="50" t="s">
-        <v>3217</v>
-      </c>
-      <c r="E47" s="48">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="58" t="s">
         <v>3218</v>
       </c>
-      <c r="B48" s="60" t="s">
-        <v>2980</v>
-      </c>
-      <c r="C48" s="58" t="s">
+      <c r="E47" s="49">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="31.2">
+      <c r="A48" s="48" t="s">
+        <v>3219</v>
+      </c>
+      <c r="B48" s="48" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C48" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="D48" s="50" t="s">
-        <v>3219</v>
-      </c>
-      <c r="E48" s="49">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="31.2">
+      <c r="D48" s="50">
+        <v>46237</v>
+      </c>
+      <c r="E48" s="48">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="48" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B49" s="48" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" s="50" t="s">
         <v>3220</v>
       </c>
-      <c r="B49" s="48" t="s">
-        <v>1447</v>
-      </c>
-      <c r="C49" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="D49" s="50">
-        <v>46237</v>
-      </c>
       <c r="E49" s="48">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="48" t="s">
-        <v>2906</v>
-      </c>
-      <c r="B50" s="48" t="s">
-        <v>2036</v>
-      </c>
-      <c r="C50" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" s="50" t="s">
-        <v>3221</v>
-      </c>
-      <c r="E50" s="48">
         <v>95</v>
       </c>
     </row>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{304E161D-64EF-4006-B45E-95B6CB4A1B94}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB40C49B-D615-46BB-B560-F194C13DF853}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7492" uniqueCount="3221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7501" uniqueCount="3226">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14104,6 +14104,21 @@
   </si>
   <si>
     <t>7/31/26 and 10/2/26</t>
+  </si>
+  <si>
+    <t>Worldwide Flight Services</t>
+  </si>
+  <si>
+    <t>5/5/26 and 5/8/26</t>
+  </si>
+  <si>
+    <t>80 - 100</t>
+  </si>
+  <si>
+    <t>Accupac</t>
+  </si>
+  <si>
+    <t>8/3/26 - 12/31/26</t>
   </si>
 </sst>
 </file>
@@ -17621,7 +17636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18462,6 +18477,40 @@
       </c>
       <c r="E49" s="48">
         <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="63" t="s">
+        <v>3221</v>
+      </c>
+      <c r="B50" s="63" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C50" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" s="65" t="s">
+        <v>3222</v>
+      </c>
+      <c r="E50" s="63" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="48" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B51" s="48" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C51" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="50" t="s">
+        <v>3225</v>
+      </c>
+      <c r="E51" s="48">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB40C49B-D615-46BB-B560-F194C13DF853}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86C30AB3-C469-4B48-82BC-690D1D0A5C8E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7501" uniqueCount="3226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7509" uniqueCount="3230">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14119,6 +14119,18 @@
   </si>
   <si>
     <t>8/3/26 - 12/31/26</t>
+  </si>
+  <si>
+    <t>Danone North America</t>
+  </si>
+  <si>
+    <t>8/4/26 and 11/2/26</t>
+  </si>
+  <si>
+    <t>DoubleTree by Hilton</t>
+  </si>
+  <si>
+    <t>8/1/26 - 8/5/26</t>
   </si>
 </sst>
 </file>
@@ -17636,7 +17648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18511,6 +18523,40 @@
       </c>
       <c r="E51" s="48">
         <v>260</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="60" t="s">
+        <v>3226</v>
+      </c>
+      <c r="B52" s="60" t="s">
+        <v>3018</v>
+      </c>
+      <c r="C52" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="50" t="s">
+        <v>3227</v>
+      </c>
+      <c r="E52" s="49">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="48" t="s">
+        <v>3228</v>
+      </c>
+      <c r="B53" s="48" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C53" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="50" t="s">
+        <v>3229</v>
+      </c>
+      <c r="E53" s="48">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86C30AB3-C469-4B48-82BC-690D1D0A5C8E}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9812E507-0BA8-458B-9711-03DF623B96CE}"/>
   <bookViews>
-    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7509" uniqueCount="3230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7512" uniqueCount="3230">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -17648,13 +17648,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E54"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17692,7 +17692,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17743,7 +17743,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17760,7 +17760,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17777,7 +17777,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17794,7 +17794,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17879,7 +17879,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17964,7 +17964,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18032,7 +18032,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18049,7 +18049,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18066,7 +18066,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18151,7 +18151,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18457,7 +18457,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18557,6 +18557,23 @@
       </c>
       <c r="E53" s="48">
         <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="48" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B54" s="48" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C54" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="50">
+        <v>46241</v>
+      </c>
+      <c r="E54" s="48">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -18571,12 +18588,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19531,7 +19548,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19650,7 +19667,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20061,12 +20078,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20103,7 +20120,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20137,7 +20154,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20256,7 +20273,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20324,7 +20341,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20358,7 +20375,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -20800,7 +20817,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21058,12 +21075,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21168,7 +21185,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21236,7 +21253,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21287,7 +21304,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21355,7 +21372,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -21729,7 +21746,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -21797,7 +21814,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -21967,7 +21984,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22222,7 +22239,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22613,7 +22630,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22681,7 +22698,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -22783,7 +22800,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -22800,7 +22817,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -22851,7 +22868,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -22919,7 +22936,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -22953,7 +22970,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23021,7 +23038,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23055,7 +23072,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23072,7 +23089,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23140,7 +23157,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23276,7 +23293,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23446,7 +23463,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23633,7 +23650,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -23976,13 +23993,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25039,7 +25056,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25073,7 +25090,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25192,7 +25209,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25226,7 +25243,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25481,7 +25498,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25549,7 +25566,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -25858,13 +25875,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25986,7 +26003,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26411,7 +26428,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -26819,7 +26836,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27162,13 +27179,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27662,7 +27679,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28036,7 +28053,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28257,7 +28274,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28291,7 +28308,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -28770,13 +28787,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28796,7 +28813,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -28864,7 +28881,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -28915,7 +28932,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29034,7 +29051,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29170,7 +29187,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29272,7 +29289,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29289,7 +29306,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29306,7 +29323,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29408,7 +29425,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29476,7 +29493,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29646,7 +29663,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29697,7 +29714,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -29969,7 +29986,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30156,7 +30173,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30482,13 +30499,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30593,7 +30610,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32296,13 +32313,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33427,7 +33444,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33444,7 +33461,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34498,7 +34515,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34557,13 +34574,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -36967,16 +36984,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -36993,7 +37010,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37010,7 +37027,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37027,7 +37044,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37044,7 +37061,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37061,7 +37078,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37078,7 +37095,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37095,7 +37112,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37112,7 +37129,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37129,7 +37146,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37146,7 +37163,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37163,7 +37180,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37180,7 +37197,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37197,7 +37214,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37214,7 +37231,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37231,7 +37248,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37248,7 +37265,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37265,7 +37282,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37282,7 +37299,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37299,7 +37316,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37316,7 +37333,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37333,7 +37350,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37350,7 +37367,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37367,7 +37384,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37384,7 +37401,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37401,7 +37418,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37418,7 +37435,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37435,7 +37452,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37452,7 +37469,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37469,7 +37486,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37486,7 +37503,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37503,7 +37520,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37520,7 +37537,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37537,7 +37554,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37554,7 +37571,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37571,7 +37588,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37588,7 +37605,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37605,7 +37622,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37622,7 +37639,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37639,7 +37656,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37656,7 +37673,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37673,7 +37690,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37690,7 +37707,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37707,7 +37724,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -37724,7 +37741,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -37741,7 +37758,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -37758,7 +37775,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -37775,7 +37792,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -37792,7 +37809,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -37809,7 +37826,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37826,7 +37843,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -37843,7 +37860,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37860,7 +37877,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -37877,7 +37894,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -37894,7 +37911,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -37911,7 +37928,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -37928,7 +37945,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -37945,7 +37962,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -37962,7 +37979,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -37979,7 +37996,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -37996,7 +38013,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38013,7 +38030,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38030,7 +38047,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38047,7 +38064,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38064,7 +38081,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38081,7 +38098,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38098,7 +38115,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38115,7 +38132,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38132,7 +38149,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38149,7 +38166,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38166,7 +38183,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38183,7 +38200,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38200,7 +38217,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38217,7 +38234,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38234,7 +38251,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38251,7 +38268,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38268,7 +38285,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38285,7 +38302,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38302,7 +38319,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38319,7 +38336,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38336,7 +38353,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38353,7 +38370,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38370,7 +38387,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38387,7 +38404,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38404,7 +38421,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38421,7 +38438,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38438,7 +38455,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38455,7 +38472,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38472,7 +38489,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38489,7 +38506,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38506,7 +38523,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38523,7 +38540,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38540,7 +38557,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38557,7 +38574,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38574,7 +38591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38591,7 +38608,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38608,7 +38625,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38625,7 +38642,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38642,7 +38659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38659,7 +38676,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38676,7 +38693,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38693,7 +38710,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38710,7 +38727,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -38727,7 +38744,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -38744,7 +38761,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -38761,7 +38778,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -38778,7 +38795,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -38795,7 +38812,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -38812,7 +38829,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -38829,7 +38846,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -38865,14 +38882,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40477,14 +40494,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41114,7 +41131,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42197,14 +42214,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -43936,13 +43953,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45680,14 +45697,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45826,7 +45843,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -45843,7 +45860,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -45894,7 +45911,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -45962,7 +45979,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46013,7 +46030,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46047,7 +46064,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46268,7 +46285,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46336,7 +46353,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46404,7 +46421,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46608,7 +46625,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -46846,7 +46863,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46914,7 +46931,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47160,7 +47177,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47262,7 +47279,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47279,7 +47296,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47313,7 +47330,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47330,7 +47347,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47381,7 +47398,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47500,7 +47517,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47571,14 +47588,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -48822,7 +48839,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49111,7 +49128,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49349,7 +49366,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49366,7 +49383,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49400,7 +49417,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49521,14 +49538,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50278,14 +50295,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50679,7 +50696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -50866,7 +50883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51162,13 +51179,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51256,7 +51273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51494,7 +51511,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -51817,7 +51834,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -51834,7 +51851,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -51851,7 +51868,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -51868,7 +51885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -51902,7 +51919,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52140,7 +52157,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52157,7 +52174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52327,7 +52344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52412,7 +52429,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52565,7 +52582,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -52752,7 +52769,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -52854,7 +52871,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -52871,7 +52888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53024,7 +53041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53041,7 +53058,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53126,7 +53143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53177,7 +53194,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53449,7 +53466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53602,7 +53619,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53670,7 +53687,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53704,7 +53721,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -53721,7 +53738,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -53976,7 +53993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54146,7 +54163,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54197,7 +54214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54282,7 +54299,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54367,7 +54384,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -54945,7 +54962,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55305,12 +55322,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55449,7 +55466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -55976,7 +55993,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56316,7 +56333,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56333,7 +56350,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56350,7 +56367,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56435,7 +56452,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56588,7 +56605,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56605,7 +56622,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56656,7 +56673,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -56778,12 +56795,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57262,7 +57279,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57687,7 +57704,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="215" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9812E507-0BA8-458B-9711-03DF623B96CE}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30E957B0-CE17-47AE-803C-CD436B73BAA1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7512" uniqueCount="3230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7510" uniqueCount="3227">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14104,15 +14104,6 @@
   </si>
   <si>
     <t>7/31/26 and 10/2/26</t>
-  </si>
-  <si>
-    <t>Worldwide Flight Services</t>
-  </si>
-  <si>
-    <t>5/5/26 and 5/8/26</t>
-  </si>
-  <si>
-    <t>80 - 100</t>
   </si>
   <si>
     <t>Accupac</t>
@@ -17030,10 +17021,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -18492,88 +18479,88 @@
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="63" t="s">
+      <c r="A50" s="48" t="s">
         <v>3221</v>
       </c>
-      <c r="B50" s="63" t="s">
-        <v>2598</v>
-      </c>
-      <c r="C50" s="64" t="s">
+      <c r="B50" s="48" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C50" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="D50" s="65" t="s">
+      <c r="D50" s="50" t="s">
         <v>3222</v>
       </c>
-      <c r="E50" s="63" t="s">
+      <c r="E50" s="48">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="60" t="s">
         <v>3223</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="48" t="s">
+      <c r="B51" s="60" t="s">
+        <v>3018</v>
+      </c>
+      <c r="C51" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" s="50" t="s">
         <v>3224</v>
       </c>
-      <c r="B51" s="48" t="s">
-        <v>1502</v>
-      </c>
-      <c r="C51" s="49" t="s">
+      <c r="E51" s="49">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="48" t="s">
+        <v>3225</v>
+      </c>
+      <c r="B52" s="48" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C52" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="D51" s="50" t="s">
-        <v>3225</v>
-      </c>
-      <c r="E51" s="48">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="60" t="s">
+      <c r="D52" s="50" t="s">
         <v>3226</v>
       </c>
-      <c r="B52" s="60" t="s">
-        <v>3018</v>
-      </c>
-      <c r="C52" s="58" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" s="50" t="s">
-        <v>3227</v>
-      </c>
-      <c r="E52" s="49">
-        <v>114</v>
+      <c r="E52" s="48">
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="48" t="s">
-        <v>3228</v>
+        <v>2935</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>2043</v>
+        <v>2705</v>
       </c>
       <c r="C53" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="D53" s="50" t="s">
-        <v>3229</v>
+      <c r="D53" s="50">
+        <v>46241</v>
       </c>
       <c r="E53" s="48">
-        <v>90</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="48" t="s">
-        <v>2935</v>
-      </c>
-      <c r="B54" s="48" t="s">
-        <v>2705</v>
-      </c>
-      <c r="C54" s="49" t="s">
+      <c r="A54" s="60" t="s">
+        <v>2960</v>
+      </c>
+      <c r="B54" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="58" t="s">
         <v>67</v>
       </c>
       <c r="D54" s="50">
-        <v>46241</v>
-      </c>
-      <c r="E54" s="48">
-        <v>121</v>
+        <v>46144</v>
+      </c>
+      <c r="E54" s="49">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30E957B0-CE17-47AE-803C-CD436B73BAA1}"/>
+  <xr:revisionPtr revIDLastSave="224" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C6C36A1-10D0-49F5-A4D0-D05E44F214D1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7510" uniqueCount="3227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7520" uniqueCount="3230">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14122,6 +14122,15 @@
   </si>
   <si>
     <t>8/1/26 - 8/5/26</t>
+  </si>
+  <si>
+    <t>Embassy Suites by Hilton</t>
+  </si>
+  <si>
+    <t>Amicus Therapeutics</t>
+  </si>
+  <si>
+    <t>8/7/26 - 10/30/26</t>
   </si>
 </sst>
 </file>
@@ -17021,6 +17030,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17635,13 +17648,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E57"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17679,7 +17692,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17730,7 +17743,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17747,7 +17760,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17764,7 +17777,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17781,7 +17794,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17798,7 +17811,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17849,7 +17862,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17866,7 +17879,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17951,7 +17964,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18019,7 +18032,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18036,7 +18049,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18053,7 +18066,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18138,7 +18151,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18149,7 +18162,7 @@
         <v>65</v>
       </c>
       <c r="D30" s="50">
-        <v>46178</v>
+        <v>46192</v>
       </c>
       <c r="E30" s="49">
         <v>61</v>
@@ -18444,7 +18457,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18561,6 +18574,57 @@
       </c>
       <c r="E54" s="49">
         <v>201</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="63" t="s">
+        <v>3227</v>
+      </c>
+      <c r="B55" s="63" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C55" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" s="65">
+        <v>46248</v>
+      </c>
+      <c r="E55" s="63">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="63" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B56" s="63" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C56" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" s="65">
+        <v>46237</v>
+      </c>
+      <c r="E56" s="63">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="48" t="s">
+        <v>3228</v>
+      </c>
+      <c r="B57" s="48" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C57" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" s="50" t="s">
+        <v>3229</v>
+      </c>
+      <c r="E57" s="48">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -18575,12 +18639,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19535,7 +19599,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19654,7 +19718,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20065,12 +20129,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20107,7 +20171,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20141,7 +20205,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20260,7 +20324,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20328,7 +20392,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20362,7 +20426,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -20804,7 +20868,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21062,12 +21126,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21172,7 +21236,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21240,7 +21304,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21291,7 +21355,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21359,7 +21423,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -21733,7 +21797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -21801,7 +21865,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -21971,7 +22035,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22226,7 +22290,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22617,7 +22681,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22685,7 +22749,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -22787,7 +22851,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -22804,7 +22868,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -22855,7 +22919,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -22923,7 +22987,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -22957,7 +23021,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23025,7 +23089,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23059,7 +23123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23076,7 +23140,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23144,7 +23208,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23280,7 +23344,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23450,7 +23514,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23637,7 +23701,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -23980,13 +24044,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25043,7 +25107,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25077,7 +25141,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25196,7 +25260,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25230,7 +25294,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25485,7 +25549,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25553,7 +25617,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -25862,13 +25926,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25990,7 +26054,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26415,7 +26479,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -26823,7 +26887,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27166,13 +27230,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27666,7 +27730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28040,7 +28104,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28261,7 +28325,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28295,7 +28359,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -28774,13 +28838,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28800,7 +28864,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -28868,7 +28932,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -28919,7 +28983,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29038,7 +29102,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29174,7 +29238,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29276,7 +29340,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29293,7 +29357,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29310,7 +29374,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29412,7 +29476,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29480,7 +29544,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29650,7 +29714,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29701,7 +29765,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -29973,7 +30037,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30160,7 +30224,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30486,13 +30550,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30597,7 +30661,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32300,13 +32364,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33431,7 +33495,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33448,7 +33512,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34502,7 +34566,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34561,13 +34625,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -36971,16 +37035,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -36997,7 +37061,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37014,7 +37078,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37031,7 +37095,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37048,7 +37112,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37065,7 +37129,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37082,7 +37146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37099,7 +37163,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37116,7 +37180,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37133,7 +37197,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37150,7 +37214,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37167,7 +37231,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37184,7 +37248,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37201,7 +37265,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37218,7 +37282,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37235,7 +37299,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37252,7 +37316,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37269,7 +37333,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37286,7 +37350,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37303,7 +37367,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37320,7 +37384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37337,7 +37401,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37354,7 +37418,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37371,7 +37435,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37388,7 +37452,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37405,7 +37469,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37422,7 +37486,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37439,7 +37503,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37456,7 +37520,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37473,7 +37537,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37490,7 +37554,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37507,7 +37571,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37524,7 +37588,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37541,7 +37605,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37558,7 +37622,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37575,7 +37639,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37592,7 +37656,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37609,7 +37673,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37626,7 +37690,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37643,7 +37707,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37660,7 +37724,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37677,7 +37741,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37694,7 +37758,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37711,7 +37775,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -37728,7 +37792,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -37745,7 +37809,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -37762,7 +37826,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -37779,7 +37843,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -37796,7 +37860,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -37813,7 +37877,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37830,7 +37894,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -37847,7 +37911,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37864,7 +37928,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -37881,7 +37945,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -37898,7 +37962,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -37915,7 +37979,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -37932,7 +37996,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -37949,7 +38013,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -37966,7 +38030,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -37983,7 +38047,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38000,7 +38064,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38017,7 +38081,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38034,7 +38098,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38051,7 +38115,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38068,7 +38132,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38085,7 +38149,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38102,7 +38166,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38119,7 +38183,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38136,7 +38200,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38153,7 +38217,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38170,7 +38234,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38187,7 +38251,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38204,7 +38268,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38221,7 +38285,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38238,7 +38302,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38255,7 +38319,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38272,7 +38336,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38289,7 +38353,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38306,7 +38370,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38323,7 +38387,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38340,7 +38404,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38357,7 +38421,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38374,7 +38438,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38391,7 +38455,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38408,7 +38472,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38425,7 +38489,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38442,7 +38506,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38459,7 +38523,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38476,7 +38540,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38493,7 +38557,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38510,7 +38574,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38527,7 +38591,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38544,7 +38608,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38561,7 +38625,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38578,7 +38642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38595,7 +38659,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38612,7 +38676,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38629,7 +38693,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38646,7 +38710,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38663,7 +38727,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38680,7 +38744,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38697,7 +38761,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38714,7 +38778,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -38731,7 +38795,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -38748,7 +38812,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -38765,7 +38829,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -38782,7 +38846,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -38799,7 +38863,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -38816,7 +38880,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -38833,7 +38897,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -38869,14 +38933,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40481,14 +40545,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41118,7 +41182,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42201,14 +42265,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -43940,13 +44004,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45684,14 +45748,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45830,7 +45894,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -45847,7 +45911,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -45898,7 +45962,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -45966,7 +46030,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46017,7 +46081,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46051,7 +46115,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46272,7 +46336,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46340,7 +46404,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46408,7 +46472,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46612,7 +46676,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -46850,7 +46914,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46918,7 +46982,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47164,7 +47228,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47266,7 +47330,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47283,7 +47347,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47317,7 +47381,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47334,7 +47398,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47385,7 +47449,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47504,7 +47568,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47575,14 +47639,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -48826,7 +48890,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49115,7 +49179,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49353,7 +49417,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49370,7 +49434,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49404,7 +49468,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49525,14 +49589,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50282,14 +50346,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50683,7 +50747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -50870,7 +50934,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51166,13 +51230,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51260,7 +51324,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51498,7 +51562,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -51821,7 +51885,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -51838,7 +51902,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -51855,7 +51919,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -51872,7 +51936,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -51906,7 +51970,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52144,7 +52208,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52161,7 +52225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52331,7 +52395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52416,7 +52480,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52569,7 +52633,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -52756,7 +52820,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -52858,7 +52922,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -52875,7 +52939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53028,7 +53092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53045,7 +53109,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53130,7 +53194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53181,7 +53245,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53453,7 +53517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53606,7 +53670,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53674,7 +53738,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53708,7 +53772,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -53725,7 +53789,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -53980,7 +54044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54150,7 +54214,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54201,7 +54265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54286,7 +54350,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54371,7 +54435,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -54949,7 +55013,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55309,12 +55373,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55453,7 +55517,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -55980,7 +56044,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56320,7 +56384,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56337,7 +56401,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56354,7 +56418,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56439,7 +56503,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56592,7 +56656,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56609,7 +56673,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56660,7 +56724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -56782,12 +56846,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57266,7 +57330,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57691,7 +57755,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="224" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C6C36A1-10D0-49F5-A4D0-D05E44F214D1}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF4ABE43-D670-4FED-859B-00BB64D509F8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7520" uniqueCount="3230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7524" uniqueCount="3231">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14131,6 +14131,9 @@
   </si>
   <si>
     <t>8/7/26 - 10/30/26</t>
+  </si>
+  <si>
+    <t>8/10/26  9/10/26</t>
   </si>
 </sst>
 </file>
@@ -17648,13 +17651,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17692,7 +17695,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17743,7 +17746,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17760,7 +17763,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17777,7 +17780,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17794,7 +17797,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17811,7 +17814,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17862,7 +17865,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17879,7 +17882,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17964,7 +17967,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18032,7 +18035,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18049,7 +18052,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18066,7 +18069,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18151,7 +18154,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18457,7 +18460,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18625,6 +18628,23 @@
       </c>
       <c r="E57" s="48">
         <v>58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="48" t="s">
+        <v>2877</v>
+      </c>
+      <c r="B58" s="48" t="s">
+        <v>2809</v>
+      </c>
+      <c r="C58" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="50" t="s">
+        <v>3230</v>
+      </c>
+      <c r="E58" s="48">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -18639,12 +18659,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19599,7 +19619,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19718,7 +19738,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20129,12 +20149,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20171,7 +20191,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20205,7 +20225,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20324,7 +20344,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20392,7 +20412,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20426,7 +20446,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -20868,7 +20888,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21126,12 +21146,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21236,7 +21256,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21304,7 +21324,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21355,7 +21375,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21423,7 +21443,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -21797,7 +21817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -21865,7 +21885,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22035,7 +22055,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22290,7 +22310,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22681,7 +22701,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22749,7 +22769,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -22851,7 +22871,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -22868,7 +22888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -22919,7 +22939,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -22987,7 +23007,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23021,7 +23041,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23089,7 +23109,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23123,7 +23143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23140,7 +23160,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23208,7 +23228,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23344,7 +23364,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23514,7 +23534,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23701,7 +23721,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24044,13 +24064,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25107,7 +25127,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25141,7 +25161,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25260,7 +25280,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25294,7 +25314,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25549,7 +25569,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25617,7 +25637,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -25926,13 +25946,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26054,7 +26074,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26479,7 +26499,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -26887,7 +26907,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27230,13 +27250,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27730,7 +27750,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28104,7 +28124,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28325,7 +28345,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28359,7 +28379,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -28838,13 +28858,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28864,7 +28884,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -28932,7 +28952,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -28983,7 +29003,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29102,7 +29122,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29238,7 +29258,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29340,7 +29360,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29357,7 +29377,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29374,7 +29394,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29476,7 +29496,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29544,7 +29564,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29714,7 +29734,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29765,7 +29785,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30037,7 +30057,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30224,7 +30244,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30550,13 +30570,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30661,7 +30681,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32364,13 +32384,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33495,7 +33515,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33512,7 +33532,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34566,7 +34586,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34625,13 +34645,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37035,16 +37055,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37061,7 +37081,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37078,7 +37098,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37095,7 +37115,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37112,7 +37132,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37129,7 +37149,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37146,7 +37166,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37163,7 +37183,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37180,7 +37200,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37197,7 +37217,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37214,7 +37234,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37231,7 +37251,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37248,7 +37268,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37265,7 +37285,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37282,7 +37302,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37299,7 +37319,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37316,7 +37336,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37333,7 +37353,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37350,7 +37370,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37367,7 +37387,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37384,7 +37404,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37401,7 +37421,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37418,7 +37438,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37435,7 +37455,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37452,7 +37472,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37469,7 +37489,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37486,7 +37506,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37503,7 +37523,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37520,7 +37540,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37537,7 +37557,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37554,7 +37574,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37571,7 +37591,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37588,7 +37608,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37605,7 +37625,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37622,7 +37642,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37639,7 +37659,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37656,7 +37676,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37673,7 +37693,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37690,7 +37710,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37707,7 +37727,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37724,7 +37744,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37741,7 +37761,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37758,7 +37778,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37775,7 +37795,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -37792,7 +37812,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -37809,7 +37829,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -37826,7 +37846,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -37843,7 +37863,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -37860,7 +37880,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -37877,7 +37897,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37894,7 +37914,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -37911,7 +37931,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37928,7 +37948,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -37945,7 +37965,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -37962,7 +37982,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -37979,7 +37999,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -37996,7 +38016,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38013,7 +38033,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38030,7 +38050,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38047,7 +38067,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38064,7 +38084,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38081,7 +38101,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38098,7 +38118,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38115,7 +38135,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38132,7 +38152,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38149,7 +38169,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38166,7 +38186,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38183,7 +38203,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38200,7 +38220,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38217,7 +38237,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38234,7 +38254,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38251,7 +38271,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38268,7 +38288,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38285,7 +38305,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38302,7 +38322,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38319,7 +38339,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38336,7 +38356,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38353,7 +38373,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38370,7 +38390,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38387,7 +38407,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38404,7 +38424,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38421,7 +38441,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38438,7 +38458,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38455,7 +38475,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38472,7 +38492,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38489,7 +38509,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38506,7 +38526,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38523,7 +38543,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38540,7 +38560,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38557,7 +38577,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38574,7 +38594,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38591,7 +38611,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38608,7 +38628,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38625,7 +38645,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38642,7 +38662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38659,7 +38679,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38676,7 +38696,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38693,7 +38713,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38710,7 +38730,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38727,7 +38747,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38744,7 +38764,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38761,7 +38781,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38778,7 +38798,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -38795,7 +38815,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -38812,7 +38832,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -38829,7 +38849,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -38846,7 +38866,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -38863,7 +38883,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -38880,7 +38900,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -38897,7 +38917,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -38933,14 +38953,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40545,14 +40565,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41182,7 +41202,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42265,14 +42285,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44004,13 +44024,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45748,14 +45768,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45894,7 +45914,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -45911,7 +45931,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -45962,7 +45982,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46030,7 +46050,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46081,7 +46101,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46115,7 +46135,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46336,7 +46356,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46404,7 +46424,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46472,7 +46492,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46676,7 +46696,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -46914,7 +46934,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46982,7 +47002,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47228,7 +47248,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47330,7 +47350,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47347,7 +47367,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47381,7 +47401,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47398,7 +47418,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47449,7 +47469,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47568,7 +47588,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47639,14 +47659,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -48890,7 +48910,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49179,7 +49199,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49417,7 +49437,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49434,7 +49454,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49468,7 +49488,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49589,14 +49609,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50346,14 +50366,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50747,7 +50767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -50934,7 +50954,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51230,13 +51250,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51324,7 +51344,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51562,7 +51582,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -51885,7 +51905,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -51902,7 +51922,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -51919,7 +51939,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -51936,7 +51956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -51970,7 +51990,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52208,7 +52228,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52225,7 +52245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52395,7 +52415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52480,7 +52500,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52633,7 +52653,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -52820,7 +52840,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -52922,7 +52942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -52939,7 +52959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53092,7 +53112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53109,7 +53129,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53194,7 +53214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53245,7 +53265,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53517,7 +53537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53670,7 +53690,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53738,7 +53758,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53772,7 +53792,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -53789,7 +53809,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54044,7 +54064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54214,7 +54234,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54265,7 +54285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54350,7 +54370,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54435,7 +54455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55013,7 +55033,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55373,12 +55393,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55517,7 +55537,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56044,7 +56064,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56384,7 +56404,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56401,7 +56421,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56418,7 +56438,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56503,7 +56523,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56656,7 +56676,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56673,7 +56693,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56724,7 +56744,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -56846,12 +56866,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57330,7 +57350,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57755,7 +57775,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/5.15.26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="8_{31325CD0-7607-466A-AD3D-EB6113250D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF4ABE43-D670-4FED-859B-00BB64D509F8}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{23270D78-830A-41CC-956E-E1974A6D31EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EBAA969-C771-4641-ABBF-9DF12BA58BB8}"/>
   <bookViews>
-    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7524" uniqueCount="3231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7527" uniqueCount="3233">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14134,6 +14134,12 @@
   </si>
   <si>
     <t>8/10/26  9/10/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acme Markets Inc. </t>
+  </si>
+  <si>
+    <t>Edgewater</t>
   </si>
 </sst>
 </file>
@@ -17033,10 +17039,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17651,7 +17653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18239,7 +18241,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18647,9 +18649,30 @@
         <v>64</v>
       </c>
     </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="48" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B59" s="48" t="s">
+        <v>3232</v>
+      </c>
+      <c r="C59" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59" s="50">
+        <v>46249</v>
+      </c>
+      <c r="E59" s="48">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="landscape" verticalDpi="1200" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -37778,7 +37801,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38900,7 +38923,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/5.15.26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{23270D78-830A-41CC-956E-E1974A6D31EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EBAA969-C771-4641-ABBF-9DF12BA58BB8}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6EDD45D-B5ED-47EA-875E-3B7224A9BA30}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7527" uniqueCount="3233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7530" uniqueCount="3233">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -17653,7 +17653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18664,6 +18664,23 @@
       </c>
       <c r="E59" s="48">
         <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="60" t="s">
+        <v>2881</v>
+      </c>
+      <c r="B60" s="60" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C60" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="50">
+        <v>46255</v>
+      </c>
+      <c r="E60" s="49">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6EDD45D-B5ED-47EA-875E-3B7224A9BA30}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20A3532C-E45D-42CA-BAB2-EA1869379619}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7530" uniqueCount="3233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7539" uniqueCount="3236">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14140,6 +14140,15 @@
   </si>
   <si>
     <t>Edgewater</t>
+  </si>
+  <si>
+    <t>Prudential Insurance Company of America</t>
+  </si>
+  <si>
+    <t>Meta</t>
+  </si>
+  <si>
+    <t>Johnson &amp; Johnson</t>
   </si>
 </sst>
 </file>
@@ -17039,6 +17048,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17653,13 +17666,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E60"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E63"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17697,7 +17710,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17748,7 +17761,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17765,7 +17778,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17782,7 +17795,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17799,7 +17812,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17816,7 +17829,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17867,7 +17880,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17884,7 +17897,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17969,7 +17982,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18037,7 +18050,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18054,7 +18067,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18071,7 +18084,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18156,7 +18169,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18241,7 +18254,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18462,7 +18475,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18681,6 +18694,57 @@
       </c>
       <c r="E60" s="49">
         <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="31.2">
+      <c r="A61" s="63" t="s">
+        <v>3233</v>
+      </c>
+      <c r="B61" s="63" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C61" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61" s="65">
+        <v>46220</v>
+      </c>
+      <c r="E61" s="63">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="63" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B62" s="63" t="s">
+        <v>3168</v>
+      </c>
+      <c r="C62" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" s="65">
+        <v>46254</v>
+      </c>
+      <c r="E62" s="63">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="48" t="s">
+        <v>3235</v>
+      </c>
+      <c r="B63" s="48" t="s">
+        <v>2937</v>
+      </c>
+      <c r="C63" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="50">
+        <v>46255</v>
+      </c>
+      <c r="E63" s="48">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -18699,12 +18763,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19659,7 +19723,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19778,7 +19842,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20189,12 +20253,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20231,7 +20295,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20265,7 +20329,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20384,7 +20448,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20452,7 +20516,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20486,7 +20550,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -20928,7 +20992,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21186,12 +21250,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21296,7 +21360,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21364,7 +21428,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21415,7 +21479,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21483,7 +21547,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -21857,7 +21921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -21925,7 +21989,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22095,7 +22159,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22350,7 +22414,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22741,7 +22805,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22809,7 +22873,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -22911,7 +22975,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -22928,7 +22992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -22979,7 +23043,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23047,7 +23111,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23081,7 +23145,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23149,7 +23213,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23183,7 +23247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23200,7 +23264,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23268,7 +23332,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23404,7 +23468,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23574,7 +23638,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23761,7 +23825,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24104,13 +24168,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25167,7 +25231,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25201,7 +25265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25320,7 +25384,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25354,7 +25418,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25609,7 +25673,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25677,7 +25741,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -25986,13 +26050,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26114,7 +26178,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26539,7 +26603,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -26947,7 +27011,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27290,13 +27354,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27790,7 +27854,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28164,7 +28228,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28385,7 +28449,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28419,7 +28483,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -28898,13 +28962,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28924,7 +28988,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -28992,7 +29056,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29043,7 +29107,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29162,7 +29226,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29298,7 +29362,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29400,7 +29464,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29417,7 +29481,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29434,7 +29498,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29536,7 +29600,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29604,7 +29668,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29774,7 +29838,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29825,7 +29889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30097,7 +30161,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30284,7 +30348,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30610,13 +30674,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30721,7 +30785,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32424,13 +32488,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33555,7 +33619,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33572,7 +33636,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34626,7 +34690,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34685,13 +34749,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37095,16 +37159,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37121,7 +37185,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37138,7 +37202,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37155,7 +37219,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37172,7 +37236,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37189,7 +37253,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37206,7 +37270,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37223,7 +37287,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37240,7 +37304,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37257,7 +37321,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37274,7 +37338,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37291,7 +37355,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37308,7 +37372,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37325,7 +37389,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37342,7 +37406,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37359,7 +37423,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37376,7 +37440,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37393,7 +37457,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37410,7 +37474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37427,7 +37491,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37444,7 +37508,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37461,7 +37525,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37478,7 +37542,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37495,7 +37559,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37512,7 +37576,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37529,7 +37593,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37546,7 +37610,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37563,7 +37627,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37580,7 +37644,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37597,7 +37661,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37614,7 +37678,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37631,7 +37695,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37648,7 +37712,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37665,7 +37729,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37682,7 +37746,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37699,7 +37763,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37716,7 +37780,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37733,7 +37797,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37750,7 +37814,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37767,7 +37831,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37784,7 +37848,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37801,7 +37865,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37818,7 +37882,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37835,7 +37899,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -37852,7 +37916,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -37869,7 +37933,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -37886,7 +37950,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -37903,7 +37967,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -37920,7 +37984,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -37937,7 +38001,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37954,7 +38018,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -37971,7 +38035,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -37988,7 +38052,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38005,7 +38069,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38022,7 +38086,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38039,7 +38103,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38056,7 +38120,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38073,7 +38137,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38090,7 +38154,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38107,7 +38171,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38124,7 +38188,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38141,7 +38205,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38158,7 +38222,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38175,7 +38239,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38192,7 +38256,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38209,7 +38273,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38226,7 +38290,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38243,7 +38307,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38260,7 +38324,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38277,7 +38341,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38294,7 +38358,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38311,7 +38375,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38328,7 +38392,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38345,7 +38409,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38362,7 +38426,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38379,7 +38443,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38396,7 +38460,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38413,7 +38477,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38430,7 +38494,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38447,7 +38511,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38464,7 +38528,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38481,7 +38545,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38498,7 +38562,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38515,7 +38579,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38532,7 +38596,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38549,7 +38613,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38566,7 +38630,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38583,7 +38647,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38600,7 +38664,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38617,7 +38681,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38634,7 +38698,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38651,7 +38715,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38668,7 +38732,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38685,7 +38749,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38702,7 +38766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38719,7 +38783,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38736,7 +38800,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38753,7 +38817,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38770,7 +38834,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38787,7 +38851,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38804,7 +38868,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38821,7 +38885,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38838,7 +38902,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -38855,7 +38919,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -38872,7 +38936,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -38889,7 +38953,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -38906,7 +38970,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -38923,7 +38987,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -38940,7 +39004,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -38957,7 +39021,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -38993,14 +39057,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40605,14 +40669,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41242,7 +41306,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42325,14 +42389,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44064,13 +44128,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45808,14 +45872,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45954,7 +46018,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -45971,7 +46035,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46022,7 +46086,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46090,7 +46154,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46141,7 +46205,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46175,7 +46239,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46396,7 +46460,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46464,7 +46528,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46532,7 +46596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46736,7 +46800,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -46974,7 +47038,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47042,7 +47106,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47288,7 +47352,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47390,7 +47454,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47407,7 +47471,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47441,7 +47505,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47458,7 +47522,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47509,7 +47573,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47628,7 +47692,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47699,14 +47763,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -48950,7 +49014,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49239,7 +49303,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49477,7 +49541,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49494,7 +49558,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49528,7 +49592,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49649,14 +49713,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50406,14 +50470,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50807,7 +50871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -50994,7 +51058,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51290,13 +51354,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51384,7 +51448,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51622,7 +51686,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -51945,7 +52009,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -51962,7 +52026,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -51979,7 +52043,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -51996,7 +52060,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52030,7 +52094,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52268,7 +52332,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52285,7 +52349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52455,7 +52519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52540,7 +52604,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52693,7 +52757,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -52880,7 +52944,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -52982,7 +53046,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -52999,7 +53063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53152,7 +53216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53169,7 +53233,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53254,7 +53318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53305,7 +53369,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53577,7 +53641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53730,7 +53794,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53798,7 +53862,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53832,7 +53896,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -53849,7 +53913,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54104,7 +54168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54274,7 +54338,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54325,7 +54389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54410,7 +54474,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54495,7 +54559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55073,7 +55137,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55433,12 +55497,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55577,7 +55641,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56104,7 +56168,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56444,7 +56508,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56461,7 +56525,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56478,7 +56542,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56563,7 +56627,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56716,7 +56780,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56733,7 +56797,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56784,7 +56848,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -56906,12 +56970,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57390,7 +57454,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57815,7 +57879,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20A3532C-E45D-42CA-BAB2-EA1869379619}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A34CFA10-05E2-41F0-9033-D73D30B03D7C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7539" uniqueCount="3236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7551" uniqueCount="3241">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14149,6 +14149,21 @@
   </si>
   <si>
     <t>Johnson &amp; Johnson</t>
+  </si>
+  <si>
+    <t>Merck &amp; Co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optum Select Management Inc. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optum Care Inc. </t>
+  </si>
+  <si>
+    <t>Rutherford</t>
+  </si>
+  <si>
+    <t>Optum Services Inc.</t>
   </si>
 </sst>
 </file>
@@ -17666,13 +17681,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E63"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E67"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17710,7 +17725,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17761,7 +17776,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17778,7 +17793,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17795,7 +17810,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17812,7 +17827,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17829,7 +17844,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17880,7 +17895,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17897,7 +17912,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17982,7 +17997,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18050,7 +18065,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18067,7 +18082,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18084,7 +18099,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18169,7 +18184,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18475,7 +18490,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18696,7 +18711,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.2">
+    <row r="61" spans="1:5" ht="31.5">
       <c r="A61" s="63" t="s">
         <v>3233</v>
       </c>
@@ -18745,6 +18760,74 @@
       </c>
       <c r="E63" s="48">
         <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="63" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B64" s="63" t="s">
+        <v>3066</v>
+      </c>
+      <c r="C64" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" s="65">
+        <v>46269</v>
+      </c>
+      <c r="E64" s="63">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="31.5">
+      <c r="A65" s="63" t="s">
+        <v>3237</v>
+      </c>
+      <c r="B65" s="63" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C65" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" s="65">
+        <v>46260</v>
+      </c>
+      <c r="E65" s="63">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="63" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B66" s="63" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C66" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D66" s="65">
+        <v>46260</v>
+      </c>
+      <c r="E66" s="63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="48" t="s">
+        <v>3240</v>
+      </c>
+      <c r="B67" s="48" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" s="50">
+        <v>46260</v>
+      </c>
+      <c r="E67" s="48">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -18763,12 +18846,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19723,7 +19806,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19842,7 +19925,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20253,12 +20336,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20295,7 +20378,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20329,7 +20412,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20448,7 +20531,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20516,7 +20599,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20550,7 +20633,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -20992,7 +21075,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21250,12 +21333,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21360,7 +21443,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21428,7 +21511,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21479,7 +21562,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21547,7 +21630,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -21921,7 +22004,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -21989,7 +22072,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22159,7 +22242,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22414,7 +22497,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22805,7 +22888,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22873,7 +22956,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -22975,7 +23058,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -22992,7 +23075,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23043,7 +23126,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23111,7 +23194,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23145,7 +23228,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23213,7 +23296,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23247,7 +23330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23264,7 +23347,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23332,7 +23415,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23468,7 +23551,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23638,7 +23721,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23825,7 +23908,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24168,13 +24251,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25231,7 +25314,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25265,7 +25348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25384,7 +25467,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25418,7 +25501,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25673,7 +25756,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25741,7 +25824,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26050,13 +26133,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26178,7 +26261,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26603,7 +26686,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27011,7 +27094,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27354,13 +27437,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27854,7 +27937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28228,7 +28311,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28449,7 +28532,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28483,7 +28566,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -28962,13 +29045,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28988,7 +29071,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29056,7 +29139,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29107,7 +29190,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29226,7 +29309,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29362,7 +29445,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29464,7 +29547,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29481,7 +29564,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29498,7 +29581,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29600,7 +29683,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29668,7 +29751,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29838,7 +29921,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29889,7 +29972,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30161,7 +30244,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30348,7 +30431,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30674,13 +30757,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30785,7 +30868,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32488,13 +32571,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33619,7 +33702,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33636,7 +33719,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34690,7 +34773,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34749,13 +34832,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37159,16 +37242,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37185,7 +37268,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37202,7 +37285,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37219,7 +37302,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37236,7 +37319,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37253,7 +37336,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37270,7 +37353,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37287,7 +37370,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37304,7 +37387,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37321,7 +37404,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37338,7 +37421,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37355,7 +37438,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37372,7 +37455,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37389,7 +37472,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37406,7 +37489,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37423,7 +37506,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37440,7 +37523,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37457,7 +37540,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37474,7 +37557,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37491,7 +37574,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37508,7 +37591,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37525,7 +37608,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37542,7 +37625,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37559,7 +37642,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37576,7 +37659,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37593,7 +37676,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37610,7 +37693,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37627,7 +37710,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37644,7 +37727,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37661,7 +37744,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37678,7 +37761,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37695,7 +37778,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37712,7 +37795,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37729,7 +37812,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37746,7 +37829,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37763,7 +37846,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37780,7 +37863,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37797,7 +37880,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37814,7 +37897,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37831,7 +37914,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37848,7 +37931,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37865,7 +37948,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37882,7 +37965,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37899,7 +37982,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -37916,7 +37999,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -37933,7 +38016,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -37950,7 +38033,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -37967,7 +38050,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -37984,7 +38067,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38001,7 +38084,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38018,7 +38101,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38035,7 +38118,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38052,7 +38135,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38069,7 +38152,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38086,7 +38169,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38103,7 +38186,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38120,7 +38203,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38137,7 +38220,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38154,7 +38237,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38171,7 +38254,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38188,7 +38271,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38205,7 +38288,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38222,7 +38305,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38239,7 +38322,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38256,7 +38339,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38273,7 +38356,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38290,7 +38373,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38307,7 +38390,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38324,7 +38407,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38341,7 +38424,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38358,7 +38441,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38375,7 +38458,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38392,7 +38475,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38409,7 +38492,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38426,7 +38509,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38443,7 +38526,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38460,7 +38543,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38477,7 +38560,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38494,7 +38577,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38511,7 +38594,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38528,7 +38611,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38545,7 +38628,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38562,7 +38645,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38579,7 +38662,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38596,7 +38679,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38613,7 +38696,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38630,7 +38713,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38647,7 +38730,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38664,7 +38747,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38681,7 +38764,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38698,7 +38781,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38715,7 +38798,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38732,7 +38815,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38749,7 +38832,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38766,7 +38849,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38783,7 +38866,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38800,7 +38883,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38817,7 +38900,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38834,7 +38917,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38851,7 +38934,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38868,7 +38951,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38885,7 +38968,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38902,7 +38985,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -38919,7 +39002,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -38936,7 +39019,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -38953,7 +39036,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -38970,7 +39053,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -38987,7 +39070,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39004,7 +39087,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39021,7 +39104,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39057,14 +39140,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40669,14 +40752,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41306,7 +41389,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42389,14 +42472,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44128,13 +44211,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45872,14 +45955,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46018,7 +46101,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46035,7 +46118,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46086,7 +46169,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46154,7 +46237,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46205,7 +46288,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46239,7 +46322,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46460,7 +46543,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46528,7 +46611,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46596,7 +46679,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46800,7 +46883,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47038,7 +47121,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47106,7 +47189,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47352,7 +47435,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47454,7 +47537,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47471,7 +47554,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47505,7 +47588,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47522,7 +47605,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47573,7 +47656,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47692,7 +47775,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47763,14 +47846,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49014,7 +49097,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49303,7 +49386,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49541,7 +49624,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49558,7 +49641,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49592,7 +49675,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49713,14 +49796,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50470,14 +50553,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50871,7 +50954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51058,7 +51141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51354,13 +51437,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51448,7 +51531,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51686,7 +51769,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52009,7 +52092,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52026,7 +52109,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52043,7 +52126,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52060,7 +52143,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52094,7 +52177,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52332,7 +52415,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52349,7 +52432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52519,7 +52602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52604,7 +52687,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52757,7 +52840,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -52944,7 +53027,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53046,7 +53129,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53063,7 +53146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53216,7 +53299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53233,7 +53316,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53318,7 +53401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53369,7 +53452,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53641,7 +53724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53794,7 +53877,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53862,7 +53945,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53896,7 +53979,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -53913,7 +53996,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54168,7 +54251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54338,7 +54421,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54389,7 +54472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54474,7 +54557,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54559,7 +54642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55137,7 +55220,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55497,12 +55580,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55641,7 +55724,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56168,7 +56251,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56508,7 +56591,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56525,7 +56608,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56542,7 +56625,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56627,7 +56710,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56780,7 +56863,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56797,7 +56880,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56848,7 +56931,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -56970,12 +57053,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57454,7 +57537,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57879,7 +57962,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A34CFA10-05E2-41F0-9033-D73D30B03D7C}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38119A8C-07CA-4124-8C1A-51EE8337BA18}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7551" uniqueCount="3241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7554" uniqueCount="3241">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -17063,10 +17063,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17681,7 +17677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18828,6 +18824,23 @@
       </c>
       <c r="E67" s="48">
         <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="48" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B68" s="48" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C68" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" s="50">
+        <v>46260</v>
+      </c>
+      <c r="E68" s="48">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38119A8C-07CA-4124-8C1A-51EE8337BA18}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB912099-6F8F-4564-916A-10EC7145758A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -17063,6 +17063,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17678,12 +17682,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
   <dimension ref="A1:E68"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17721,7 +17725,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17772,7 +17776,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17789,7 +17793,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17806,7 +17810,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17823,7 +17827,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17840,7 +17844,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17891,7 +17895,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17908,7 +17912,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17993,7 +17997,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18061,7 +18065,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18078,7 +18082,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18095,7 +18099,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18180,7 +18184,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18486,7 +18490,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18707,7 +18711,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.5">
+    <row r="61" spans="1:5" ht="31.2">
       <c r="A61" s="63" t="s">
         <v>3233</v>
       </c>
@@ -18755,7 +18759,7 @@
         <v>46255</v>
       </c>
       <c r="E63" s="48">
-        <v>56</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -18775,7 +18779,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.5">
+    <row r="65" spans="1:5" ht="31.2">
       <c r="A65" s="63" t="s">
         <v>3237</v>
       </c>
@@ -18859,12 +18863,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19819,7 +19823,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19938,7 +19942,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20349,12 +20353,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20391,7 +20395,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20425,7 +20429,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20544,7 +20548,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20612,7 +20616,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20646,7 +20650,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21088,7 +21092,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21346,12 +21350,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21456,7 +21460,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21524,7 +21528,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21575,7 +21579,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21643,7 +21647,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22017,7 +22021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22085,7 +22089,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22255,7 +22259,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22510,7 +22514,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22901,7 +22905,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22969,7 +22973,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23071,7 +23075,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23088,7 +23092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23139,7 +23143,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23207,7 +23211,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23241,7 +23245,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23309,7 +23313,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23343,7 +23347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23360,7 +23364,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23428,7 +23432,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23564,7 +23568,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23734,7 +23738,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23921,7 +23925,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24264,13 +24268,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25327,7 +25331,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25361,7 +25365,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25480,7 +25484,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25514,7 +25518,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25769,7 +25773,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25837,7 +25841,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26146,13 +26150,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26274,7 +26278,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26699,7 +26703,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27107,7 +27111,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27450,13 +27454,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27950,7 +27954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28324,7 +28328,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28545,7 +28549,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28579,7 +28583,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29058,13 +29062,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29084,7 +29088,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29152,7 +29156,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29203,7 +29207,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29322,7 +29326,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29458,7 +29462,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29560,7 +29564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29577,7 +29581,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29594,7 +29598,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29696,7 +29700,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29764,7 +29768,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29934,7 +29938,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -29985,7 +29989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30257,7 +30261,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30444,7 +30448,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30770,13 +30774,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30881,7 +30885,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32584,13 +32588,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33715,7 +33719,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33732,7 +33736,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34786,7 +34790,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34845,13 +34849,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37255,16 +37259,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37281,7 +37285,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37298,7 +37302,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37315,7 +37319,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37332,7 +37336,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37349,7 +37353,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37366,7 +37370,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37383,7 +37387,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37400,7 +37404,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37417,7 +37421,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37434,7 +37438,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37451,7 +37455,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37468,7 +37472,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37485,7 +37489,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37502,7 +37506,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37519,7 +37523,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37536,7 +37540,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37553,7 +37557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37570,7 +37574,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37587,7 +37591,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37604,7 +37608,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37621,7 +37625,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37638,7 +37642,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37655,7 +37659,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37672,7 +37676,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37689,7 +37693,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37706,7 +37710,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37723,7 +37727,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37740,7 +37744,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37757,7 +37761,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37774,7 +37778,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37791,7 +37795,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37808,7 +37812,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37825,7 +37829,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37842,7 +37846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37859,7 +37863,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37876,7 +37880,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37893,7 +37897,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37910,7 +37914,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37927,7 +37931,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37944,7 +37948,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37961,7 +37965,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -37978,7 +37982,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -37995,7 +37999,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38012,7 +38016,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38029,7 +38033,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38046,7 +38050,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38063,7 +38067,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38080,7 +38084,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38097,7 +38101,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38114,7 +38118,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38131,7 +38135,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38148,7 +38152,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38165,7 +38169,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38182,7 +38186,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38199,7 +38203,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38216,7 +38220,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38233,7 +38237,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38250,7 +38254,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38267,7 +38271,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38284,7 +38288,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38301,7 +38305,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38318,7 +38322,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38335,7 +38339,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38352,7 +38356,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38369,7 +38373,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38386,7 +38390,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38403,7 +38407,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38420,7 +38424,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38437,7 +38441,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38454,7 +38458,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38471,7 +38475,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38488,7 +38492,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38505,7 +38509,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38522,7 +38526,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38539,7 +38543,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38556,7 +38560,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38573,7 +38577,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38590,7 +38594,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38607,7 +38611,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38624,7 +38628,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38641,7 +38645,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38658,7 +38662,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38675,7 +38679,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38692,7 +38696,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38709,7 +38713,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38726,7 +38730,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38743,7 +38747,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38760,7 +38764,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38777,7 +38781,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38794,7 +38798,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38811,7 +38815,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38828,7 +38832,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38845,7 +38849,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38862,7 +38866,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38879,7 +38883,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38896,7 +38900,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38913,7 +38917,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38930,7 +38934,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38947,7 +38951,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38964,7 +38968,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -38981,7 +38985,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -38998,7 +39002,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39015,7 +39019,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39032,7 +39036,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39049,7 +39053,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39066,7 +39070,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39083,7 +39087,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39100,7 +39104,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39117,7 +39121,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39153,14 +39157,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40765,14 +40769,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41402,7 +41406,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42485,14 +42489,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44224,13 +44228,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45968,14 +45972,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46114,7 +46118,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46131,7 +46135,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46182,7 +46186,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46250,7 +46254,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46301,7 +46305,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46335,7 +46339,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46556,7 +46560,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46624,7 +46628,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46692,7 +46696,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46896,7 +46900,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47134,7 +47138,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47202,7 +47206,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47448,7 +47452,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47550,7 +47554,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47567,7 +47571,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47601,7 +47605,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47618,7 +47622,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47669,7 +47673,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47788,7 +47792,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47859,14 +47863,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49110,7 +49114,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49399,7 +49403,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49637,7 +49641,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49654,7 +49658,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49688,7 +49692,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49809,14 +49813,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50566,14 +50570,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50967,7 +50971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51154,7 +51158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51450,13 +51454,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51544,7 +51548,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51782,7 +51786,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52105,7 +52109,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52122,7 +52126,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52139,7 +52143,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52156,7 +52160,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52190,7 +52194,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52428,7 +52432,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52445,7 +52449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52615,7 +52619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52700,7 +52704,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52853,7 +52857,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53040,7 +53044,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53142,7 +53146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53159,7 +53163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53312,7 +53316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53329,7 +53333,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53414,7 +53418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53465,7 +53469,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53737,7 +53741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53890,7 +53894,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53958,7 +53962,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -53992,7 +53996,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54009,7 +54013,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54264,7 +54268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54434,7 +54438,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54485,7 +54489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54570,7 +54574,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54655,7 +54659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55233,7 +55237,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55593,12 +55597,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55737,7 +55741,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56264,7 +56268,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56604,7 +56608,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56621,7 +56625,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56638,7 +56642,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56723,7 +56727,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56876,7 +56880,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56893,7 +56897,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56944,7 +56948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57066,12 +57070,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57550,7 +57554,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57975,7 +57979,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB912099-6F8F-4564-916A-10EC7145758A}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9605915-577C-48F2-B4EC-3C9203A49935}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7554" uniqueCount="3241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7557" uniqueCount="3243">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14164,6 +14164,12 @@
   </si>
   <si>
     <t>Optum Services Inc.</t>
+  </si>
+  <si>
+    <t>Citibank, N.A.</t>
+  </si>
+  <si>
+    <t>Hudson and Bergen Counties</t>
   </si>
 </sst>
 </file>
@@ -17063,10 +17069,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17681,7 +17683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18845,6 +18847,23 @@
       </c>
       <c r="E68" s="48">
         <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="31.2">
+      <c r="A69" s="60" t="s">
+        <v>3241</v>
+      </c>
+      <c r="B69" s="60" t="s">
+        <v>3242</v>
+      </c>
+      <c r="C69" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" s="50">
+        <v>46201</v>
+      </c>
+      <c r="E69" s="49">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9605915-577C-48F2-B4EC-3C9203A49935}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8315BFE5-5502-41A2-ADBA-2D2E239CEA2F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7557" uniqueCount="3243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7560" uniqueCount="3244">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14170,6 +14170,9 @@
   </si>
   <si>
     <t>Hudson and Bergen Counties</t>
+  </si>
+  <si>
+    <t>Cumberland County</t>
   </si>
 </sst>
 </file>
@@ -17069,6 +17072,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17683,13 +17690,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E70"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17727,7 +17734,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17778,7 +17785,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17795,7 +17802,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17812,7 +17819,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17829,7 +17836,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17846,7 +17853,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17897,7 +17904,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17914,7 +17921,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -17999,7 +18006,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18067,7 +18074,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18084,7 +18091,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18101,7 +18108,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18186,7 +18193,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18271,7 +18278,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18492,7 +18499,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18713,7 +18720,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.2">
+    <row r="61" spans="1:5" ht="31.5">
       <c r="A61" s="63" t="s">
         <v>3233</v>
       </c>
@@ -18781,7 +18788,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.2">
+    <row r="65" spans="1:5" ht="31.5">
       <c r="A65" s="63" t="s">
         <v>3237</v>
       </c>
@@ -18849,7 +18856,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="60" t="s">
         <v>3241</v>
       </c>
@@ -18864,6 +18871,23 @@
       </c>
       <c r="E69" s="49">
         <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="48" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B70" s="48" t="s">
+        <v>3243</v>
+      </c>
+      <c r="C70" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" s="50">
+        <v>46280</v>
+      </c>
+      <c r="E70" s="48">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -18882,12 +18906,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19842,7 +19866,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -19961,7 +19985,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20372,12 +20396,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20414,7 +20438,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20448,7 +20472,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20567,7 +20591,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20635,7 +20659,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20669,7 +20693,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21111,7 +21135,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21369,12 +21393,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21479,7 +21503,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21547,7 +21571,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21598,7 +21622,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21666,7 +21690,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22040,7 +22064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22108,7 +22132,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22278,7 +22302,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22533,7 +22557,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -22924,7 +22948,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -22992,7 +23016,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23094,7 +23118,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23111,7 +23135,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23162,7 +23186,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23230,7 +23254,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23264,7 +23288,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23332,7 +23356,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23366,7 +23390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23383,7 +23407,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23451,7 +23475,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23587,7 +23611,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23757,7 +23781,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -23944,7 +23968,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24287,13 +24311,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25350,7 +25374,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25384,7 +25408,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25503,7 +25527,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25537,7 +25561,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25792,7 +25816,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25860,7 +25884,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26169,13 +26193,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26297,7 +26321,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26722,7 +26746,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27130,7 +27154,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27473,13 +27497,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -27973,7 +27997,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28347,7 +28371,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28568,7 +28592,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28602,7 +28626,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29081,13 +29105,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29107,7 +29131,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29175,7 +29199,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29226,7 +29250,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29345,7 +29369,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29481,7 +29505,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29583,7 +29607,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29600,7 +29624,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29617,7 +29641,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29719,7 +29743,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29787,7 +29811,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -29957,7 +29981,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30008,7 +30032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30280,7 +30304,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30467,7 +30491,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30793,13 +30817,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30904,7 +30928,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32607,13 +32631,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33738,7 +33762,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33755,7 +33779,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34809,7 +34833,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34868,13 +34892,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37278,16 +37302,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37304,7 +37328,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37321,7 +37345,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37338,7 +37362,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37355,7 +37379,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37372,7 +37396,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37389,7 +37413,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37406,7 +37430,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37423,7 +37447,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37440,7 +37464,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37457,7 +37481,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37474,7 +37498,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37491,7 +37515,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37508,7 +37532,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37525,7 +37549,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37542,7 +37566,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37559,7 +37583,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37576,7 +37600,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37593,7 +37617,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37610,7 +37634,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37627,7 +37651,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37644,7 +37668,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37661,7 +37685,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37678,7 +37702,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37695,7 +37719,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37712,7 +37736,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37729,7 +37753,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37746,7 +37770,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37763,7 +37787,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37780,7 +37804,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37797,7 +37821,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37814,7 +37838,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37831,7 +37855,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37848,7 +37872,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37865,7 +37889,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37882,7 +37906,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37899,7 +37923,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37916,7 +37940,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -37933,7 +37957,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -37950,7 +37974,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -37967,7 +37991,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -37984,7 +38008,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38001,7 +38025,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38018,7 +38042,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38035,7 +38059,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38052,7 +38076,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38069,7 +38093,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38086,7 +38110,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38103,7 +38127,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38120,7 +38144,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38137,7 +38161,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38154,7 +38178,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38171,7 +38195,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38188,7 +38212,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38205,7 +38229,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38222,7 +38246,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38239,7 +38263,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38256,7 +38280,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38273,7 +38297,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38290,7 +38314,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38307,7 +38331,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38324,7 +38348,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38341,7 +38365,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38358,7 +38382,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38375,7 +38399,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38392,7 +38416,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38409,7 +38433,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38426,7 +38450,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38443,7 +38467,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38460,7 +38484,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38477,7 +38501,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38494,7 +38518,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38511,7 +38535,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38528,7 +38552,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38545,7 +38569,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38562,7 +38586,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38579,7 +38603,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38596,7 +38620,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38613,7 +38637,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38630,7 +38654,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38647,7 +38671,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38664,7 +38688,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38681,7 +38705,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38698,7 +38722,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38715,7 +38739,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38732,7 +38756,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38749,7 +38773,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38766,7 +38790,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38783,7 +38807,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38800,7 +38824,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38817,7 +38841,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38834,7 +38858,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38851,7 +38875,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38868,7 +38892,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38885,7 +38909,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38902,7 +38926,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38919,7 +38943,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -38936,7 +38960,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -38953,7 +38977,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -38970,7 +38994,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -38987,7 +39011,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39004,7 +39028,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39021,7 +39045,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39038,7 +39062,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39055,7 +39079,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39072,7 +39096,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39089,7 +39113,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39106,7 +39130,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39123,7 +39147,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39140,7 +39164,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39176,14 +39200,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40788,14 +40812,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41425,7 +41449,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42508,14 +42532,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44247,13 +44271,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -45991,14 +46015,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46137,7 +46161,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46154,7 +46178,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46205,7 +46229,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46273,7 +46297,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46324,7 +46348,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46358,7 +46382,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46579,7 +46603,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46647,7 +46671,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46715,7 +46739,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46919,7 +46943,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47157,7 +47181,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47225,7 +47249,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47471,7 +47495,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47573,7 +47597,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47590,7 +47614,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47624,7 +47648,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47641,7 +47665,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47692,7 +47716,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47811,7 +47835,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47882,14 +47906,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49133,7 +49157,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49422,7 +49446,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49660,7 +49684,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49677,7 +49701,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49711,7 +49735,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49832,14 +49856,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50589,14 +50613,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50990,7 +51014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51177,7 +51201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51473,13 +51497,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51567,7 +51591,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51805,7 +51829,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52128,7 +52152,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52145,7 +52169,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52162,7 +52186,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52179,7 +52203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52213,7 +52237,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52451,7 +52475,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52468,7 +52492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52638,7 +52662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52723,7 +52747,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52876,7 +52900,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53063,7 +53087,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53165,7 +53189,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53182,7 +53206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53335,7 +53359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53352,7 +53376,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53437,7 +53461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53488,7 +53512,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53760,7 +53784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53913,7 +53937,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -53981,7 +54005,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54015,7 +54039,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54032,7 +54056,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54287,7 +54311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54457,7 +54481,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54508,7 +54532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54593,7 +54617,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54678,7 +54702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55256,7 +55280,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55616,12 +55640,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55760,7 +55784,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56287,7 +56311,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56627,7 +56651,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56644,7 +56668,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56661,7 +56685,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56746,7 +56770,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56899,7 +56923,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56916,7 +56940,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -56967,7 +56991,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57089,12 +57113,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57573,7 +57597,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -57998,7 +58022,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8315BFE5-5502-41A2-ADBA-2D2E239CEA2F}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F3F8D8B-47B1-47C5-BFDB-246AD1A84C25}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7560" uniqueCount="3244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7563" uniqueCount="3245">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14173,6 +14173,9 @@
   </si>
   <si>
     <t>Cumberland County</t>
+  </si>
+  <si>
+    <t>Digital Room LLC</t>
   </si>
 </sst>
 </file>
@@ -17690,7 +17693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18278,7 +18281,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18888,6 +18891,23 @@
       </c>
       <c r="E70" s="48">
         <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="48" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B71" s="48" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C71" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" s="50">
+        <v>46281</v>
+      </c>
+      <c r="E71" s="48">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F3F8D8B-47B1-47C5-BFDB-246AD1A84C25}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F27497D3-7B71-4B9B-98E1-8D26C023256F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7563" uniqueCount="3245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7569" uniqueCount="3246">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14176,6 +14176,9 @@
   </si>
   <si>
     <t>Digital Room LLC</t>
+  </si>
+  <si>
+    <t>Verizon Corp Resources Group LLC</t>
   </si>
 </sst>
 </file>
@@ -17075,10 +17078,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17693,7 +17692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18908,6 +18907,40 @@
       </c>
       <c r="E71" s="48">
         <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="31.5">
+      <c r="A72" s="60" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B72" s="60" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C72" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" s="50">
+        <v>46283</v>
+      </c>
+      <c r="E72" s="49">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="31.5">
+      <c r="A73" s="60" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B73" s="60" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C73" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" s="50">
+        <v>46241</v>
+      </c>
+      <c r="E73" s="49">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -38045,7 +38078,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39167,7 +39200,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F27497D3-7B71-4B9B-98E1-8D26C023256F}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61C314C1-4DF6-4688-BB01-F796F5237FAE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7569" uniqueCount="3246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7575" uniqueCount="3249">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14179,6 +14179,15 @@
   </si>
   <si>
     <t>Verizon Corp Resources Group LLC</t>
+  </si>
+  <si>
+    <t>Automatic Data Processing, Inc.</t>
+  </si>
+  <si>
+    <t>International Paper, Barrington Box Plant</t>
+  </si>
+  <si>
+    <t>Barrington</t>
   </si>
 </sst>
 </file>
@@ -17078,6 +17087,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17692,13 +17705,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E73"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E75"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17736,7 +17749,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17787,7 +17800,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17804,7 +17817,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17821,7 +17834,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17838,7 +17851,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17855,7 +17868,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17906,7 +17919,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17923,7 +17936,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18008,7 +18021,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18076,7 +18089,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18093,7 +18106,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18110,7 +18123,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18195,7 +18208,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18501,7 +18514,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18722,7 +18735,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.5">
+    <row r="61" spans="1:5" ht="31.2">
       <c r="A61" s="63" t="s">
         <v>3233</v>
       </c>
@@ -18790,7 +18803,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.5">
+    <row r="65" spans="1:5" ht="31.2">
       <c r="A65" s="63" t="s">
         <v>3237</v>
       </c>
@@ -18858,7 +18871,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="60" t="s">
         <v>3241</v>
       </c>
@@ -18909,7 +18922,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.5">
+    <row r="72" spans="1:5" ht="31.2">
       <c r="A72" s="60" t="s">
         <v>3245</v>
       </c>
@@ -18926,7 +18939,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.5">
+    <row r="73" spans="1:5" ht="31.2">
       <c r="A73" s="60" t="s">
         <v>3245</v>
       </c>
@@ -18941,6 +18954,40 @@
       </c>
       <c r="E73" s="49">
         <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="31.2">
+      <c r="A74" s="63" t="s">
+        <v>3246</v>
+      </c>
+      <c r="B74" s="63" t="s">
+        <v>2890</v>
+      </c>
+      <c r="C74" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" s="65">
+        <v>46290</v>
+      </c>
+      <c r="E74" s="63">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="31.2">
+      <c r="A75" s="48" t="s">
+        <v>3247</v>
+      </c>
+      <c r="B75" s="48" t="s">
+        <v>3248</v>
+      </c>
+      <c r="C75" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" s="50">
+        <v>46289</v>
+      </c>
+      <c r="E75" s="48">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -18959,12 +19006,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -19919,7 +19966,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20038,7 +20085,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20449,12 +20496,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20491,7 +20538,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20525,7 +20572,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20644,7 +20691,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20712,7 +20759,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20746,7 +20793,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21188,7 +21235,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21446,12 +21493,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21556,7 +21603,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21624,7 +21671,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21675,7 +21722,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21743,7 +21790,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22117,7 +22164,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22185,7 +22232,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22355,7 +22402,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22610,7 +22657,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23001,7 +23048,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23069,7 +23116,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23171,7 +23218,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23188,7 +23235,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23239,7 +23286,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23307,7 +23354,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23341,7 +23388,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23409,7 +23456,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23443,7 +23490,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23460,7 +23507,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23528,7 +23575,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23664,7 +23711,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23834,7 +23881,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24021,7 +24068,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24364,13 +24411,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25427,7 +25474,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25461,7 +25508,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25580,7 +25627,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25614,7 +25661,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25869,7 +25916,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -25937,7 +25984,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26246,13 +26293,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26374,7 +26421,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26799,7 +26846,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27207,7 +27254,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27550,13 +27597,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28050,7 +28097,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28424,7 +28471,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28645,7 +28692,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28679,7 +28726,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29158,13 +29205,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29184,7 +29231,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29252,7 +29299,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29303,7 +29350,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29422,7 +29469,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29558,7 +29605,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29660,7 +29707,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29677,7 +29724,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29694,7 +29741,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29796,7 +29843,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29864,7 +29911,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30034,7 +30081,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30085,7 +30132,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30357,7 +30404,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30544,7 +30591,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30870,13 +30917,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -30981,7 +31028,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32684,13 +32731,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33815,7 +33862,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33832,7 +33879,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34886,7 +34933,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -34945,13 +34992,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37355,16 +37402,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37381,7 +37428,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37398,7 +37445,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37415,7 +37462,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37432,7 +37479,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37449,7 +37496,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37466,7 +37513,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37483,7 +37530,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37500,7 +37547,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37517,7 +37564,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37534,7 +37581,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37551,7 +37598,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37568,7 +37615,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37585,7 +37632,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37602,7 +37649,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37619,7 +37666,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37636,7 +37683,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37653,7 +37700,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37670,7 +37717,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37687,7 +37734,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37704,7 +37751,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37721,7 +37768,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37738,7 +37785,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37755,7 +37802,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37772,7 +37819,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37789,7 +37836,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37806,7 +37853,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37823,7 +37870,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37840,7 +37887,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37857,7 +37904,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37874,7 +37921,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37891,7 +37938,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37908,7 +37955,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -37925,7 +37972,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -37942,7 +37989,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -37959,7 +38006,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -37976,7 +38023,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -37993,7 +38040,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38010,7 +38057,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38027,7 +38074,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38044,7 +38091,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38061,7 +38108,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38078,7 +38125,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38095,7 +38142,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38112,7 +38159,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38129,7 +38176,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38146,7 +38193,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38163,7 +38210,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38180,7 +38227,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38197,7 +38244,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38214,7 +38261,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38231,7 +38278,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38248,7 +38295,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38265,7 +38312,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38282,7 +38329,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38299,7 +38346,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38316,7 +38363,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38333,7 +38380,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38350,7 +38397,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38367,7 +38414,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38384,7 +38431,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38401,7 +38448,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38418,7 +38465,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38435,7 +38482,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38452,7 +38499,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38469,7 +38516,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38486,7 +38533,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38503,7 +38550,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38520,7 +38567,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38537,7 +38584,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38554,7 +38601,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38571,7 +38618,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38588,7 +38635,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38605,7 +38652,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38622,7 +38669,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38639,7 +38686,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38656,7 +38703,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38673,7 +38720,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38690,7 +38737,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38707,7 +38754,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38724,7 +38771,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38741,7 +38788,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38758,7 +38805,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38775,7 +38822,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38792,7 +38839,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38809,7 +38856,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38826,7 +38873,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38843,7 +38890,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38860,7 +38907,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38877,7 +38924,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38894,7 +38941,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38911,7 +38958,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -38928,7 +38975,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -38945,7 +38992,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -38962,7 +39009,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -38979,7 +39026,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -38996,7 +39043,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39013,7 +39060,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39030,7 +39077,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39047,7 +39094,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39064,7 +39111,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39081,7 +39128,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39098,7 +39145,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39115,7 +39162,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39132,7 +39179,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39149,7 +39196,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39166,7 +39213,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39183,7 +39230,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39200,7 +39247,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39217,7 +39264,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39253,14 +39300,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40865,14 +40912,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41502,7 +41549,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42585,14 +42632,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44324,13 +44371,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46068,14 +46115,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46214,7 +46261,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46231,7 +46278,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46282,7 +46329,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46350,7 +46397,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46401,7 +46448,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46435,7 +46482,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46656,7 +46703,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46724,7 +46771,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46792,7 +46839,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -46996,7 +47043,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47234,7 +47281,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47302,7 +47349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47548,7 +47595,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47650,7 +47697,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47667,7 +47714,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47701,7 +47748,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47718,7 +47765,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47769,7 +47816,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47888,7 +47935,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -47959,14 +48006,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49210,7 +49257,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49499,7 +49546,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49737,7 +49784,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49754,7 +49801,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49788,7 +49835,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49909,14 +49956,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50666,14 +50713,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51067,7 +51114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51254,7 +51301,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51550,13 +51597,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51644,7 +51691,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51882,7 +51929,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52205,7 +52252,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52222,7 +52269,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52239,7 +52286,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52256,7 +52303,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52290,7 +52337,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52528,7 +52575,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52545,7 +52592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52715,7 +52762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52800,7 +52847,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -52953,7 +53000,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53140,7 +53187,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53242,7 +53289,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53259,7 +53306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53412,7 +53459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53429,7 +53476,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53514,7 +53561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53565,7 +53612,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53837,7 +53884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -53990,7 +54037,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54058,7 +54105,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54092,7 +54139,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54109,7 +54156,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54364,7 +54411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54534,7 +54581,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54585,7 +54632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54670,7 +54717,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54755,7 +54802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55333,7 +55380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55693,12 +55740,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55837,7 +55884,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56364,7 +56411,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56704,7 +56751,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56721,7 +56768,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56738,7 +56785,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56823,7 +56870,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -56976,7 +57023,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -56993,7 +57040,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57044,7 +57091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57166,12 +57213,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57650,7 +57697,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58075,7 +58122,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61C314C1-4DF6-4688-BB01-F796F5237FAE}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5681D407-0BD0-4528-B799-1A798067B5DD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7575" uniqueCount="3249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7578" uniqueCount="3250">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14188,6 +14188,9 @@
   </si>
   <si>
     <t>Barrington</t>
+  </si>
+  <si>
+    <t>Samsung SDS America, Inc</t>
   </si>
 </sst>
 </file>
@@ -17705,7 +17708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -18988,6 +18991,23 @@
       </c>
       <c r="E75" s="48">
         <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="48" t="s">
+        <v>3249</v>
+      </c>
+      <c r="B76" s="48" t="s">
+        <v>2934</v>
+      </c>
+      <c r="C76" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" s="50">
+        <v>46296</v>
+      </c>
+      <c r="E76" s="48">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5681D407-0BD0-4528-B799-1A798067B5DD}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B08A57DF-4357-499A-9B2F-6A3123EA7759}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7578" uniqueCount="3250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7581" uniqueCount="3251">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14191,6 +14191,9 @@
   </si>
   <si>
     <t>Samsung SDS America, Inc</t>
+  </si>
+  <si>
+    <t>Headquarters Hotel Mgmt, LLC d/b/a Sheraton Atlantic City Convention Center Hotel</t>
   </si>
 </sst>
 </file>
@@ -17708,7 +17711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
@@ -19008,6 +19011,23 @@
       </c>
       <c r="E76" s="48">
         <v>179</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="62.4">
+      <c r="A77" s="60" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B77" s="60" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C77" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77" s="50">
+        <v>46296</v>
+      </c>
+      <c r="E77" s="49">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B08A57DF-4357-499A-9B2F-6A3123EA7759}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{233520DF-8C26-4973-9192-6ED1F9FAB99D}"/>
   <bookViews>
-    <workbookView xWindow="19092" yWindow="-1596" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7581" uniqueCount="3251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7584" uniqueCount="3252">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14194,6 +14194,9 @@
   </si>
   <si>
     <t>Headquarters Hotel Mgmt, LLC d/b/a Sheraton Atlantic City Convention Center Hotel</t>
+  </si>
+  <si>
+    <t>Fusion Transport LLC</t>
   </si>
 </sst>
 </file>
@@ -17711,13 +17714,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E77"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E78"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17755,7 +17758,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17806,7 +17809,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17823,7 +17826,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17840,7 +17843,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17857,7 +17860,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17874,7 +17877,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17925,7 +17928,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17942,7 +17945,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18027,7 +18030,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18095,7 +18098,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18112,7 +18115,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18129,7 +18132,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18214,7 +18217,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18520,7 +18523,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18741,7 +18744,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.2">
+    <row r="61" spans="1:5" ht="31.5">
       <c r="A61" s="63" t="s">
         <v>3233</v>
       </c>
@@ -18809,7 +18812,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.2">
+    <row r="65" spans="1:5" ht="31.5">
       <c r="A65" s="63" t="s">
         <v>3237</v>
       </c>
@@ -18877,7 +18880,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="60" t="s">
         <v>3241</v>
       </c>
@@ -18928,7 +18931,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.2">
+    <row r="72" spans="1:5" ht="31.5">
       <c r="A72" s="60" t="s">
         <v>3245</v>
       </c>
@@ -18945,7 +18948,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.2">
+    <row r="73" spans="1:5" ht="31.5">
       <c r="A73" s="60" t="s">
         <v>3245</v>
       </c>
@@ -18962,7 +18965,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.2">
+    <row r="74" spans="1:5" ht="31.5">
       <c r="A74" s="63" t="s">
         <v>3246</v>
       </c>
@@ -18979,7 +18982,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.2">
+    <row r="75" spans="1:5" ht="31.5">
       <c r="A75" s="48" t="s">
         <v>3247</v>
       </c>
@@ -19013,7 +19016,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="62.4">
+    <row r="77" spans="1:5" ht="63">
       <c r="A77" s="60" t="s">
         <v>3250</v>
       </c>
@@ -19028,6 +19031,23 @@
       </c>
       <c r="E77" s="49">
         <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="48" t="s">
+        <v>3251</v>
+      </c>
+      <c r="B78" s="48" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C78" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="D78" s="50">
+        <v>46296</v>
+      </c>
+      <c r="E78" s="48">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -19046,12 +19066,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20006,7 +20026,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20125,7 +20145,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20536,12 +20556,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20578,7 +20598,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20612,7 +20632,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20731,7 +20751,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20799,7 +20819,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20833,7 +20853,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21275,7 +21295,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21533,12 +21553,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21643,7 +21663,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21711,7 +21731,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21762,7 +21782,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21830,7 +21850,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22204,7 +22224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22272,7 +22292,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22442,7 +22462,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22697,7 +22717,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23088,7 +23108,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23156,7 +23176,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23258,7 +23278,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23275,7 +23295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23326,7 +23346,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23394,7 +23414,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23428,7 +23448,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23496,7 +23516,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23530,7 +23550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23547,7 +23567,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23615,7 +23635,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23751,7 +23771,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23921,7 +23941,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24108,7 +24128,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24451,13 +24471,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25514,7 +25534,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25548,7 +25568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25667,7 +25687,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25701,7 +25721,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25956,7 +25976,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26024,7 +26044,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26333,13 +26353,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26461,7 +26481,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26886,7 +26906,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27294,7 +27314,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27637,13 +27657,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28137,7 +28157,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28511,7 +28531,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28732,7 +28752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28766,7 +28786,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29245,13 +29265,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29271,7 +29291,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29339,7 +29359,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29390,7 +29410,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29509,7 +29529,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29645,7 +29665,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29747,7 +29767,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29764,7 +29784,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29781,7 +29801,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29883,7 +29903,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29951,7 +29971,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30121,7 +30141,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30172,7 +30192,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30444,7 +30464,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30631,7 +30651,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30957,13 +30977,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31068,7 +31088,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32771,13 +32791,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33902,7 +33922,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33919,7 +33939,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34973,7 +34993,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35032,13 +35052,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37442,16 +37462,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37468,7 +37488,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37485,7 +37505,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37502,7 +37522,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37519,7 +37539,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37536,7 +37556,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37553,7 +37573,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37570,7 +37590,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37587,7 +37607,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37604,7 +37624,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37621,7 +37641,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37638,7 +37658,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37655,7 +37675,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37672,7 +37692,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37689,7 +37709,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37706,7 +37726,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37723,7 +37743,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37740,7 +37760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37757,7 +37777,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37774,7 +37794,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37791,7 +37811,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37808,7 +37828,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37825,7 +37845,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37842,7 +37862,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37859,7 +37879,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37876,7 +37896,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37893,7 +37913,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37910,7 +37930,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37927,7 +37947,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37944,7 +37964,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37961,7 +37981,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37978,7 +37998,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -37995,7 +38015,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38012,7 +38032,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38029,7 +38049,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38046,7 +38066,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38063,7 +38083,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38080,7 +38100,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38097,7 +38117,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38114,7 +38134,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38131,7 +38151,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38148,7 +38168,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38165,7 +38185,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38182,7 +38202,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38199,7 +38219,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="63">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38216,7 +38236,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38233,7 +38253,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38250,7 +38270,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38267,7 +38287,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38284,7 +38304,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38301,7 +38321,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38318,7 +38338,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38335,7 +38355,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38352,7 +38372,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38369,7 +38389,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38386,7 +38406,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38403,7 +38423,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38420,7 +38440,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38437,7 +38457,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38454,7 +38474,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38471,7 +38491,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38488,7 +38508,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38505,7 +38525,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38522,7 +38542,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38539,7 +38559,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38556,7 +38576,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38573,7 +38593,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38590,7 +38610,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38607,7 +38627,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38624,7 +38644,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38641,7 +38661,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38658,7 +38678,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38675,7 +38695,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38692,7 +38712,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38709,7 +38729,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38726,7 +38746,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38743,7 +38763,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38760,7 +38780,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38777,7 +38797,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38794,7 +38814,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38811,7 +38831,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38828,7 +38848,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38845,7 +38865,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38862,7 +38882,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38879,7 +38899,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38896,7 +38916,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38913,7 +38933,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38930,7 +38950,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38947,7 +38967,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38964,7 +38984,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -38981,7 +39001,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -38998,7 +39018,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39015,7 +39035,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39032,7 +39052,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39049,7 +39069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39066,7 +39086,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39083,7 +39103,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39100,7 +39120,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39117,7 +39137,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39134,7 +39154,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39151,7 +39171,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39168,7 +39188,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39185,7 +39205,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39202,7 +39222,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39219,7 +39239,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39236,7 +39256,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39253,7 +39273,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39270,7 +39290,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39287,7 +39307,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39304,7 +39324,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39340,14 +39360,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40952,14 +40972,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41589,7 +41609,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42672,14 +42692,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44411,13 +44431,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46155,14 +46175,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46301,7 +46321,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46318,7 +46338,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46369,7 +46389,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46437,7 +46457,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46488,7 +46508,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46522,7 +46542,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46743,7 +46763,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46811,7 +46831,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46879,7 +46899,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47083,7 +47103,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47321,7 +47341,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47389,7 +47409,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47635,7 +47655,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47737,7 +47757,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47754,7 +47774,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47788,7 +47808,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47805,7 +47825,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47856,7 +47876,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47975,7 +47995,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48046,14 +48066,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49297,7 +49317,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49586,7 +49606,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49824,7 +49844,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49841,7 +49861,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49875,7 +49895,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -49996,14 +50016,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50753,14 +50773,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51154,7 +51174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51341,7 +51361,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51637,13 +51657,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51731,7 +51751,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51969,7 +51989,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52292,7 +52312,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52309,7 +52329,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52326,7 +52346,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52343,7 +52363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52377,7 +52397,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52615,7 +52635,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52632,7 +52652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52802,7 +52822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52887,7 +52907,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53040,7 +53060,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53227,7 +53247,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53329,7 +53349,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53346,7 +53366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53499,7 +53519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53516,7 +53536,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53601,7 +53621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53652,7 +53672,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53924,7 +53944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54077,7 +54097,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54145,7 +54165,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54179,7 +54199,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54196,7 +54216,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54451,7 +54471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54621,7 +54641,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54672,7 +54692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54757,7 +54777,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54842,7 +54862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55420,7 +55440,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55780,12 +55800,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55924,7 +55944,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56451,7 +56471,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56791,7 +56811,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56808,7 +56828,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56825,7 +56845,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56910,7 +56930,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57063,7 +57083,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57080,7 +57100,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57131,7 +57151,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57253,12 +57273,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57737,7 +57757,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58162,7 +58182,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{233520DF-8C26-4973-9192-6ED1F9FAB99D}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9690303-0AC6-46B6-9C4B-B7D5A3676F3C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7584" uniqueCount="3252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7593" uniqueCount="3256">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14197,6 +14197,18 @@
   </si>
   <si>
     <t>Fusion Transport LLC</t>
+  </si>
+  <si>
+    <t>Notions Marketing</t>
+  </si>
+  <si>
+    <t>Winfit LLC</t>
+  </si>
+  <si>
+    <t>Mercer County</t>
+  </si>
+  <si>
+    <t>Novartis Pharmaceuticals Corporation</t>
   </si>
 </sst>
 </file>
@@ -17096,10 +17108,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17714,13 +17722,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E78"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E81"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17758,7 +17766,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17809,7 +17817,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17826,7 +17834,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17843,7 +17851,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17860,7 +17868,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17877,7 +17885,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17928,7 +17936,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17945,7 +17953,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18030,7 +18038,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18098,7 +18106,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18115,7 +18123,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18132,7 +18140,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18217,7 +18225,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18523,7 +18531,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18744,7 +18752,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.5">
+    <row r="61" spans="1:5" ht="31.2">
       <c r="A61" s="63" t="s">
         <v>3233</v>
       </c>
@@ -18812,7 +18820,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.5">
+    <row r="65" spans="1:5" ht="31.2">
       <c r="A65" s="63" t="s">
         <v>3237</v>
       </c>
@@ -18880,7 +18888,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="60" t="s">
         <v>3241</v>
       </c>
@@ -18931,7 +18939,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.5">
+    <row r="72" spans="1:5" ht="31.2">
       <c r="A72" s="60" t="s">
         <v>3245</v>
       </c>
@@ -18948,7 +18956,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.5">
+    <row r="73" spans="1:5" ht="31.2">
       <c r="A73" s="60" t="s">
         <v>3245</v>
       </c>
@@ -18965,7 +18973,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.5">
+    <row r="74" spans="1:5" ht="31.2">
       <c r="A74" s="63" t="s">
         <v>3246</v>
       </c>
@@ -18982,7 +18990,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.5">
+    <row r="75" spans="1:5" ht="31.2">
       <c r="A75" s="48" t="s">
         <v>3247</v>
       </c>
@@ -19016,7 +19024,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="63">
+    <row r="77" spans="1:5" ht="62.4">
       <c r="A77" s="60" t="s">
         <v>3250</v>
       </c>
@@ -19030,7 +19038,7 @@
         <v>46296</v>
       </c>
       <c r="E77" s="49">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -19048,6 +19056,57 @@
       </c>
       <c r="E78" s="48">
         <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="60" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B79" s="60" t="s">
+        <v>2612</v>
+      </c>
+      <c r="C79" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D79" s="50">
+        <v>46205</v>
+      </c>
+      <c r="E79" s="49">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="60" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B80" s="60" t="s">
+        <v>3254</v>
+      </c>
+      <c r="C80" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D80" s="50">
+        <v>46208</v>
+      </c>
+      <c r="E80" s="49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="31.2">
+      <c r="A81" s="60" t="s">
+        <v>3255</v>
+      </c>
+      <c r="B81" s="60" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C81" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D81" s="50">
+        <v>46297</v>
+      </c>
+      <c r="E81" s="49">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -19066,12 +19125,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20026,7 +20085,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20145,7 +20204,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20556,12 +20615,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20598,7 +20657,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20632,7 +20691,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20751,7 +20810,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20819,7 +20878,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20853,7 +20912,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21295,7 +21354,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21553,12 +21612,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21663,7 +21722,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21731,7 +21790,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21782,7 +21841,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21850,7 +21909,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22224,7 +22283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22292,7 +22351,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22462,7 +22521,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22717,7 +22776,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23108,7 +23167,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23176,7 +23235,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23278,7 +23337,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23295,7 +23354,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23346,7 +23405,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23414,7 +23473,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23448,7 +23507,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23516,7 +23575,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23550,7 +23609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23567,7 +23626,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23635,7 +23694,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23771,7 +23830,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -23941,7 +24000,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24128,7 +24187,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24471,13 +24530,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25534,7 +25593,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25568,7 +25627,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25687,7 +25746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25721,7 +25780,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -25976,7 +26035,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26044,7 +26103,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26353,13 +26412,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26481,7 +26540,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26906,7 +26965,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27314,7 +27373,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27657,13 +27716,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28157,7 +28216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28531,7 +28590,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28752,7 +28811,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28786,7 +28845,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29265,13 +29324,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29291,7 +29350,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29359,7 +29418,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29410,7 +29469,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29529,7 +29588,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29665,7 +29724,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29767,7 +29826,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29784,7 +29843,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29801,7 +29860,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29903,7 +29962,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -29971,7 +30030,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30141,7 +30200,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30192,7 +30251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30464,7 +30523,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30651,7 +30710,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -30977,13 +31036,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31088,7 +31147,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32791,13 +32850,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33922,7 +33981,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33939,7 +33998,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -34993,7 +35052,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35052,13 +35111,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37462,16 +37521,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37488,7 +37547,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37505,7 +37564,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37522,7 +37581,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37539,7 +37598,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37556,7 +37615,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37573,7 +37632,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37590,7 +37649,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37607,7 +37666,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37624,7 +37683,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37641,7 +37700,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37658,7 +37717,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37675,7 +37734,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37692,7 +37751,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37709,7 +37768,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37726,7 +37785,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37743,7 +37802,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37760,7 +37819,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37777,7 +37836,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37794,7 +37853,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37811,7 +37870,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37828,7 +37887,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37845,7 +37904,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37862,7 +37921,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37879,7 +37938,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37896,7 +37955,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37913,7 +37972,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37930,7 +37989,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -37947,7 +38006,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -37964,7 +38023,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -37981,7 +38040,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -37998,7 +38057,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38015,7 +38074,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38032,7 +38091,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38049,7 +38108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38066,7 +38125,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38083,7 +38142,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38100,7 +38159,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38117,7 +38176,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38134,7 +38193,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38151,7 +38210,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38168,7 +38227,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38185,7 +38244,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38202,7 +38261,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38219,7 +38278,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="63">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38236,7 +38295,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38253,7 +38312,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38270,7 +38329,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38287,7 +38346,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38304,7 +38363,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38321,7 +38380,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38338,7 +38397,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38355,7 +38414,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38372,7 +38431,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38389,7 +38448,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38406,7 +38465,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38423,7 +38482,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38440,7 +38499,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38457,7 +38516,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38474,7 +38533,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38491,7 +38550,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38508,7 +38567,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38525,7 +38584,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38542,7 +38601,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38559,7 +38618,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38576,7 +38635,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38593,7 +38652,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38610,7 +38669,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38627,7 +38686,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38644,7 +38703,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38661,7 +38720,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38678,7 +38737,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38695,7 +38754,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38712,7 +38771,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38729,7 +38788,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38746,7 +38805,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38763,7 +38822,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38780,7 +38839,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38797,7 +38856,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38814,7 +38873,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38831,7 +38890,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38848,7 +38907,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38865,7 +38924,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38882,7 +38941,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38899,7 +38958,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38916,7 +38975,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38933,7 +38992,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -38950,7 +39009,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -38967,7 +39026,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -38984,7 +39043,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39001,7 +39060,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39018,7 +39077,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39035,7 +39094,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39052,7 +39111,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39069,7 +39128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39086,7 +39145,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39103,7 +39162,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39120,7 +39179,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39137,7 +39196,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39154,7 +39213,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39171,7 +39230,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39188,7 +39247,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39205,7 +39264,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39222,7 +39281,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39239,7 +39298,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39256,7 +39315,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39273,7 +39332,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39290,7 +39349,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39307,7 +39366,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39324,7 +39383,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39360,14 +39419,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -40972,14 +41031,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41609,7 +41668,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42692,14 +42751,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44431,13 +44490,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46175,14 +46234,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46321,7 +46380,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46338,7 +46397,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46389,7 +46448,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46457,7 +46516,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46508,7 +46567,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46542,7 +46601,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46763,7 +46822,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46831,7 +46890,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46899,7 +46958,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47103,7 +47162,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47341,7 +47400,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47409,7 +47468,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47655,7 +47714,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47757,7 +47816,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47774,7 +47833,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47808,7 +47867,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47825,7 +47884,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47876,7 +47935,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -47995,7 +48054,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48049,7 +48108,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" fitToHeight="3" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="65" fitToHeight="3" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -48066,14 +48125,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49317,7 +49376,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49606,7 +49665,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49844,7 +49903,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49861,7 +49920,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49895,7 +49954,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50016,14 +50075,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50773,14 +50832,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51174,7 +51233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51361,7 +51420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51657,13 +51716,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51751,7 +51810,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -51989,7 +52048,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52312,7 +52371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52329,7 +52388,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52346,7 +52405,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52363,7 +52422,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52397,7 +52456,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52635,7 +52694,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52652,7 +52711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52822,7 +52881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52907,7 +52966,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53060,7 +53119,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53247,7 +53306,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53349,7 +53408,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53366,7 +53425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53519,7 +53578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53536,7 +53595,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53621,7 +53680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53672,7 +53731,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -53944,7 +54003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54097,7 +54156,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54165,7 +54224,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54199,7 +54258,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54216,7 +54275,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54471,7 +54530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54641,7 +54700,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54692,7 +54751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54777,7 +54836,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54862,7 +54921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55440,7 +55499,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55800,12 +55859,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -55944,7 +56003,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56471,7 +56530,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56811,7 +56870,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56828,7 +56887,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56845,7 +56904,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56930,7 +56989,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57083,7 +57142,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57100,7 +57159,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57151,7 +57210,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57273,12 +57332,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57757,7 +57816,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58182,7 +58241,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>
@@ -58661,7 +58720,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="17" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="20" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9690303-0AC6-46B6-9C4B-B7D5A3676F3C}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4655C3DE-3D91-4834-8CD6-673816CE9360}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7593" uniqueCount="3256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7596" uniqueCount="3256">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -17108,6 +17108,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17722,13 +17726,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E82"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17766,7 +17770,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17817,7 +17821,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17834,7 +17838,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17851,7 +17855,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17868,7 +17872,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17885,7 +17889,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17936,7 +17940,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17953,7 +17957,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18038,7 +18042,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18106,7 +18110,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18123,7 +18127,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18140,7 +18144,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18225,7 +18229,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18531,7 +18535,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3219</v>
       </c>
@@ -18752,7 +18756,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.2">
+    <row r="61" spans="1:5" ht="31.5">
       <c r="A61" s="63" t="s">
         <v>3233</v>
       </c>
@@ -18820,7 +18824,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.2">
+    <row r="65" spans="1:5" ht="31.5">
       <c r="A65" s="63" t="s">
         <v>3237</v>
       </c>
@@ -18888,7 +18892,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="60" t="s">
         <v>3241</v>
       </c>
@@ -18939,7 +18943,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.2">
+    <row r="72" spans="1:5" ht="31.5">
       <c r="A72" s="60" t="s">
         <v>3245</v>
       </c>
@@ -18956,7 +18960,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.2">
+    <row r="73" spans="1:5" ht="31.5">
       <c r="A73" s="60" t="s">
         <v>3245</v>
       </c>
@@ -18973,7 +18977,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.2">
+    <row r="74" spans="1:5" ht="31.5">
       <c r="A74" s="63" t="s">
         <v>3246</v>
       </c>
@@ -18990,7 +18994,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.2">
+    <row r="75" spans="1:5" ht="31.5">
       <c r="A75" s="48" t="s">
         <v>3247</v>
       </c>
@@ -19024,7 +19028,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="62.4">
+    <row r="77" spans="1:5" ht="63">
       <c r="A77" s="60" t="s">
         <v>3250</v>
       </c>
@@ -19092,7 +19096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="60" t="s">
         <v>3255</v>
       </c>
@@ -19107,6 +19111,23 @@
       </c>
       <c r="E81" s="49">
         <v>322</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="60" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B82" s="60" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C82" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D82" s="50">
+        <v>46211</v>
+      </c>
+      <c r="E82" s="49">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -19125,12 +19146,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20085,7 +20106,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20204,7 +20225,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20615,12 +20636,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20657,7 +20678,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20691,7 +20712,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20810,7 +20831,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -20878,7 +20899,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -20912,7 +20933,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21354,7 +21375,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21595,7 +21616,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="8" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="11" fitToHeight="8" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -21612,12 +21633,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21722,7 +21743,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21790,7 +21811,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -21841,7 +21862,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -21909,7 +21930,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22283,7 +22304,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22351,7 +22372,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22521,7 +22542,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22776,7 +22797,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23167,7 +23188,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23235,7 +23256,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23337,7 +23358,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23354,7 +23375,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23405,7 +23426,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23473,7 +23494,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23507,7 +23528,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23575,7 +23596,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23609,7 +23630,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23626,7 +23647,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23694,7 +23715,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -23830,7 +23851,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24000,7 +24021,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24187,7 +24208,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24530,13 +24551,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25593,7 +25614,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25627,7 +25648,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25746,7 +25767,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25780,7 +25801,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26035,7 +26056,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26103,7 +26124,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26412,13 +26433,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26540,7 +26561,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -26965,7 +26986,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27373,7 +27394,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27716,13 +27737,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28216,7 +28237,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28590,7 +28611,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28811,7 +28832,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -28845,7 +28866,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29307,7 +29328,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="7" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="32" fitToHeight="7" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -29324,13 +29345,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29350,7 +29371,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29418,7 +29439,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29469,7 +29490,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29588,7 +29609,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29724,7 +29745,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -29826,7 +29847,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -29843,7 +29864,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -29860,7 +29881,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -29962,7 +29983,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30030,7 +30051,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30200,7 +30221,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30251,7 +30272,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30523,7 +30544,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30710,7 +30731,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31036,13 +31057,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31147,7 +31168,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -32850,13 +32871,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -33981,7 +34002,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -33998,7 +34019,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35052,7 +35073,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35111,13 +35132,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37521,16 +37542,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37547,7 +37568,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37564,7 +37585,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37581,7 +37602,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37598,7 +37619,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37615,7 +37636,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37632,7 +37653,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37649,7 +37670,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37666,7 +37687,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37683,7 +37704,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37700,7 +37721,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37717,7 +37738,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37734,7 +37755,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37751,7 +37772,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37768,7 +37789,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37785,7 +37806,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37802,7 +37823,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37819,7 +37840,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -37836,7 +37857,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -37853,7 +37874,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -37870,7 +37891,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -37887,7 +37908,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -37904,7 +37925,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -37921,7 +37942,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -37938,7 +37959,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -37955,7 +37976,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -37972,7 +37993,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -37989,7 +38010,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38006,7 +38027,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38023,7 +38044,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38040,7 +38061,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38057,7 +38078,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38074,7 +38095,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38091,7 +38112,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38108,7 +38129,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38125,7 +38146,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38142,7 +38163,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38159,7 +38180,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38176,7 +38197,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38193,7 +38214,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38210,7 +38231,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38227,7 +38248,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38244,7 +38265,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38261,7 +38282,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38278,7 +38299,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38295,7 +38316,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38312,7 +38333,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38329,7 +38350,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38346,7 +38367,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38363,7 +38384,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38380,7 +38401,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38397,7 +38418,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38414,7 +38435,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38431,7 +38452,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38448,7 +38469,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38465,7 +38486,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38482,7 +38503,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38499,7 +38520,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38516,7 +38537,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38533,7 +38554,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38550,7 +38571,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38567,7 +38588,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38584,7 +38605,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38601,7 +38622,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38618,7 +38639,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38635,7 +38656,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38652,7 +38673,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38669,7 +38690,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38686,7 +38707,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38703,7 +38724,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38720,7 +38741,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38737,7 +38758,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38754,7 +38775,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38771,7 +38792,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38788,7 +38809,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38805,7 +38826,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38822,7 +38843,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -38839,7 +38860,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -38856,7 +38877,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -38873,7 +38894,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -38890,7 +38911,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -38907,7 +38928,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -38924,7 +38945,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -38941,7 +38962,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -38958,7 +38979,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -38975,7 +38996,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -38992,7 +39013,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39009,7 +39030,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39026,7 +39047,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39043,7 +39064,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39060,7 +39081,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39077,7 +39098,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39094,7 +39115,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39111,7 +39132,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39128,7 +39149,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39145,7 +39166,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39162,7 +39183,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39179,7 +39200,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39196,7 +39217,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39213,7 +39234,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39230,7 +39251,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39247,7 +39268,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39264,7 +39285,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39281,7 +39302,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39298,7 +39319,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39315,7 +39336,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39332,7 +39353,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39349,7 +39370,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39366,7 +39387,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39383,7 +39404,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39419,14 +39440,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41031,14 +41052,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41668,7 +41689,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42751,14 +42772,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44490,13 +44511,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46234,14 +46255,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46380,7 +46401,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46397,7 +46418,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46448,7 +46469,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46516,7 +46537,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46567,7 +46588,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46601,7 +46622,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46822,7 +46843,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -46890,7 +46911,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -46958,7 +46979,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47162,7 +47183,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47400,7 +47421,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47468,7 +47489,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47714,7 +47735,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47816,7 +47837,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -47833,7 +47854,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -47867,7 +47888,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -47884,7 +47905,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -47935,7 +47956,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48054,7 +48075,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48108,7 +48129,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="65" fitToHeight="3" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="10" fitToHeight="3" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -48125,14 +48146,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49376,7 +49397,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49665,7 +49686,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -49903,7 +49924,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -49920,7 +49941,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -49954,7 +49975,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50075,14 +50096,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -50832,14 +50853,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51233,7 +51254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51420,7 +51441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51716,13 +51737,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51810,7 +51831,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52048,7 +52069,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52371,7 +52392,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52388,7 +52409,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52405,7 +52426,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52422,7 +52443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52456,7 +52477,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52694,7 +52715,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52711,7 +52732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -52881,7 +52902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -52966,7 +52987,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53119,7 +53140,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53306,7 +53327,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53408,7 +53429,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53425,7 +53446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53578,7 +53599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53595,7 +53616,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53680,7 +53701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53731,7 +53752,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54003,7 +54024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54156,7 +54177,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54224,7 +54245,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54258,7 +54279,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54275,7 +54296,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54530,7 +54551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54700,7 +54721,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54751,7 +54772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -54836,7 +54857,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -54921,7 +54942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55499,7 +55520,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -55859,12 +55880,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56003,7 +56024,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56530,7 +56551,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -56870,7 +56891,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -56887,7 +56908,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -56904,7 +56925,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -56989,7 +57010,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57142,7 +57163,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57159,7 +57180,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57210,7 +57231,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57315,7 +57336,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="40" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="10" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -57332,12 +57353,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57816,7 +57837,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58241,7 +58262,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>
@@ -58720,7 +58741,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="20" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="99" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4655C3DE-3D91-4834-8CD6-673816CE9360}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{056F22C7-0E93-4B12-9822-9EA3F196B277}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14085,15 +14085,9 @@
     <t>7/24/26 - 11/20/26</t>
   </si>
   <si>
-    <t>FreshRealm</t>
-  </si>
-  <si>
     <t>Linden</t>
   </si>
   <si>
-    <t>6/27/26 - 727/26</t>
-  </si>
-  <si>
     <t>Reckitt Benckiser LLC</t>
   </si>
   <si>
@@ -14209,6 +14203,12 @@
   </si>
   <si>
     <t>Novartis Pharmaceuticals Corporation</t>
+  </si>
+  <si>
+    <t>FreshRealm, Inc.</t>
+  </si>
+  <si>
+    <t>7/27/26 - 8/31/26</t>
   </si>
 </sst>
 </file>
@@ -18502,25 +18502,25 @@
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="48" t="s">
+      <c r="A46" s="63" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B46" s="63" t="s">
         <v>3214</v>
       </c>
-      <c r="B46" s="48" t="s">
-        <v>3215</v>
-      </c>
-      <c r="C46" s="49" t="s">
+      <c r="C46" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="D46" s="50" t="s">
-        <v>3216</v>
-      </c>
-      <c r="E46" s="48">
-        <v>637</v>
+      <c r="D46" s="65" t="s">
+        <v>3255</v>
+      </c>
+      <c r="E46" s="63">
+        <v>628</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="58" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="B47" s="60" t="s">
         <v>2980</v>
@@ -18529,7 +18529,7 @@
         <v>66</v>
       </c>
       <c r="D47" s="50" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="E47" s="49">
         <v>57</v>
@@ -18537,7 +18537,7 @@
     </row>
     <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="B48" s="48" t="s">
         <v>1447</v>
@@ -18563,7 +18563,7 @@
         <v>67</v>
       </c>
       <c r="D49" s="50" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="E49" s="48">
         <v>95</v>
@@ -18571,7 +18571,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="48" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="B50" s="48" t="s">
         <v>1502</v>
@@ -18580,7 +18580,7 @@
         <v>67</v>
       </c>
       <c r="D50" s="50" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="E50" s="48">
         <v>260</v>
@@ -18588,7 +18588,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="60" t="s">
-        <v>3223</v>
+        <v>3221</v>
       </c>
       <c r="B51" s="60" t="s">
         <v>3018</v>
@@ -18597,7 +18597,7 @@
         <v>67</v>
       </c>
       <c r="D51" s="50" t="s">
-        <v>3224</v>
+        <v>3222</v>
       </c>
       <c r="E51" s="49">
         <v>114</v>
@@ -18605,7 +18605,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="48" t="s">
-        <v>3225</v>
+        <v>3223</v>
       </c>
       <c r="B52" s="48" t="s">
         <v>2043</v>
@@ -18614,7 +18614,7 @@
         <v>67</v>
       </c>
       <c r="D52" s="50" t="s">
-        <v>3226</v>
+        <v>3224</v>
       </c>
       <c r="E52" s="48">
         <v>90</v>
@@ -18656,7 +18656,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="63" t="s">
-        <v>3227</v>
+        <v>3225</v>
       </c>
       <c r="B55" s="63" t="s">
         <v>2036</v>
@@ -18690,7 +18690,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="48" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B57" s="48" t="s">
         <v>1479</v>
@@ -18699,7 +18699,7 @@
         <v>67</v>
       </c>
       <c r="D57" s="50" t="s">
-        <v>3229</v>
+        <v>3227</v>
       </c>
       <c r="E57" s="48">
         <v>58</v>
@@ -18716,7 +18716,7 @@
         <v>67</v>
       </c>
       <c r="D58" s="50" t="s">
-        <v>3230</v>
+        <v>3228</v>
       </c>
       <c r="E58" s="48">
         <v>64</v>
@@ -18724,10 +18724,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="48" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="C59" s="49" t="s">
         <v>67</v>
@@ -18758,7 +18758,7 @@
     </row>
     <row r="61" spans="1:5" ht="31.5">
       <c r="A61" s="63" t="s">
-        <v>3233</v>
+        <v>3231</v>
       </c>
       <c r="B61" s="63" t="s">
         <v>1441</v>
@@ -18775,7 +18775,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="63" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
       <c r="B62" s="63" t="s">
         <v>3168</v>
@@ -18792,7 +18792,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="48" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
       <c r="B63" s="48" t="s">
         <v>2937</v>
@@ -18809,7 +18809,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="63" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="B64" s="63" t="s">
         <v>3066</v>
@@ -18826,7 +18826,7 @@
     </row>
     <row r="65" spans="1:5" ht="31.5">
       <c r="A65" s="63" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="B65" s="63" t="s">
         <v>2043</v>
@@ -18843,10 +18843,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="63" t="s">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="B66" s="63" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
       <c r="C66" s="64" t="s">
         <v>68</v>
@@ -18860,7 +18860,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="48" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
       <c r="B67" s="48" t="s">
         <v>2705</v>
@@ -18894,10 +18894,10 @@
     </row>
     <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="60" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
       <c r="B69" s="60" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="C69" s="58" t="s">
         <v>68</v>
@@ -18914,7 +18914,7 @@
         <v>2910</v>
       </c>
       <c r="B70" s="48" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="C70" s="49" t="s">
         <v>68</v>
@@ -18928,7 +18928,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="48" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="B71" s="48" t="s">
         <v>2824</v>
@@ -18945,7 +18945,7 @@
     </row>
     <row r="72" spans="1:5" ht="31.5">
       <c r="A72" s="60" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B72" s="60" t="s">
         <v>2705</v>
@@ -18962,7 +18962,7 @@
     </row>
     <row r="73" spans="1:5" ht="31.5">
       <c r="A73" s="60" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
       <c r="B73" s="60" t="s">
         <v>2705</v>
@@ -18979,7 +18979,7 @@
     </row>
     <row r="74" spans="1:5" ht="31.5">
       <c r="A74" s="63" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="B74" s="63" t="s">
         <v>2890</v>
@@ -18996,10 +18996,10 @@
     </row>
     <row r="75" spans="1:5" ht="31.5">
       <c r="A75" s="48" t="s">
-        <v>3247</v>
+        <v>3245</v>
       </c>
       <c r="B75" s="48" t="s">
-        <v>3248</v>
+        <v>3246</v>
       </c>
       <c r="C75" s="49" t="s">
         <v>68</v>
@@ -19013,7 +19013,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="48" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
       <c r="B76" s="48" t="s">
         <v>2934</v>
@@ -19030,7 +19030,7 @@
     </row>
     <row r="77" spans="1:5" ht="63">
       <c r="A77" s="60" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
       <c r="B77" s="60" t="s">
         <v>1500</v>
@@ -19047,7 +19047,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="48" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
       <c r="B78" s="48" t="s">
         <v>1439</v>
@@ -19064,7 +19064,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="60" t="s">
-        <v>3252</v>
+        <v>3250</v>
       </c>
       <c r="B79" s="60" t="s">
         <v>2612</v>
@@ -19081,10 +19081,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="60" t="s">
-        <v>3253</v>
+        <v>3251</v>
       </c>
       <c r="B80" s="60" t="s">
-        <v>3254</v>
+        <v>3252</v>
       </c>
       <c r="C80" s="58" t="s">
         <v>69</v>
@@ -19098,7 +19098,7 @@
     </row>
     <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="60" t="s">
-        <v>3255</v>
+        <v>3253</v>
       </c>
       <c r="B81" s="60" t="s">
         <v>1519</v>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{056F22C7-0E93-4B12-9822-9EA3F196B277}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCEBCB61-EE37-4B32-94FE-4A14410DB26B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7596" uniqueCount="3256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7602" uniqueCount="3258">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14209,6 +14209,12 @@
   </si>
   <si>
     <t>7/27/26 - 8/31/26</t>
+  </si>
+  <si>
+    <t>The Cannabist Company</t>
+  </si>
+  <si>
+    <t>Mars WrigleyConfectionary US, LLC</t>
   </si>
 </sst>
 </file>
@@ -17108,10 +17114,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17726,7 +17728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18314,7 +18316,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -19128,6 +19130,40 @@
       </c>
       <c r="E82" s="49">
         <v>172</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="60" t="s">
+        <v>3256</v>
+      </c>
+      <c r="B83" s="60" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C83" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D83" s="50">
+        <v>46306</v>
+      </c>
+      <c r="E83" s="49">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="47.25">
+      <c r="A84" s="60" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B84" s="60" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C84" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D84" s="50">
+        <v>46311</v>
+      </c>
+      <c r="E84" s="49">
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/7.17.26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCEBCB61-EE37-4B32-94FE-4A14410DB26B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{185E781A-61E8-4EA0-8AD9-269F8B45CF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13395" yWindow="1905" windowWidth="14940" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7602" uniqueCount="3258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7609" uniqueCount="3261">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14215,6 +14215,15 @@
   </si>
   <si>
     <t>Mars WrigleyConfectionary US, LLC</t>
+  </si>
+  <si>
+    <t>Samsung Electronics America, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verizon Corp Resources Group LLC </t>
+  </si>
+  <si>
+    <t>9/30/26 - 10/14/26</t>
   </si>
 </sst>
 </file>
@@ -17728,7 +17737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19164,6 +19173,40 @@
       </c>
       <c r="E84" s="49">
         <v>307</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="31.5">
+      <c r="A85" s="60" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B85" s="60" t="s">
+        <v>2958</v>
+      </c>
+      <c r="C85" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" s="50" t="s">
+        <v>3260</v>
+      </c>
+      <c r="E85" s="49">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="31.5">
+      <c r="A86" s="60" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B86" s="60" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C86" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D86" s="50">
+        <v>46311</v>
+      </c>
+      <c r="E86" s="49">
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/7.17.26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{185E781A-61E8-4EA0-8AD9-269F8B45CF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94F4692A-4E22-4ABB-A023-65165993BFCD}"/>
   <bookViews>
-    <workbookView xWindow="13395" yWindow="1905" windowWidth="14940" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7609" uniqueCount="3261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7608" uniqueCount="3259">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14217,13 +14217,7 @@
     <t>Mars WrigleyConfectionary US, LLC</t>
   </si>
   <si>
-    <t>Samsung Electronics America, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verizon Corp Resources Group LLC </t>
-  </si>
-  <si>
-    <t>9/30/26 - 10/14/26</t>
+    <t xml:space="preserve">Samsung Electronics America, Inc. </t>
   </si>
 </sst>
 </file>
@@ -18325,7 +18319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -19158,7 +19152,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="31.5">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19183,10 +19177,10 @@
         <v>2958</v>
       </c>
       <c r="C85" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="D85" s="50" t="s">
-        <v>3260</v>
+        <v>69</v>
+      </c>
+      <c r="D85" s="50">
+        <v>46295</v>
       </c>
       <c r="E85" s="49">
         <v>739</v>
@@ -19194,7 +19188,7 @@
     </row>
     <row r="86" spans="1:5" ht="31.5">
       <c r="A86" s="60" t="s">
-        <v>3259</v>
+        <v>3243</v>
       </c>
       <c r="B86" s="60" t="s">
         <v>2705</v>
@@ -21695,7 +21689,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="11" fitToHeight="8" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup fitToHeight="8" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -29407,7 +29401,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="32" fitToHeight="7" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup fitToHeight="7" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -38344,7 +38338,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39466,7 +39460,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -57415,7 +57409,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="19" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -58820,7 +58814,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="99" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="16" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94F4692A-4E22-4ABB-A023-65165993BFCD}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04DF2683-3B3D-475B-B0C6-0F5FD85C5354}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7608" uniqueCount="3259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7618" uniqueCount="3263">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14218,6 +14218,18 @@
   </si>
   <si>
     <t xml:space="preserve">Samsung Electronics America, Inc. </t>
+  </si>
+  <si>
+    <t>Petvet Care Centers LLC</t>
+  </si>
+  <si>
+    <t>Egg Harbor Twp</t>
+  </si>
+  <si>
+    <t>BASF Corporation</t>
+  </si>
+  <si>
+    <t>11/1/26 - 12/31/26</t>
   </si>
 </sst>
 </file>
@@ -17117,6 +17129,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17731,7 +17747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19132,7 +19148,7 @@
         <v>46211</v>
       </c>
       <c r="E82" s="49">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -19201,6 +19217,57 @@
       </c>
       <c r="E86" s="49">
         <v>282</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="31.5">
+      <c r="A87" s="60" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B87" s="60" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C87" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D87" s="50">
+        <v>46283</v>
+      </c>
+      <c r="E87" s="49">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="60" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B88" s="60" t="s">
+        <v>3260</v>
+      </c>
+      <c r="C88" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D88" s="50">
+        <v>46303</v>
+      </c>
+      <c r="E88" s="49">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="60" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B89" s="60" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C89" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" s="50" t="s">
+        <v>3262</v>
+      </c>
+      <c r="E89" s="49">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04DF2683-3B3D-475B-B0C6-0F5FD85C5354}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17890984-6F5F-4560-942A-A6A9AE2D77E4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7618" uniqueCount="3263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7621" uniqueCount="3264">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14230,6 +14230,9 @@
   </si>
   <si>
     <t>11/1/26 - 12/31/26</t>
+  </si>
+  <si>
+    <t>Hudson County</t>
   </si>
 </sst>
 </file>
@@ -17129,10 +17132,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17747,7 +17746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19268,6 +19267,23 @@
       </c>
       <c r="E89" s="49">
         <v>62</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="60" t="s">
+        <v>3239</v>
+      </c>
+      <c r="B90" s="60" t="s">
+        <v>3263</v>
+      </c>
+      <c r="C90" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D90" s="50">
+        <v>46326</v>
+      </c>
+      <c r="E90" s="49">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17890984-6F5F-4560-942A-A6A9AE2D77E4}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F735B94-BC50-4832-AEE0-F3779838E328}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7621" uniqueCount="3264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7625" uniqueCount="3266">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14233,6 +14233,12 @@
   </si>
   <si>
     <t>Hudson County</t>
+  </si>
+  <si>
+    <t>Gerresheimer</t>
+  </si>
+  <si>
+    <t>9/1/26 - 7/30/27</t>
   </si>
 </sst>
 </file>
@@ -17132,6 +17138,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17746,13 +17756,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E90"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E91"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17790,7 +17800,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17841,7 +17851,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17858,7 +17868,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17875,7 +17885,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17892,7 +17902,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17909,7 +17919,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17960,7 +17970,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17977,7 +17987,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18062,7 +18072,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18130,7 +18140,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18147,7 +18157,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18164,7 +18174,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18249,7 +18259,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18555,7 +18565,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3217</v>
       </c>
@@ -18776,7 +18786,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.5">
+    <row r="61" spans="1:5" ht="31.2">
       <c r="A61" s="63" t="s">
         <v>3231</v>
       </c>
@@ -18844,7 +18854,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.5">
+    <row r="65" spans="1:5" ht="31.2">
       <c r="A65" s="63" t="s">
         <v>3235</v>
       </c>
@@ -18912,7 +18922,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="60" t="s">
         <v>3239</v>
       </c>
@@ -18963,7 +18973,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.5">
+    <row r="72" spans="1:5" ht="31.2">
       <c r="A72" s="60" t="s">
         <v>3243</v>
       </c>
@@ -18980,7 +18990,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.5">
+    <row r="73" spans="1:5" ht="31.2">
       <c r="A73" s="60" t="s">
         <v>3243</v>
       </c>
@@ -18997,7 +19007,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.5">
+    <row r="74" spans="1:5" ht="31.2">
       <c r="A74" s="63" t="s">
         <v>3244</v>
       </c>
@@ -19014,7 +19024,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.5">
+    <row r="75" spans="1:5" ht="31.2">
       <c r="A75" s="48" t="s">
         <v>3245</v>
       </c>
@@ -19048,7 +19058,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="63">
+    <row r="77" spans="1:5" ht="62.4">
       <c r="A77" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19116,7 +19126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="60" t="s">
         <v>3253</v>
       </c>
@@ -19167,7 +19177,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.5">
+    <row r="84" spans="1:5" ht="31.2">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19184,7 +19194,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="31.5">
+    <row r="85" spans="1:5" ht="31.2">
       <c r="A85" s="60" t="s">
         <v>3258</v>
       </c>
@@ -19201,7 +19211,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="31.5">
+    <row r="86" spans="1:5" ht="31.2">
       <c r="A86" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19218,7 +19228,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.5">
+    <row r="87" spans="1:5" ht="31.2">
       <c r="A87" s="60" t="s">
         <v>3231</v>
       </c>
@@ -19284,6 +19294,23 @@
       </c>
       <c r="E90" s="49">
         <v>59</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="48" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B91" s="48" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C91" s="49" t="s">
+        <v>364</v>
+      </c>
+      <c r="D91" s="50" t="s">
+        <v>3265</v>
+      </c>
+      <c r="E91" s="48">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -19302,12 +19329,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20262,7 +20289,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20381,7 +20408,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20792,12 +20819,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20834,7 +20861,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20868,7 +20895,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -20987,7 +21014,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -21055,7 +21082,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -21089,7 +21116,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21531,7 +21558,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21789,12 +21816,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21899,7 +21926,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21967,7 +21994,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -22018,7 +22045,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -22086,7 +22113,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22460,7 +22487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22528,7 +22555,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22698,7 +22725,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22953,7 +22980,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23344,7 +23371,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23412,7 +23439,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23514,7 +23541,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23531,7 +23558,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23582,7 +23609,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23650,7 +23677,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23684,7 +23711,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23752,7 +23779,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23786,7 +23813,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23803,7 +23830,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23871,7 +23898,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -24007,7 +24034,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24177,7 +24204,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24364,7 +24391,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24707,13 +24734,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25770,7 +25797,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25804,7 +25831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25923,7 +25950,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25957,7 +25984,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26212,7 +26239,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26280,7 +26307,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26589,13 +26616,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26717,7 +26744,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -27142,7 +27169,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27550,7 +27577,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27893,13 +27920,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28393,7 +28420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28767,7 +28794,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -28988,7 +29015,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -29022,7 +29049,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29501,13 +29528,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29527,7 +29554,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29595,7 +29622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29646,7 +29673,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29765,7 +29792,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29901,7 +29928,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -30003,7 +30030,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -30020,7 +30047,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -30037,7 +30064,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -30139,7 +30166,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30207,7 +30234,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30377,7 +30404,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30428,7 +30455,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30700,7 +30727,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30887,7 +30914,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31213,13 +31240,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31324,7 +31351,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -33027,13 +33054,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -34158,7 +34185,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -34175,7 +34202,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35229,7 +35256,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35288,13 +35315,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37698,16 +37725,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37724,7 +37751,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37741,7 +37768,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37758,7 +37785,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37775,7 +37802,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37792,7 +37819,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37809,7 +37836,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37826,7 +37853,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37843,7 +37870,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37860,7 +37887,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37877,7 +37904,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37894,7 +37921,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37911,7 +37938,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37928,7 +37955,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37945,7 +37972,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37962,7 +37989,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -37979,7 +38006,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -37996,7 +38023,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -38013,7 +38040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -38030,7 +38057,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -38047,7 +38074,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -38064,7 +38091,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -38081,7 +38108,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -38098,7 +38125,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -38115,7 +38142,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -38132,7 +38159,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -38149,7 +38176,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -38166,7 +38193,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38183,7 +38210,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38200,7 +38227,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38217,7 +38244,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38234,7 +38261,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38251,7 +38278,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38268,7 +38295,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38285,7 +38312,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38302,7 +38329,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38319,7 +38346,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38336,7 +38363,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38353,7 +38380,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38370,7 +38397,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38387,7 +38414,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38404,7 +38431,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38421,7 +38448,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38438,7 +38465,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38455,7 +38482,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38472,7 +38499,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38489,7 +38516,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38506,7 +38533,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38523,7 +38550,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38540,7 +38567,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38557,7 +38584,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38574,7 +38601,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38591,7 +38618,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38608,7 +38635,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38625,7 +38652,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38642,7 +38669,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38659,7 +38686,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38676,7 +38703,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38693,7 +38720,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38710,7 +38737,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38727,7 +38754,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38744,7 +38771,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38761,7 +38788,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38778,7 +38805,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38795,7 +38822,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38812,7 +38839,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38829,7 +38856,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38846,7 +38873,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38863,7 +38890,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38880,7 +38907,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38897,7 +38924,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38914,7 +38941,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38931,7 +38958,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38948,7 +38975,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38965,7 +38992,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -38982,7 +39009,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -38999,7 +39026,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -39016,7 +39043,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -39033,7 +39060,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -39050,7 +39077,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -39067,7 +39094,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -39084,7 +39111,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -39101,7 +39128,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -39118,7 +39145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -39135,7 +39162,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -39152,7 +39179,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -39169,7 +39196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39186,7 +39213,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39203,7 +39230,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39220,7 +39247,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39237,7 +39264,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39254,7 +39281,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39271,7 +39298,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39288,7 +39315,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39305,7 +39332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39322,7 +39349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39339,7 +39366,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39356,7 +39383,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39373,7 +39400,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39390,7 +39417,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39407,7 +39434,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39424,7 +39451,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39441,7 +39468,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39458,7 +39485,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39475,7 +39502,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39492,7 +39519,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39509,7 +39536,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39526,7 +39553,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39543,7 +39570,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39560,7 +39587,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39596,14 +39623,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41208,14 +41235,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41845,7 +41872,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42928,14 +42955,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44667,13 +44694,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46411,14 +46438,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46557,7 +46584,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46574,7 +46601,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46625,7 +46652,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46693,7 +46720,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46744,7 +46771,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46778,7 +46805,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -46999,7 +47026,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -47067,7 +47094,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47135,7 +47162,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47339,7 +47366,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47577,7 +47604,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47645,7 +47672,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47891,7 +47918,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -47993,7 +48020,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -48010,7 +48037,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -48044,7 +48071,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -48061,7 +48088,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -48112,7 +48139,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48231,7 +48258,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48302,14 +48329,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49553,7 +49580,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49842,7 +49869,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -50080,7 +50107,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -50097,7 +50124,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -50131,7 +50158,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50252,14 +50279,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51009,14 +51036,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51410,7 +51437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51597,7 +51624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51893,13 +51920,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51987,7 +52014,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52225,7 +52252,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52548,7 +52575,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52565,7 +52592,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52582,7 +52609,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52599,7 +52626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52633,7 +52660,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52871,7 +52898,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52888,7 +52915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -53058,7 +53085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -53143,7 +53170,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53296,7 +53323,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53483,7 +53510,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53585,7 +53612,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53602,7 +53629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53755,7 +53782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53772,7 +53799,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53857,7 +53884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53908,7 +53935,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54180,7 +54207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54333,7 +54360,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54401,7 +54428,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54435,7 +54462,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54452,7 +54479,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54707,7 +54734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54877,7 +54904,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54928,7 +54955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -55013,7 +55040,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -55098,7 +55125,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55676,7 +55703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -56036,12 +56063,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56180,7 +56207,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56707,7 +56734,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -57047,7 +57074,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -57064,7 +57091,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -57081,7 +57108,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -57166,7 +57193,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57319,7 +57346,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57336,7 +57363,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57387,7 +57414,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57509,12 +57536,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -57993,7 +58020,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58418,7 +58445,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F735B94-BC50-4832-AEE0-F3779838E328}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E52F3F1-84FF-4EC7-B610-F2B9C57D3588}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7625" uniqueCount="3266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7628" uniqueCount="3267">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14239,6 +14239,9 @@
   </si>
   <si>
     <t>9/1/26 - 7/30/27</t>
+  </si>
+  <si>
+    <t>Grocery Delivery E-Services USA, Inc DBA Hello Fresh</t>
   </si>
 </sst>
 </file>
@@ -17138,10 +17141,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17756,13 +17755,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E91"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E92"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17800,7 +17799,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17851,7 +17850,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17868,7 +17867,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17885,7 +17884,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17902,7 +17901,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17919,7 +17918,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17970,7 +17969,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -17987,7 +17986,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18072,7 +18071,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18140,7 +18139,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18157,7 +18156,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18174,7 +18173,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18259,7 +18258,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18565,7 +18564,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3217</v>
       </c>
@@ -18786,7 +18785,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.2">
+    <row r="61" spans="1:5" ht="31.5">
       <c r="A61" s="63" t="s">
         <v>3231</v>
       </c>
@@ -18854,7 +18853,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.2">
+    <row r="65" spans="1:5" ht="31.5">
       <c r="A65" s="63" t="s">
         <v>3235</v>
       </c>
@@ -18922,7 +18921,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="60" t="s">
         <v>3239</v>
       </c>
@@ -18973,7 +18972,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.2">
+    <row r="72" spans="1:5" ht="31.5">
       <c r="A72" s="60" t="s">
         <v>3243</v>
       </c>
@@ -18990,7 +18989,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.2">
+    <row r="73" spans="1:5" ht="31.5">
       <c r="A73" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19007,7 +19006,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.2">
+    <row r="74" spans="1:5" ht="31.5">
       <c r="A74" s="63" t="s">
         <v>3244</v>
       </c>
@@ -19024,7 +19023,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.2">
+    <row r="75" spans="1:5" ht="31.5">
       <c r="A75" s="48" t="s">
         <v>3245</v>
       </c>
@@ -19058,7 +19057,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="62.4">
+    <row r="77" spans="1:5" ht="63">
       <c r="A77" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19126,7 +19125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="60" t="s">
         <v>3253</v>
       </c>
@@ -19177,7 +19176,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.2">
+    <row r="84" spans="1:5" ht="31.5">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19194,7 +19193,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="31.2">
+    <row r="85" spans="1:5" ht="31.5">
       <c r="A85" s="60" t="s">
         <v>3258</v>
       </c>
@@ -19211,7 +19210,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="31.2">
+    <row r="86" spans="1:5" ht="31.5">
       <c r="A86" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19228,7 +19227,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.2">
+    <row r="87" spans="1:5" ht="31.5">
       <c r="A87" s="60" t="s">
         <v>3231</v>
       </c>
@@ -19311,6 +19310,23 @@
       </c>
       <c r="E91" s="48">
         <v>139</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="31.5">
+      <c r="A92" s="60" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B92" s="60" t="s">
+        <v>2955</v>
+      </c>
+      <c r="C92" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D92" s="50">
+        <v>46343</v>
+      </c>
+      <c r="E92" s="49">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -19329,12 +19345,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20289,7 +20305,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20408,7 +20424,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20819,12 +20835,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20861,7 +20877,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -20895,7 +20911,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -21014,7 +21030,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -21082,7 +21098,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -21116,7 +21132,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21558,7 +21574,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21816,12 +21832,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -21926,7 +21942,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -21994,7 +22010,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -22045,7 +22061,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -22113,7 +22129,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22487,7 +22503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22555,7 +22571,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22725,7 +22741,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -22980,7 +22996,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23371,7 +23387,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23439,7 +23455,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23541,7 +23557,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23558,7 +23574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23609,7 +23625,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23677,7 +23693,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23711,7 +23727,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23779,7 +23795,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23813,7 +23829,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23830,7 +23846,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -23898,7 +23914,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -24034,7 +24050,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24204,7 +24220,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24391,7 +24407,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24734,13 +24750,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25797,7 +25813,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25831,7 +25847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -25950,7 +25966,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -25984,7 +26000,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26239,7 +26255,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26307,7 +26323,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26616,13 +26632,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26744,7 +26760,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -27169,7 +27185,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27577,7 +27593,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -27920,13 +27936,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28420,7 +28436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28794,7 +28810,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -29015,7 +29031,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -29049,7 +29065,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29528,13 +29544,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29554,7 +29570,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29622,7 +29638,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29673,7 +29689,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29792,7 +29808,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -29928,7 +29944,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -30030,7 +30046,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -30047,7 +30063,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -30064,7 +30080,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -30166,7 +30182,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30234,7 +30250,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30404,7 +30420,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30455,7 +30471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30727,7 +30743,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -30914,7 +30930,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31240,13 +31256,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31351,7 +31367,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -33054,13 +33070,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -34185,7 +34201,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -34202,7 +34218,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35256,7 +35272,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35315,13 +35331,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37725,16 +37741,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37751,7 +37767,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37768,7 +37784,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37785,7 +37801,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37802,7 +37818,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37819,7 +37835,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37836,7 +37852,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37853,7 +37869,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37870,7 +37886,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37887,7 +37903,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -37904,7 +37920,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37921,7 +37937,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -37938,7 +37954,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -37955,7 +37971,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -37972,7 +37988,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -37989,7 +38005,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38006,7 +38022,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -38023,7 +38039,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -38040,7 +38056,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -38057,7 +38073,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -38074,7 +38090,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -38091,7 +38107,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -38108,7 +38124,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -38125,7 +38141,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -38142,7 +38158,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -38159,7 +38175,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -38176,7 +38192,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -38193,7 +38209,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38210,7 +38226,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38227,7 +38243,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38244,7 +38260,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38261,7 +38277,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38278,7 +38294,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38295,7 +38311,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38312,7 +38328,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38329,7 +38345,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38346,7 +38362,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38363,7 +38379,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38380,7 +38396,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38397,7 +38413,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38414,7 +38430,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38431,7 +38447,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38448,7 +38464,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38465,7 +38481,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38482,7 +38498,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38499,7 +38515,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38516,7 +38532,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38533,7 +38549,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38550,7 +38566,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38567,7 +38583,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38584,7 +38600,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38601,7 +38617,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38618,7 +38634,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38635,7 +38651,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38652,7 +38668,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38669,7 +38685,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38686,7 +38702,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38703,7 +38719,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38720,7 +38736,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38737,7 +38753,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38754,7 +38770,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38771,7 +38787,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38788,7 +38804,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38805,7 +38821,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38822,7 +38838,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38839,7 +38855,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38856,7 +38872,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38873,7 +38889,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38890,7 +38906,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38907,7 +38923,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38924,7 +38940,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -38941,7 +38957,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38958,7 +38974,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -38975,7 +38991,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38992,7 +39008,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -39009,7 +39025,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -39026,7 +39042,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -39043,7 +39059,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -39060,7 +39076,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -39077,7 +39093,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -39094,7 +39110,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -39111,7 +39127,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -39128,7 +39144,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -39145,7 +39161,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -39162,7 +39178,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -39179,7 +39195,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -39196,7 +39212,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39213,7 +39229,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39230,7 +39246,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39247,7 +39263,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39264,7 +39280,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39281,7 +39297,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39298,7 +39314,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39315,7 +39331,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39332,7 +39348,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39349,7 +39365,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39366,7 +39382,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39383,7 +39399,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39400,7 +39416,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39417,7 +39433,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39434,7 +39450,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39451,7 +39467,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39468,7 +39484,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39485,7 +39501,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39502,7 +39518,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39519,7 +39535,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39536,7 +39552,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39553,7 +39569,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39570,7 +39586,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39587,7 +39603,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39623,14 +39639,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41235,14 +41251,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41872,7 +41888,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -42955,14 +42971,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44694,13 +44710,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46438,14 +46454,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46584,7 +46600,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46601,7 +46617,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46652,7 +46668,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46720,7 +46736,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46771,7 +46787,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46805,7 +46821,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -47026,7 +47042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -47094,7 +47110,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47162,7 +47178,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47366,7 +47382,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47604,7 +47620,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47672,7 +47688,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -47918,7 +47934,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -48020,7 +48036,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -48037,7 +48053,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -48071,7 +48087,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -48088,7 +48104,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -48139,7 +48155,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48258,7 +48274,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48329,14 +48345,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49580,7 +49596,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49869,7 +49885,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -50107,7 +50123,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -50124,7 +50140,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -50158,7 +50174,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50279,14 +50295,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51036,14 +51052,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51437,7 +51453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51624,7 +51640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -51920,13 +51936,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -52014,7 +52030,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52252,7 +52268,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52575,7 +52591,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52592,7 +52608,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52609,7 +52625,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52626,7 +52642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52660,7 +52676,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -52898,7 +52914,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -52915,7 +52931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -53085,7 +53101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -53170,7 +53186,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53323,7 +53339,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53510,7 +53526,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53612,7 +53628,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53629,7 +53645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53782,7 +53798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53799,7 +53815,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53884,7 +53900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -53935,7 +53951,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54207,7 +54223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54360,7 +54376,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54428,7 +54444,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54462,7 +54478,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54479,7 +54495,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54734,7 +54750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -54904,7 +54920,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -54955,7 +54971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -55040,7 +55056,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -55125,7 +55141,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55703,7 +55719,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -56063,12 +56079,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56207,7 +56223,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56734,7 +56750,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -57074,7 +57090,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -57091,7 +57107,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -57108,7 +57124,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -57193,7 +57209,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57346,7 +57362,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57363,7 +57379,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57414,7 +57430,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57536,12 +57552,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -58020,7 +58036,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58445,7 +58461,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>
@@ -58924,7 +58940,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="16" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="99" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E52F3F1-84FF-4EC7-B610-F2B9C57D3588}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{825B2177-409A-43E2-9886-056AD711173D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7628" uniqueCount="3267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7632" uniqueCount="3268">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14242,6 +14242,9 @@
   </si>
   <si>
     <t>Grocery Delivery E-Services USA, Inc DBA Hello Fresh</t>
+  </si>
+  <si>
+    <t>8/19/26 - 11/15/26</t>
   </si>
 </sst>
 </file>
@@ -17141,6 +17144,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17755,7 +17762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18343,7 +18350,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -19176,7 +19183,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.5">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19312,7 +19319,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="47.25">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19327,6 +19334,23 @@
       </c>
       <c r="E92" s="49">
         <v>374</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="60" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B93" s="60" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C93" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D93" s="50" t="s">
+        <v>3267</v>
+      </c>
+      <c r="E93" s="49">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -38464,7 +38488,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39586,7 +39610,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -57535,7 +57559,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="19" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="16" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -58940,7 +58964,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="99" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="15" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{825B2177-409A-43E2-9886-056AD711173D}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E94C2CCC-92DB-41FD-A6F4-3A6D35F0EBA1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7632" uniqueCount="3268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7639" uniqueCount="3272">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14245,6 +14245,18 @@
   </si>
   <si>
     <t>8/19/26 - 11/15/26</t>
+  </si>
+  <si>
+    <t>Optum</t>
+  </si>
+  <si>
+    <t>Cenlar FSB</t>
+  </si>
+  <si>
+    <t>Ewing Twp.</t>
+  </si>
+  <si>
+    <t>8/21/26 - 10/30/26</t>
   </si>
 </sst>
 </file>
@@ -17762,7 +17774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18350,7 +18362,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -19183,7 +19195,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="31.5">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19319,7 +19331,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="47.25">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19351,6 +19363,40 @@
       </c>
       <c r="E93" s="49">
         <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="60" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B94" s="60" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C94" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D94" s="50">
+        <v>46363</v>
+      </c>
+      <c r="E94" s="49">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="60" t="s">
+        <v>3269</v>
+      </c>
+      <c r="B95" s="60" t="s">
+        <v>3270</v>
+      </c>
+      <c r="C95" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D95" s="50" t="s">
+        <v>3271</v>
+      </c>
+      <c r="E95" s="49">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -38488,7 +38534,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.75">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39610,7 +39656,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.5">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/8.28.26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E94C2CCC-92DB-41FD-A6F4-3A6D35F0EBA1}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C398B6E3-B4C4-4281-AEA0-07F39F2F97A9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -57,6 +57,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'2019 WARN Notices'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'2020 WARN Notices'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'2021 WARN Notices'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2026 WARN Notices'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7639" uniqueCount="3272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7643" uniqueCount="3275">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14257,6 +14258,15 @@
   </si>
   <si>
     <t>8/21/26 - 10/30/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enablx, INC </t>
+  </si>
+  <si>
+    <t>Rockaway Township</t>
+  </si>
+  <si>
+    <t>12/31/26 - 3/31/27</t>
   </si>
 </sst>
 </file>
@@ -17156,10 +17166,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17774,7 +17780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -18362,7 +18368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -19195,7 +19201,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.5">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19331,7 +19337,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="47.25">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19397,6 +19403,23 @@
       </c>
       <c r="E95" s="49">
         <v>50</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="60" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B96" s="60" t="s">
+        <v>3273</v>
+      </c>
+      <c r="C96" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D96" s="50" t="s">
+        <v>3274</v>
+      </c>
+      <c r="E96" s="49">
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -38534,7 +38557,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -39656,7 +39679,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.5">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/jesse_elliot_dol_nj_gov/Documents/Documents/Documents/Jesse Elliot/Communications Office/Websites/DOL/Revisions/8.28.26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C398B6E3-B4C4-4281-AEA0-07F39F2F97A9}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24213DDD-46C0-4EF6-8923-2397CA5D6127}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -57,7 +57,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'2019 WARN Notices'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'2020 WARN Notices'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'2021 WARN Notices'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2026 WARN Notices'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -69,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7643" uniqueCount="3275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7646" uniqueCount="3276">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14260,10 +14259,13 @@
     <t>8/21/26 - 10/30/26</t>
   </si>
   <si>
-    <t xml:space="preserve">Enablx, INC </t>
-  </si>
-  <si>
-    <t>Rockaway Township</t>
+    <t>Cellares Corporation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enablx, Inc. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rockaway Twp. </t>
   </si>
   <si>
     <t>12/31/26 - 3/31/27</t>
@@ -17780,13 +17782,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E96"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <dimension ref="A1:E97"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17824,7 +17826,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.5">
+    <row r="3" spans="1:5" ht="31.2">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17875,7 +17877,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="47.25">
+    <row r="6" spans="1:5" ht="46.8">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17892,7 +17894,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="47.25">
+    <row r="7" spans="1:5" ht="46.8">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17909,7 +17911,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.5">
+    <row r="8" spans="1:5" ht="31.2">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17926,7 +17928,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17943,7 +17945,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78.75">
+    <row r="10" spans="1:5" ht="78">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17994,7 +17996,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="47.25">
+    <row r="13" spans="1:5" ht="46.8">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -18011,7 +18013,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.5">
+    <row r="14" spans="1:5" ht="31.2">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18096,7 +18098,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18164,7 +18166,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="63">
+    <row r="23" spans="1:5" ht="62.4">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18181,7 +18183,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.5">
+    <row r="24" spans="1:5" ht="31.2">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18198,7 +18200,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="47.25">
+    <row r="25" spans="1:5" ht="46.8">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18283,7 +18285,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.5">
+    <row r="30" spans="1:5" ht="31.2">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18368,7 +18370,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="31.5">
+    <row r="35" spans="1:5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18589,7 +18591,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="48" t="s">
         <v>3217</v>
       </c>
@@ -18810,7 +18812,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.5">
+    <row r="61" spans="1:5" ht="31.2">
       <c r="A61" s="63" t="s">
         <v>3231</v>
       </c>
@@ -18878,7 +18880,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.5">
+    <row r="65" spans="1:5" ht="31.2">
       <c r="A65" s="63" t="s">
         <v>3235</v>
       </c>
@@ -18946,7 +18948,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="60" t="s">
         <v>3239</v>
       </c>
@@ -18997,7 +18999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.5">
+    <row r="72" spans="1:5" ht="31.2">
       <c r="A72" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19014,7 +19016,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.5">
+    <row r="73" spans="1:5" ht="31.2">
       <c r="A73" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19031,7 +19033,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.5">
+    <row r="74" spans="1:5" ht="31.2">
       <c r="A74" s="63" t="s">
         <v>3244</v>
       </c>
@@ -19048,7 +19050,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.5">
+    <row r="75" spans="1:5" ht="31.2">
       <c r="A75" s="48" t="s">
         <v>3245</v>
       </c>
@@ -19082,7 +19084,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="63">
+    <row r="77" spans="1:5" ht="62.4">
       <c r="A77" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19150,7 +19152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="60" t="s">
         <v>3253</v>
       </c>
@@ -19201,7 +19203,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="31.2">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19218,7 +19220,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="31.5">
+    <row r="85" spans="1:5" ht="31.2">
       <c r="A85" s="60" t="s">
         <v>3258</v>
       </c>
@@ -19235,7 +19237,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="31.5">
+    <row r="86" spans="1:5" ht="31.2">
       <c r="A86" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19252,7 +19254,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.5">
+    <row r="87" spans="1:5" ht="31.2">
       <c r="A87" s="60" t="s">
         <v>3231</v>
       </c>
@@ -19337,7 +19339,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="47.25">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19410,15 +19412,32 @@
         <v>3272</v>
       </c>
       <c r="B96" s="60" t="s">
-        <v>3273</v>
+        <v>1542</v>
       </c>
       <c r="C96" s="58" t="s">
         <v>364</v>
       </c>
-      <c r="D96" s="50" t="s">
+      <c r="D96" s="50">
+        <v>46345</v>
+      </c>
+      <c r="E96" s="49">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="60" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B97" s="60" t="s">
         <v>3274</v>
       </c>
-      <c r="E96" s="49">
+      <c r="C97" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="D97" s="50" t="s">
+        <v>3275</v>
+      </c>
+      <c r="E97" s="49">
         <v>187</v>
       </c>
     </row>
@@ -19438,12 +19457,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="50.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20398,7 +20417,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5" ht="28.8">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20517,7 +20536,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30">
+    <row r="64" spans="1:5" ht="28.8">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20928,12 +20947,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="58.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20970,7 +20989,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -21004,7 +21023,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -21123,7 +21142,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -21191,7 +21210,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -21225,7 +21244,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21667,7 +21686,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21925,12 +21944,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -22035,7 +22054,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="28.8">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -22103,7 +22122,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -22154,7 +22173,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -22222,7 +22241,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22596,7 +22615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22664,7 +22683,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22834,7 +22853,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -23089,7 +23108,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23480,7 +23499,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30">
+    <row r="92" spans="1:5" ht="28.8">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23548,7 +23567,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30">
+    <row r="96" spans="1:5" ht="28.8">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23650,7 +23669,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="45">
+    <row r="102" spans="1:5" ht="28.8">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23667,7 +23686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="30">
+    <row r="103" spans="1:5" ht="28.8">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23718,7 +23737,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23786,7 +23805,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5" ht="28.8">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23820,7 +23839,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30">
+    <row r="112" spans="1:5">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23888,7 +23907,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5" ht="28.8">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23922,7 +23941,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30">
+    <row r="118" spans="1:5" ht="28.8">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23939,7 +23958,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -24007,7 +24026,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="30">
+    <row r="123" spans="1:5">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -24143,7 +24162,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="30">
+    <row r="131" spans="1:5">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24313,7 +24332,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="30">
+    <row r="141" spans="1:5" ht="28.8">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24500,7 +24519,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="30">
+    <row r="152" spans="1:5">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24843,13 +24862,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25906,7 +25925,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="30">
+    <row r="63" spans="1:5">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25940,7 +25959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -26059,7 +26078,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="30">
+    <row r="72" spans="1:5" ht="28.8">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -26093,7 +26112,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26348,7 +26367,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="30">
+    <row r="89" spans="1:5" ht="28.8">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26416,7 +26435,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="30">
+    <row r="93" spans="1:5" ht="28.8">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26725,13 +26744,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26853,7 +26872,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -27278,7 +27297,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30">
+    <row r="33" spans="1:5" ht="28.8">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27686,7 +27705,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30">
+    <row r="57" spans="1:5">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -28029,13 +28048,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28529,7 +28548,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28903,7 +28922,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5" ht="28.8">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -29124,7 +29143,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30">
+    <row r="65" spans="1:5">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -29158,7 +29177,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5" ht="28.8">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29637,13 +29656,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29663,7 +29682,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" ht="28.8">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29731,7 +29750,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29782,7 +29801,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29901,7 +29920,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -30037,7 +30056,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -30139,7 +30158,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="30">
+    <row r="30" spans="1:5" ht="28.8">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -30156,7 +30175,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30">
+    <row r="31" spans="1:5" ht="28.8">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -30173,7 +30192,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="45">
+    <row r="32" spans="1:5" ht="28.8">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -30275,7 +30294,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30343,7 +30362,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30513,7 +30532,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30">
+    <row r="52" spans="1:5">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30564,7 +30583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30">
+    <row r="55" spans="1:5">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30836,7 +30855,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30">
+    <row r="71" spans="1:5" ht="28.8">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -31023,7 +31042,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30">
+    <row r="82" spans="1:5" ht="28.8">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31349,13 +31368,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31460,7 +31479,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -33163,13 +33182,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -34294,7 +34313,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -34311,7 +34330,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="30">
+    <row r="68" spans="1:5">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35365,7 +35384,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="30">
+    <row r="130" spans="1:5" ht="28.8">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35424,13 +35443,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37834,16 +37853,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75">
+    <row r="1" spans="1:5" ht="15.6">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37860,7 +37879,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.5">
+    <row r="2" spans="1:5" ht="31.2">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37877,7 +37896,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75">
+    <row r="3" spans="1:5" ht="15.6">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37894,7 +37913,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.5">
+    <row r="4" spans="1:5" ht="31.2">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37911,7 +37930,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="47.25">
+    <row r="5" spans="1:5" ht="46.8">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37928,7 +37947,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75">
+    <row r="6" spans="1:5" ht="15.6">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37945,7 +37964,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75">
+    <row r="7" spans="1:5" ht="15.6">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37962,7 +37981,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75">
+    <row r="8" spans="1:5" ht="15.6">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37979,7 +37998,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.5">
+    <row r="9" spans="1:5" ht="31.2">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -37996,7 +38015,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75">
+    <row r="10" spans="1:5" ht="15.6">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -38013,7 +38032,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.5">
+    <row r="11" spans="1:5" ht="31.2">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -38030,7 +38049,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="94.5">
+    <row r="12" spans="1:5" ht="93.6">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -38047,7 +38066,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75">
+    <row r="13" spans="1:5" ht="15.6">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -38064,7 +38083,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75">
+    <row r="14" spans="1:5" ht="15.6">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -38081,7 +38100,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
+    <row r="15" spans="1:5" ht="15.6">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -38098,7 +38117,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75">
+    <row r="16" spans="1:5" ht="15.6">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38115,7 +38134,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="63">
+    <row r="17" spans="1:5" ht="62.4">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -38132,7 +38151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="63">
+    <row r="18" spans="1:5" ht="62.4">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -38149,7 +38168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.5">
+    <row r="19" spans="1:5" ht="31.2">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -38166,7 +38185,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75">
+    <row r="20" spans="1:5" ht="15.6">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -38183,7 +38202,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="47.25">
+    <row r="21" spans="1:5" ht="46.8">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -38200,7 +38219,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75">
+    <row r="22" spans="1:5" ht="15.6">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -38217,7 +38236,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75">
+    <row r="23" spans="1:5" ht="15.6">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -38234,7 +38253,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75">
+    <row r="24" spans="1:5" ht="15.6">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -38251,7 +38270,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75">
+    <row r="25" spans="1:5" ht="15.6">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -38268,7 +38287,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75">
+    <row r="26" spans="1:5" ht="15.6">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -38285,7 +38304,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.5">
+    <row r="27" spans="1:5" ht="31.2">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -38302,7 +38321,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75">
+    <row r="28" spans="1:5" ht="15.6">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38319,7 +38338,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75">
+    <row r="29" spans="1:5" ht="15.6">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38336,7 +38355,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75">
+    <row r="30" spans="1:5" ht="15.6">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38353,7 +38372,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="94.5">
+    <row r="31" spans="1:5" ht="93.6">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38370,7 +38389,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="63">
+    <row r="32" spans="1:5" ht="62.4">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38387,7 +38406,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75">
+    <row r="33" spans="1:5" ht="15.6">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38404,7 +38423,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="63">
+    <row r="34" spans="1:5" ht="62.4">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38421,7 +38440,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75">
+    <row r="35" spans="1:5" ht="15.6">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38438,7 +38457,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75">
+    <row r="36" spans="1:5" ht="15.6">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38455,7 +38474,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75">
+    <row r="37" spans="1:5" ht="15.6">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38472,7 +38491,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="63">
+    <row r="38" spans="1:5" ht="62.4">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38489,7 +38508,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75">
+    <row r="39" spans="1:5" ht="15.6">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38506,7 +38525,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75">
+    <row r="40" spans="1:5" ht="15.6">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38523,7 +38542,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75">
+    <row r="41" spans="1:5" ht="15.6">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38540,7 +38559,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75">
+    <row r="42" spans="1:5" ht="15.6">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38557,7 +38576,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="15.6">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38574,7 +38593,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75">
+    <row r="44" spans="1:5" ht="15.6">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38591,7 +38610,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="47.25">
+    <row r="45" spans="1:5" ht="46.8">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38608,7 +38627,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75">
+    <row r="46" spans="1:5" ht="15.6">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38625,7 +38644,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75">
+    <row r="47" spans="1:5" ht="15.6">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38642,7 +38661,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.5">
+    <row r="48" spans="1:5" ht="31.2">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38659,7 +38678,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75">
+    <row r="49" spans="1:5" ht="15.6">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38676,7 +38695,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.5">
+    <row r="50" spans="1:5" ht="31.2">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38693,7 +38712,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75">
+    <row r="51" spans="1:5" ht="15.6">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38710,7 +38729,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75">
+    <row r="52" spans="1:5" ht="15.6">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38727,7 +38746,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75">
+    <row r="53" spans="1:5" ht="15.6">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38744,7 +38763,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.5">
+    <row r="54" spans="1:5" ht="31.2">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38761,7 +38780,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.75">
+    <row r="55" spans="1:5" ht="15.6">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38778,7 +38797,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="94.5">
+    <row r="56" spans="1:5" ht="93.6">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38795,7 +38814,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75">
+    <row r="57" spans="1:5" ht="15.6">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38812,7 +38831,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75">
+    <row r="58" spans="1:5" ht="15.6">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38829,7 +38848,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75">
+    <row r="59" spans="1:5" ht="15.6">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38846,7 +38865,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75">
+    <row r="60" spans="1:5" ht="15.6">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38863,7 +38882,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="47.25">
+    <row r="61" spans="1:5" ht="46.8">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38880,7 +38899,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75">
+    <row r="62" spans="1:5" ht="15.6">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38897,7 +38916,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75">
+    <row r="63" spans="1:5" ht="15.6">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38914,7 +38933,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75">
+    <row r="64" spans="1:5" ht="15.6">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38931,7 +38950,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75">
+    <row r="65" spans="1:5" ht="15.6">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38948,7 +38967,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75">
+    <row r="66" spans="1:5" ht="15.6">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38965,7 +38984,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75">
+    <row r="67" spans="1:5" ht="15.6">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -38982,7 +39001,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75">
+    <row r="68" spans="1:5" ht="15.6">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -38999,7 +39018,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.75">
+    <row r="69" spans="1:5" ht="15.6">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -39016,7 +39035,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.5">
+    <row r="70" spans="1:5" ht="31.2">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -39033,7 +39052,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75">
+    <row r="71" spans="1:5" ht="15.6">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -39050,7 +39069,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75">
+    <row r="72" spans="1:5" ht="15.6">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -39067,7 +39086,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75">
+    <row r="73" spans="1:5" ht="15.6">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -39084,7 +39103,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="47.25">
+    <row r="74" spans="1:5" ht="46.8">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -39101,7 +39120,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75">
+    <row r="75" spans="1:5" ht="15.6">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -39118,7 +39137,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75">
+    <row r="76" spans="1:5" ht="15.6">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -39135,7 +39154,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.5">
+    <row r="77" spans="1:5" ht="31.2">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -39152,7 +39171,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.5">
+    <row r="78" spans="1:5" ht="31.2">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -39169,7 +39188,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.5">
+    <row r="79" spans="1:5" ht="31.2">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -39186,7 +39205,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.75">
+    <row r="80" spans="1:5" ht="15.6">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -39203,7 +39222,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.5">
+    <row r="81" spans="1:5" ht="31.2">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -39220,7 +39239,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75">
+    <row r="82" spans="1:5" ht="15.6">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -39237,7 +39256,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.5">
+    <row r="83" spans="1:5" ht="31.2">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -39254,7 +39273,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="47.25">
+    <row r="84" spans="1:5" ht="46.8">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -39271,7 +39290,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75">
+    <row r="85" spans="1:5" ht="15.6">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -39288,7 +39307,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.75">
+    <row r="86" spans="1:5" ht="15.6">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -39305,7 +39324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.75">
+    <row r="87" spans="1:5" ht="15.6">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39322,7 +39341,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.75">
+    <row r="88" spans="1:5" ht="15.6">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39339,7 +39358,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.75">
+    <row r="89" spans="1:5" ht="15.6">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39356,7 +39375,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75">
+    <row r="90" spans="1:5" ht="15.6">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39373,7 +39392,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="47.25">
+    <row r="91" spans="1:5" ht="46.8">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39390,7 +39409,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.5">
+    <row r="92" spans="1:5" ht="31.2">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39407,7 +39426,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.5">
+    <row r="93" spans="1:5" ht="31.2">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39424,7 +39443,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39441,7 +39460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39458,7 +39477,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.75">
+    <row r="96" spans="1:5" ht="15.6">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39475,7 +39494,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75">
+    <row r="97" spans="1:5" ht="15.6">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39492,7 +39511,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39509,7 +39528,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.5">
+    <row r="99" spans="1:5" ht="31.2">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39526,7 +39545,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75">
+    <row r="100" spans="1:5" ht="15.6">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39543,7 +39562,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75">
+    <row r="101" spans="1:5" ht="15.6">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39560,7 +39579,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.5">
+    <row r="102" spans="1:5" ht="31.2">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39577,7 +39596,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.75">
+    <row r="103" spans="1:5" ht="15.6">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39594,7 +39613,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.75">
+    <row r="104" spans="1:5" ht="15.6">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39611,7 +39630,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.75">
+    <row r="105" spans="1:5" ht="15.6">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39628,7 +39647,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.75">
+    <row r="106" spans="1:5" ht="15.6">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39645,7 +39664,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75">
+    <row r="107" spans="1:5" ht="15.6">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39662,7 +39681,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.75">
+    <row r="108" spans="1:5" ht="15.6">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39679,7 +39698,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="47.25">
+    <row r="109" spans="1:5" ht="31.2">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39696,7 +39715,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.75">
+    <row r="110" spans="1:5" ht="15.6">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39732,14 +39751,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41344,14 +41363,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41981,7 +42000,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30">
+    <row r="38" spans="1:5">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -43064,14 +43083,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44803,13 +44822,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46547,14 +46566,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46693,7 +46712,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="47.25">
+    <row r="9" spans="1:5" ht="46.8">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46710,7 +46729,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="47.25">
+    <row r="10" spans="1:5" ht="46.8">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46761,7 +46780,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.5">
+    <row r="13" spans="1:5" ht="31.2">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46829,7 +46848,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="47.25">
+    <row r="17" spans="1:5" ht="46.8">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46880,7 +46899,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.5">
+    <row r="20" spans="1:5" ht="31.2">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46914,7 +46933,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.5">
+    <row r="22" spans="1:5" ht="31.2">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -47135,7 +47154,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="63">
+    <row r="35" spans="1:5" ht="62.4">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -47203,7 +47222,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5">
+    <row r="39" spans="1:5" ht="31.2">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47271,7 +47290,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.5">
+    <row r="43" spans="1:5" ht="31.2">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47475,7 +47494,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
+    <row r="55" spans="1:5" ht="78">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47713,7 +47732,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.5">
+    <row r="69" spans="1:5" ht="31.2">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47781,7 +47800,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="63">
+    <row r="73" spans="1:5" ht="62.4">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -48027,7 +48046,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.5">
+    <row r="88" spans="1:5" ht="31.2">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -48129,7 +48148,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.5">
+    <row r="94" spans="1:5" ht="31.2">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -48146,7 +48165,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.5">
+    <row r="95" spans="1:5" ht="31.2">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -48180,7 +48199,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78.75">
+    <row r="97" spans="1:5" ht="78">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -48197,7 +48216,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.5">
+    <row r="98" spans="1:5" ht="31.2">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -48248,7 +48267,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.5">
+    <row r="101" spans="1:5" ht="31.2">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48367,7 +48386,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="63">
+    <row r="108" spans="1:5" ht="62.4">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48438,14 +48457,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49689,7 +49708,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5" ht="28.8">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49978,7 +49997,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45">
+    <row r="91" spans="1:5" ht="43.2">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -50216,7 +50235,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="75">
+    <row r="105" spans="1:5" ht="72">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -50233,7 +50252,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30">
+    <row r="106" spans="1:5" ht="28.8">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -50267,7 +50286,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30">
+    <row r="108" spans="1:5" ht="28.8">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50388,14 +50407,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51145,14 +51164,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51546,7 +51565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30">
+    <row r="24" spans="1:5" ht="28.8">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51733,7 +51752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:13" ht="28.8">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -52029,13 +52048,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -52123,7 +52142,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30">
+    <row r="6" spans="1:5" ht="28.8">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52361,7 +52380,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52684,7 +52703,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30">
+    <row r="39" spans="1:5" ht="28.8">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52701,7 +52720,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52718,7 +52737,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30">
+    <row r="41" spans="1:5" ht="28.8">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52735,7 +52754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30">
+    <row r="42" spans="1:5" ht="28.8">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52769,7 +52788,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30">
+    <row r="44" spans="1:5" ht="28.8">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -53007,7 +53026,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30">
+    <row r="58" spans="1:5">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -53024,7 +53043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30">
+    <row r="59" spans="1:5" ht="28.8">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -53194,7 +53213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="30">
+    <row r="69" spans="1:5" ht="28.8">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -53279,7 +53298,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30">
+    <row r="74" spans="1:5">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53432,7 +53451,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30">
+    <row r="83" spans="1:5">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53619,7 +53638,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30">
+    <row r="94" spans="1:5">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53721,7 +53740,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="30">
+    <row r="100" spans="1:5">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53738,7 +53757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="30">
+    <row r="101" spans="1:5" ht="28.8">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53891,7 +53910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30">
+    <row r="110" spans="1:5">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53908,7 +53927,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="30">
+    <row r="111" spans="1:5" ht="28.8">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -53993,7 +54012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="30">
+    <row r="116" spans="1:5">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -54044,7 +54063,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="30">
+    <row r="119" spans="1:5" ht="28.8">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54316,7 +54335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="30">
+    <row r="135" spans="1:5">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54469,7 +54488,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="30">
+    <row r="144" spans="1:5" ht="28.8">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54537,7 +54556,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54571,7 +54590,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="30">
+    <row r="150" spans="1:5" ht="28.8">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54588,7 +54607,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="30">
+    <row r="151" spans="1:5">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54843,7 +54862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="30">
+    <row r="166" spans="1:5">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -55013,7 +55032,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5" ht="30">
+    <row r="176" spans="1:5">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -55064,7 +55083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="30">
+    <row r="179" spans="1:5" ht="28.8">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -55149,7 +55168,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5" ht="30">
+    <row r="184" spans="1:5">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -55234,7 +55253,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5" ht="30">
+    <row r="189" spans="1:5">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55812,7 +55831,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30">
+    <row r="223" spans="1:5">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -56172,12 +56191,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56316,7 +56335,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56843,7 +56862,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30">
+    <row r="40" spans="1:5" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -57183,7 +57202,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="28.8">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -57200,7 +57219,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30">
+    <row r="61" spans="1:5" ht="28.8">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -57217,7 +57236,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30">
+    <row r="62" spans="1:5" ht="28.8">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -57302,7 +57321,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57455,7 +57474,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30">
+    <row r="76" spans="1:5" ht="28.8">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57472,7 +57491,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30">
+    <row r="77" spans="1:5" ht="28.8">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57523,7 +57542,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="30">
+    <row r="80" spans="1:5" ht="28.8">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57628,7 +57647,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="16" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="40" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -57645,12 +57664,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -58129,7 +58148,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="30">
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58554,7 +58573,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="30">
+    <row r="54" spans="1:5">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>
@@ -59033,7 +59052,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="15" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="20" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24213DDD-46C0-4EF6-8923-2397CA5D6127}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2613A98-5DFA-41A8-B280-2938AA589FA3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 WARN Notices" sheetId="25" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7646" uniqueCount="3276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7650" uniqueCount="3277">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14269,6 +14269,9 @@
   </si>
   <si>
     <t>12/31/26 - 3/31/27</t>
+  </si>
+  <si>
+    <t>11/25/26  - 11/30/26</t>
   </si>
 </sst>
 </file>
@@ -17168,6 +17171,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17782,13 +17789,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:E98"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="26.6640625" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" style="41" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="33" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="33" customWidth="1"/>
     <col min="5" max="5" width="20" style="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17826,7 +17833,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="31.5">
       <c r="A3" s="60" t="s">
         <v>3151</v>
       </c>
@@ -17877,7 +17884,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="47.25">
       <c r="A6" s="60" t="s">
         <v>3156</v>
       </c>
@@ -17894,7 +17901,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46.8">
+    <row r="7" spans="1:5" ht="47.25">
       <c r="A7" s="60" t="s">
         <v>3158</v>
       </c>
@@ -17911,7 +17918,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="31.5">
       <c r="A8" s="60" t="s">
         <v>3161</v>
       </c>
@@ -17928,7 +17935,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="60" t="s">
         <v>3164</v>
       </c>
@@ -17945,7 +17952,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="78">
+    <row r="10" spans="1:5" ht="78.75">
       <c r="A10" s="48" t="s">
         <v>3110</v>
       </c>
@@ -17996,7 +18003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46.8">
+    <row r="13" spans="1:5" ht="47.25">
       <c r="A13" s="48" t="s">
         <v>3169</v>
       </c>
@@ -18013,7 +18020,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="31.2">
+    <row r="14" spans="1:5" ht="31.5">
       <c r="A14" s="60" t="s">
         <v>3172</v>
       </c>
@@ -18098,7 +18105,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="48" t="s">
         <v>3178</v>
       </c>
@@ -18166,7 +18173,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="62.4">
+    <row r="23" spans="1:5" ht="63">
       <c r="A23" s="63" t="s">
         <v>2870</v>
       </c>
@@ -18183,7 +18190,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="31.2">
+    <row r="24" spans="1:5" ht="31.5">
       <c r="A24" s="48" t="s">
         <v>3184</v>
       </c>
@@ -18200,7 +18207,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46.8">
+    <row r="25" spans="1:5" ht="47.25">
       <c r="A25" s="60" t="s">
         <v>3057</v>
       </c>
@@ -18285,7 +18292,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="31.2">
+    <row r="30" spans="1:5" ht="31.5">
       <c r="A30" s="60" t="s">
         <v>3193</v>
       </c>
@@ -18370,7 +18377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="31.5">
       <c r="A35" s="48" t="s">
         <v>3114</v>
       </c>
@@ -18591,7 +18598,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="48" t="s">
         <v>3217</v>
       </c>
@@ -18812,7 +18819,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="31.2">
+    <row r="61" spans="1:5" ht="31.5">
       <c r="A61" s="63" t="s">
         <v>3231</v>
       </c>
@@ -18880,7 +18887,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="31.2">
+    <row r="65" spans="1:5" ht="31.5">
       <c r="A65" s="63" t="s">
         <v>3235</v>
       </c>
@@ -18948,7 +18955,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="60" t="s">
         <v>3239</v>
       </c>
@@ -18999,7 +19006,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="31.2">
+    <row r="72" spans="1:5" ht="31.5">
       <c r="A72" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19016,7 +19023,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="31.2">
+    <row r="73" spans="1:5" ht="31.5">
       <c r="A73" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19033,7 +19040,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="31.2">
+    <row r="74" spans="1:5" ht="31.5">
       <c r="A74" s="63" t="s">
         <v>3244</v>
       </c>
@@ -19050,7 +19057,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="31.2">
+    <row r="75" spans="1:5" ht="31.5">
       <c r="A75" s="48" t="s">
         <v>3245</v>
       </c>
@@ -19084,7 +19091,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="62.4">
+    <row r="77" spans="1:5" ht="63">
       <c r="A77" s="60" t="s">
         <v>3248</v>
       </c>
@@ -19152,7 +19159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="60" t="s">
         <v>3253</v>
       </c>
@@ -19203,7 +19210,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="31.2">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="60" t="s">
         <v>3257</v>
       </c>
@@ -19220,7 +19227,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="31.2">
+    <row r="85" spans="1:5" ht="31.5">
       <c r="A85" s="60" t="s">
         <v>3258</v>
       </c>
@@ -19237,7 +19244,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="31.2">
+    <row r="86" spans="1:5" ht="31.5">
       <c r="A86" s="60" t="s">
         <v>3243</v>
       </c>
@@ -19254,7 +19261,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="31.2">
+    <row r="87" spans="1:5" ht="31.5">
       <c r="A87" s="60" t="s">
         <v>3231</v>
       </c>
@@ -19339,7 +19346,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="47.25">
       <c r="A92" s="60" t="s">
         <v>3266</v>
       </c>
@@ -19439,6 +19446,23 @@
       </c>
       <c r="E97" s="49">
         <v>187</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="48" t="s">
+        <v>3204</v>
+      </c>
+      <c r="B98" s="48" t="s">
+        <v>2694</v>
+      </c>
+      <c r="C98" s="49" t="s">
+        <v>394</v>
+      </c>
+      <c r="D98" s="50" t="s">
+        <v>3276</v>
+      </c>
+      <c r="E98" s="48">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -19457,12 +19481,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E86"/>
-  <sheetFormatPr defaultColWidth="20.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="20.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20417,7 +20441,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="28.8">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="2" t="s">
         <v>719</v>
       </c>
@@ -20536,7 +20560,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="28.8">
+    <row r="64" spans="1:5" ht="30">
       <c r="A64" s="2" t="s">
         <v>728</v>
       </c>
@@ -20947,12 +20971,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E57"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="58.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20989,7 +21013,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
         <v>752</v>
       </c>
@@ -21023,7 +21047,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="2" t="s">
         <v>755</v>
       </c>
@@ -21142,7 +21166,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="28.8">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="2" t="s">
         <v>764</v>
       </c>
@@ -21210,7 +21234,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="28.8">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="2" t="s">
         <v>769</v>
       </c>
@@ -21244,7 +21268,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>771</v>
       </c>
@@ -21686,7 +21710,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>654</v>
       </c>
@@ -21944,12 +21968,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E170"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -22054,7 +22078,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="2" t="s">
         <v>817</v>
       </c>
@@ -22122,7 +22146,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="28.8">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="2" t="s">
         <v>819</v>
       </c>
@@ -22173,7 +22197,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="2" t="s">
         <v>764</v>
       </c>
@@ -22241,7 +22265,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8">
+    <row r="18" spans="1:5" ht="30">
       <c r="A18" s="2" t="s">
         <v>824</v>
       </c>
@@ -22615,7 +22639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>841</v>
       </c>
@@ -22683,7 +22707,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="2" t="s">
         <v>846</v>
       </c>
@@ -22853,7 +22877,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>853</v>
       </c>
@@ -23108,7 +23132,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="2" t="s">
         <v>871</v>
       </c>
@@ -23499,7 +23523,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="28.8">
+    <row r="92" spans="1:5" ht="30">
       <c r="A92" s="2" t="s">
         <v>906</v>
       </c>
@@ -23567,7 +23591,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="28.8">
+    <row r="96" spans="1:5" ht="30">
       <c r="A96" s="2" t="s">
         <v>912</v>
       </c>
@@ -23669,7 +23693,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="28.8">
+    <row r="102" spans="1:5" ht="45">
       <c r="A102" s="2" t="s">
         <v>922</v>
       </c>
@@ -23686,7 +23710,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="28.8">
+    <row r="103" spans="1:5" ht="30">
       <c r="A103" s="2" t="s">
         <v>924</v>
       </c>
@@ -23737,7 +23761,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="2" t="s">
         <v>929</v>
       </c>
@@ -23805,7 +23829,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="28.8">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="2" t="s">
         <v>935</v>
       </c>
@@ -23839,7 +23863,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" ht="30">
       <c r="A112" s="2" t="s">
         <v>939</v>
       </c>
@@ -23907,7 +23931,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="28.8">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="2" t="s">
         <v>944</v>
       </c>
@@ -23941,7 +23965,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="28.8">
+    <row r="118" spans="1:5" ht="30">
       <c r="A118" s="2" t="s">
         <v>946</v>
       </c>
@@ -23958,7 +23982,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="2" t="s">
         <v>947</v>
       </c>
@@ -24026,7 +24050,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" ht="30">
       <c r="A123" s="2" t="s">
         <v>952</v>
       </c>
@@ -24162,7 +24186,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" ht="30">
       <c r="A131" s="2" t="s">
         <v>961</v>
       </c>
@@ -24332,7 +24356,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="28.8">
+    <row r="141" spans="1:5" ht="30">
       <c r="A141" s="2" t="s">
         <v>976</v>
       </c>
@@ -24519,7 +24543,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" ht="30">
       <c r="A152" s="2" t="s">
         <v>993</v>
       </c>
@@ -24862,13 +24886,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E109"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="57.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="57.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25925,7 +25949,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="30">
       <c r="A63" s="4" t="s">
         <v>1052</v>
       </c>
@@ -25959,7 +25983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1054</v>
       </c>
@@ -26078,7 +26102,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="28.8">
+    <row r="72" spans="1:5" ht="30">
       <c r="A72" s="4" t="s">
         <v>1059</v>
       </c>
@@ -26112,7 +26136,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>1061</v>
       </c>
@@ -26367,7 +26391,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="28.8">
+    <row r="89" spans="1:5" ht="30">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -26435,7 +26459,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="28.8">
+    <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
         <v>1079</v>
       </c>
@@ -26744,13 +26768,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="58.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26872,7 +26896,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="30">
       <c r="A8" s="4" t="s">
         <v>1103</v>
       </c>
@@ -27297,7 +27321,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="28.8">
+    <row r="33" spans="1:5" ht="30">
       <c r="A33" s="4" t="s">
         <v>1128</v>
       </c>
@@ -27705,7 +27729,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="30">
       <c r="A57" s="4" t="s">
         <v>1153</v>
       </c>
@@ -28048,13 +28072,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -28548,7 +28572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1187</v>
       </c>
@@ -28922,7 +28946,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="28.8">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1204</v>
       </c>
@@ -29143,7 +29167,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="30">
       <c r="A65" s="4" t="s">
         <v>1218</v>
       </c>
@@ -29177,7 +29201,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="28.8">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1196</v>
       </c>
@@ -29656,13 +29680,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E99"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="55.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -29682,7 +29706,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="4" t="s">
         <v>1240</v>
       </c>
@@ -29750,7 +29774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>606</v>
       </c>
@@ -29801,7 +29825,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="4" t="s">
         <v>1247</v>
       </c>
@@ -29920,7 +29944,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" ht="30">
       <c r="A16" s="4" t="s">
         <v>1256</v>
       </c>
@@ -30056,7 +30080,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>1267</v>
       </c>
@@ -30158,7 +30182,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="28.8">
+    <row r="30" spans="1:5" ht="30">
       <c r="A30" s="4" t="s">
         <v>1274</v>
       </c>
@@ -30175,7 +30199,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="28.8">
+    <row r="31" spans="1:5" ht="30">
       <c r="A31" s="4" t="s">
         <v>1275</v>
       </c>
@@ -30192,7 +30216,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="28.8">
+    <row r="32" spans="1:5" ht="45">
       <c r="A32" s="4" t="s">
         <v>1276</v>
       </c>
@@ -30294,7 +30318,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>1282</v>
       </c>
@@ -30362,7 +30386,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>1287</v>
       </c>
@@ -30532,7 +30556,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="30">
       <c r="A52" s="4" t="s">
         <v>1298</v>
       </c>
@@ -30583,7 +30607,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="30">
       <c r="A55" s="4" t="s">
         <v>1303</v>
       </c>
@@ -30855,7 +30879,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="28.8">
+    <row r="71" spans="1:5" ht="30">
       <c r="A71" s="4" t="s">
         <v>817</v>
       </c>
@@ -31042,7 +31066,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="28.8">
+    <row r="82" spans="1:5" ht="30">
       <c r="A82" s="4" t="s">
         <v>1326</v>
       </c>
@@ -31368,13 +31392,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E105"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="52.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -31479,7 +31503,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
         <v>1352</v>
       </c>
@@ -33182,13 +33206,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E133"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -34313,7 +34337,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="4" t="s">
         <v>1617</v>
       </c>
@@ -34330,7 +34354,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="30">
       <c r="A68" s="4" t="s">
         <v>1619</v>
       </c>
@@ -35384,7 +35408,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="28.8">
+    <row r="130" spans="1:5" ht="30">
       <c r="A130" s="4" t="s">
         <v>1714</v>
       </c>
@@ -35443,13 +35467,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -37853,16 +37877,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E110"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="32" t="s">
         <v>59</v>
       </c>
@@ -37879,7 +37903,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="31.2">
+    <row r="2" spans="1:5" ht="31.5">
       <c r="A2" s="30" t="s">
         <v>2967</v>
       </c>
@@ -37896,7 +37920,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.6">
+    <row r="3" spans="1:5" ht="15.75">
       <c r="A3" s="30" t="s">
         <v>2670</v>
       </c>
@@ -37913,7 +37937,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="31.5">
       <c r="A4" s="34" t="s">
         <v>2970</v>
       </c>
@@ -37930,7 +37954,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="47.25">
       <c r="A5" s="41" t="s">
         <v>2972</v>
       </c>
@@ -37947,7 +37971,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6">
+    <row r="6" spans="1:5" ht="15.75">
       <c r="A6" s="30" t="s">
         <v>2974</v>
       </c>
@@ -37964,7 +37988,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.6">
+    <row r="7" spans="1:5" ht="15.75">
       <c r="A7" s="30" t="s">
         <v>2976</v>
       </c>
@@ -37981,7 +38005,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.6">
+    <row r="8" spans="1:5" ht="15.75">
       <c r="A8" s="30" t="s">
         <v>2978</v>
       </c>
@@ -37998,7 +38022,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="31.2">
+    <row r="9" spans="1:5" ht="31.5">
       <c r="A9" s="30" t="s">
         <v>2979</v>
       </c>
@@ -38015,7 +38039,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.6">
+    <row r="10" spans="1:5" ht="15.75">
       <c r="A10" s="30" t="s">
         <v>2982</v>
       </c>
@@ -38032,7 +38056,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="31.2">
+    <row r="11" spans="1:5" ht="31.5">
       <c r="A11" s="30" t="s">
         <v>2967</v>
       </c>
@@ -38049,7 +38073,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="93.6">
+    <row r="12" spans="1:5" ht="94.5">
       <c r="A12" s="34" t="s">
         <v>2984</v>
       </c>
@@ -38066,7 +38090,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6">
+    <row r="13" spans="1:5" ht="15.75">
       <c r="A13" s="30" t="s">
         <v>2987</v>
       </c>
@@ -38083,7 +38107,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.6">
+    <row r="14" spans="1:5" ht="15.75">
       <c r="A14" s="34" t="s">
         <v>2990</v>
       </c>
@@ -38100,7 +38124,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.6">
+    <row r="15" spans="1:5" ht="15.75">
       <c r="A15" s="30" t="s">
         <v>2991</v>
       </c>
@@ -38117,7 +38141,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.6">
+    <row r="16" spans="1:5" ht="15.75">
       <c r="A16" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38134,7 +38158,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="62.4">
+    <row r="17" spans="1:5" ht="63">
       <c r="A17" s="34" t="s">
         <v>2994</v>
       </c>
@@ -38151,7 +38175,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="62.4">
+    <row r="18" spans="1:5" ht="63">
       <c r="A18" s="34" t="s">
         <v>2997</v>
       </c>
@@ -38168,7 +38192,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="31.2">
+    <row r="19" spans="1:5" ht="31.5">
       <c r="A19" s="34" t="s">
         <v>2999</v>
       </c>
@@ -38185,7 +38209,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.6">
+    <row r="20" spans="1:5" ht="15.75">
       <c r="A20" s="34" t="s">
         <v>2693</v>
       </c>
@@ -38202,7 +38226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46.8">
+    <row r="21" spans="1:5" ht="47.25">
       <c r="A21" s="34" t="s">
         <v>3002</v>
       </c>
@@ -38219,7 +38243,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.6">
+    <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="30" t="s">
         <v>3004</v>
       </c>
@@ -38236,7 +38260,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.6">
+    <row r="23" spans="1:5" ht="15.75">
       <c r="A23" s="34" t="s">
         <v>3006</v>
       </c>
@@ -38253,7 +38277,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.6">
+    <row r="24" spans="1:5" ht="15.75">
       <c r="A24" s="34" t="s">
         <v>3008</v>
       </c>
@@ -38270,7 +38294,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6">
+    <row r="25" spans="1:5" ht="15.75">
       <c r="A25" s="34" t="s">
         <v>2978</v>
       </c>
@@ -38287,7 +38311,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.6">
+    <row r="26" spans="1:5" ht="15.75">
       <c r="A26" s="30" t="s">
         <v>3010</v>
       </c>
@@ -38304,7 +38328,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="31.2">
+    <row r="27" spans="1:5" ht="31.5">
       <c r="A27" s="30" t="s">
         <v>3012</v>
       </c>
@@ -38321,7 +38345,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.6">
+    <row r="28" spans="1:5" ht="15.75">
       <c r="A28" s="34" t="s">
         <v>3014</v>
       </c>
@@ -38338,7 +38362,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6">
+    <row r="29" spans="1:5" ht="15.75">
       <c r="A29" s="34" t="s">
         <v>3016</v>
       </c>
@@ -38355,7 +38379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.6">
+    <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="34" t="s">
         <v>3017</v>
       </c>
@@ -38372,7 +38396,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="93.6">
+    <row r="31" spans="1:5" ht="94.5">
       <c r="A31" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38389,7 +38413,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="62.4">
+    <row r="32" spans="1:5" ht="63">
       <c r="A32" s="34" t="s">
         <v>3020</v>
       </c>
@@ -38406,7 +38430,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6">
+    <row r="33" spans="1:5" ht="15.75">
       <c r="A33" s="34" t="s">
         <v>3023</v>
       </c>
@@ -38423,7 +38447,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="62.4">
+    <row r="34" spans="1:5" ht="63">
       <c r="A34" s="34" t="s">
         <v>3024</v>
       </c>
@@ -38440,7 +38464,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.6">
+    <row r="35" spans="1:5" ht="15.75">
       <c r="A35" s="34" t="s">
         <v>3026</v>
       </c>
@@ -38457,7 +38481,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.6">
+    <row r="36" spans="1:5" ht="15.75">
       <c r="A36" s="34" t="s">
         <v>3027</v>
       </c>
@@ -38474,7 +38498,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6">
+    <row r="37" spans="1:5" ht="15.75">
       <c r="A37" s="34" t="s">
         <v>3028</v>
       </c>
@@ -38491,7 +38515,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="62.4">
+    <row r="38" spans="1:5" ht="63">
       <c r="A38" s="34" t="s">
         <v>3030</v>
       </c>
@@ -38508,7 +38532,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.6">
+    <row r="39" spans="1:5" ht="15.75">
       <c r="A39" s="34" t="s">
         <v>3032</v>
       </c>
@@ -38525,7 +38549,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.6">
+    <row r="40" spans="1:5" ht="15.75">
       <c r="A40" s="34" t="s">
         <v>3033</v>
       </c>
@@ -38542,7 +38566,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.6">
+    <row r="41" spans="1:5" ht="15.75">
       <c r="A41" s="34" t="s">
         <v>2670</v>
       </c>
@@ -38559,7 +38583,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.6">
+    <row r="42" spans="1:5" ht="15.75">
       <c r="A42" s="34" t="s">
         <v>3035</v>
       </c>
@@ -38576,7 +38600,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.6">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="34" t="s">
         <v>3037</v>
       </c>
@@ -38593,7 +38617,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.6">
+    <row r="44" spans="1:5" ht="15.75">
       <c r="A44" s="34" t="s">
         <v>3038</v>
       </c>
@@ -38610,7 +38634,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="46.8">
+    <row r="45" spans="1:5" ht="47.25">
       <c r="A45" s="34" t="s">
         <v>3041</v>
       </c>
@@ -38627,7 +38651,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.6">
+    <row r="46" spans="1:5" ht="15.75">
       <c r="A46" s="34" t="s">
         <v>3043</v>
       </c>
@@ -38644,7 +38668,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.6">
+    <row r="47" spans="1:5" ht="15.75">
       <c r="A47" s="34" t="s">
         <v>3044</v>
       </c>
@@ -38661,7 +38685,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="31.2">
+    <row r="48" spans="1:5" ht="31.5">
       <c r="A48" s="34" t="s">
         <v>3046</v>
       </c>
@@ -38678,7 +38702,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.6">
+    <row r="49" spans="1:5" ht="15.75">
       <c r="A49" s="34" t="s">
         <v>3048</v>
       </c>
@@ -38695,7 +38719,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="31.2">
+    <row r="50" spans="1:5" ht="31.5">
       <c r="A50" s="34" t="s">
         <v>2967</v>
       </c>
@@ -38712,7 +38736,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.6">
+    <row r="51" spans="1:5" ht="15.75">
       <c r="A51" s="34" t="s">
         <v>3051</v>
       </c>
@@ -38729,7 +38753,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.6">
+    <row r="52" spans="1:5" ht="15.75">
       <c r="A52" s="34" t="s">
         <v>2932</v>
       </c>
@@ -38746,7 +38770,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6">
+    <row r="53" spans="1:5" ht="15.75">
       <c r="A53" s="34" t="s">
         <v>3055</v>
       </c>
@@ -38763,7 +38787,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="31.2">
+    <row r="54" spans="1:5" ht="31.5">
       <c r="A54" s="34" t="s">
         <v>3057</v>
       </c>
@@ -38780,7 +38804,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="15.6">
+    <row r="55" spans="1:5" ht="15.75">
       <c r="A55" s="34" t="s">
         <v>3059</v>
       </c>
@@ -38797,7 +38821,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="93.6">
+    <row r="56" spans="1:5" ht="94.5">
       <c r="A56" s="34" t="s">
         <v>3060</v>
       </c>
@@ -38814,7 +38838,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.6">
+    <row r="57" spans="1:5" ht="15.75">
       <c r="A57" s="34" t="s">
         <v>3062</v>
       </c>
@@ -38831,7 +38855,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.6">
+    <row r="58" spans="1:5" ht="15.75">
       <c r="A58" s="34" t="s">
         <v>3065</v>
       </c>
@@ -38848,7 +38872,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.6">
+    <row r="59" spans="1:5" ht="15.75">
       <c r="A59" s="34" t="s">
         <v>3067</v>
       </c>
@@ -38865,7 +38889,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.6">
+    <row r="60" spans="1:5" ht="15.75">
       <c r="A60" s="34" t="s">
         <v>3071</v>
       </c>
@@ -38882,7 +38906,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="46.8">
+    <row r="61" spans="1:5" ht="47.25">
       <c r="A61" s="34" t="s">
         <v>2992</v>
       </c>
@@ -38899,7 +38923,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.6">
+    <row r="62" spans="1:5" ht="15.75">
       <c r="A62" s="34" t="s">
         <v>2940</v>
       </c>
@@ -38916,7 +38940,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.6">
+    <row r="63" spans="1:5" ht="15.75">
       <c r="A63" s="34" t="s">
         <v>3074</v>
       </c>
@@ -38933,7 +38957,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.6">
+    <row r="64" spans="1:5" ht="15.75">
       <c r="A64" s="34" t="s">
         <v>3075</v>
       </c>
@@ -38950,7 +38974,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.6">
+    <row r="65" spans="1:5" ht="15.75">
       <c r="A65" s="34" t="s">
         <v>3004</v>
       </c>
@@ -38967,7 +38991,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.6">
+    <row r="66" spans="1:5" ht="15.75">
       <c r="A66" s="34" t="s">
         <v>3077</v>
       </c>
@@ -38984,7 +39008,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.6">
+    <row r="67" spans="1:5" ht="15.75">
       <c r="A67" s="34" t="s">
         <v>3079</v>
       </c>
@@ -39001,7 +39025,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.6">
+    <row r="68" spans="1:5" ht="15.75">
       <c r="A68" s="34" t="s">
         <v>3081</v>
       </c>
@@ -39018,7 +39042,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6">
+    <row r="69" spans="1:5" ht="15.75">
       <c r="A69" s="34" t="s">
         <v>2932</v>
       </c>
@@ -39035,7 +39059,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="31.2">
+    <row r="70" spans="1:5" ht="31.5">
       <c r="A70" s="34" t="s">
         <v>2967</v>
       </c>
@@ -39052,7 +39076,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.6">
+    <row r="71" spans="1:5" ht="15.75">
       <c r="A71" s="34" t="s">
         <v>3085</v>
       </c>
@@ -39069,7 +39093,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.6">
+    <row r="72" spans="1:5" ht="15.75">
       <c r="A72" s="34" t="s">
         <v>3004</v>
       </c>
@@ -39086,7 +39110,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.6">
+    <row r="73" spans="1:5" ht="15.75">
       <c r="A73" s="34" t="s">
         <v>3087</v>
       </c>
@@ -39103,7 +39127,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="46.8">
+    <row r="74" spans="1:5" ht="47.25">
       <c r="A74" s="34" t="s">
         <v>3057</v>
       </c>
@@ -39120,7 +39144,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.6">
+    <row r="75" spans="1:5" ht="15.75">
       <c r="A75" s="34" t="s">
         <v>2185</v>
       </c>
@@ -39137,7 +39161,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.6">
+    <row r="76" spans="1:5" ht="15.75">
       <c r="A76" s="34" t="s">
         <v>3089</v>
       </c>
@@ -39154,7 +39178,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="31.2">
+    <row r="77" spans="1:5" ht="31.5">
       <c r="A77" s="34" t="s">
         <v>3092</v>
       </c>
@@ -39171,7 +39195,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="31.2">
+    <row r="78" spans="1:5" ht="31.5">
       <c r="A78" s="34" t="s">
         <v>3099</v>
       </c>
@@ -39188,7 +39212,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="31.2">
+    <row r="79" spans="1:5" ht="31.5">
       <c r="A79" s="34" t="s">
         <v>3111</v>
       </c>
@@ -39205,7 +39229,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15.6">
+    <row r="80" spans="1:5" ht="15.75">
       <c r="A80" s="34" t="s">
         <v>3114</v>
       </c>
@@ -39222,7 +39246,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="31.2">
+    <row r="81" spans="1:5" ht="31.5">
       <c r="A81" s="46" t="s">
         <v>3092</v>
       </c>
@@ -39239,7 +39263,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.6">
+    <row r="82" spans="1:5" ht="15.75">
       <c r="A82" s="46" t="s">
         <v>3094</v>
       </c>
@@ -39256,7 +39280,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="31.2">
+    <row r="83" spans="1:5" ht="31.5">
       <c r="A83" s="46" t="s">
         <v>3096</v>
       </c>
@@ -39273,7 +39297,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="46.8">
+    <row r="84" spans="1:5" ht="47.25">
       <c r="A84" s="46" t="s">
         <v>3098</v>
       </c>
@@ -39290,7 +39314,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.6">
+    <row r="85" spans="1:5" ht="15.75">
       <c r="A85" s="46" t="s">
         <v>3100</v>
       </c>
@@ -39307,7 +39331,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15.6">
+    <row r="86" spans="1:5" ht="15.75">
       <c r="A86" s="47" t="s">
         <v>3102</v>
       </c>
@@ -39324,7 +39348,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="15.6">
+    <row r="87" spans="1:5" ht="15.75">
       <c r="A87" s="46" t="s">
         <v>3105</v>
       </c>
@@ -39341,7 +39365,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="15.6">
+    <row r="88" spans="1:5" ht="15.75">
       <c r="A88" s="46" t="s">
         <v>3107</v>
       </c>
@@ -39358,7 +39382,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="15.6">
+    <row r="89" spans="1:5" ht="15.75">
       <c r="A89" s="46" t="s">
         <v>3108</v>
       </c>
@@ -39375,7 +39399,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.6">
+    <row r="90" spans="1:5" ht="15.75">
       <c r="A90" s="46" t="s">
         <v>3110</v>
       </c>
@@ -39392,7 +39416,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="46.8">
+    <row r="91" spans="1:5" ht="47.25">
       <c r="A91" s="46" t="s">
         <v>3116</v>
       </c>
@@ -39409,7 +39433,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="31.2">
+    <row r="92" spans="1:5" ht="31.5">
       <c r="A92" s="46" t="s">
         <v>3118</v>
       </c>
@@ -39426,7 +39450,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="31.2">
+    <row r="93" spans="1:5" ht="31.5">
       <c r="A93" s="46" t="s">
         <v>3120</v>
       </c>
@@ -39443,7 +39467,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="46" t="s">
         <v>3123</v>
       </c>
@@ -39460,7 +39484,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="46" t="s">
         <v>2999</v>
       </c>
@@ -39477,7 +39501,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="15.6">
+    <row r="96" spans="1:5" ht="15.75">
       <c r="A96" s="46" t="s">
         <v>2693</v>
       </c>
@@ -39494,7 +39518,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.6">
+    <row r="97" spans="1:5" ht="15.75">
       <c r="A97" s="46" t="s">
         <v>3125</v>
       </c>
@@ -39511,7 +39535,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="48" t="s">
         <v>3002</v>
       </c>
@@ -39528,7 +39552,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="31.2">
+    <row r="99" spans="1:5" ht="31.5">
       <c r="A99" s="48" t="s">
         <v>3129</v>
       </c>
@@ -39545,7 +39569,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.6">
+    <row r="100" spans="1:5" ht="15.75">
       <c r="A100" s="48" t="s">
         <v>2967</v>
       </c>
@@ -39562,7 +39586,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.6">
+    <row r="101" spans="1:5" ht="15.75">
       <c r="A101" s="48" t="s">
         <v>2932</v>
       </c>
@@ -39579,7 +39603,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="31.2">
+    <row r="102" spans="1:5" ht="31.5">
       <c r="A102" s="48" t="s">
         <v>3132</v>
       </c>
@@ -39596,7 +39620,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="15.6">
+    <row r="103" spans="1:5" ht="15.75">
       <c r="A103" s="51" t="s">
         <v>2935</v>
       </c>
@@ -39613,7 +39637,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="15.6">
+    <row r="104" spans="1:5" ht="15.75">
       <c r="A104" s="48" t="s">
         <v>3134</v>
       </c>
@@ -39630,7 +39654,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="15.6">
+    <row r="105" spans="1:5" ht="15.75">
       <c r="A105" s="51" t="s">
         <v>3136</v>
       </c>
@@ -39647,7 +39671,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="15.6">
+    <row r="106" spans="1:5" ht="15.75">
       <c r="A106" s="48" t="s">
         <v>3138</v>
       </c>
@@ -39664,7 +39688,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.6">
+    <row r="107" spans="1:5" ht="15.75">
       <c r="A107" s="46" t="s">
         <v>3139</v>
       </c>
@@ -39681,7 +39705,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="15.6">
+    <row r="108" spans="1:5" ht="15.75">
       <c r="A108" s="34" t="s">
         <v>3144</v>
       </c>
@@ -39698,7 +39722,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="31.2">
+    <row r="109" spans="1:5" ht="47.25">
       <c r="A109" s="34" t="s">
         <v>3146</v>
       </c>
@@ -39715,7 +39739,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="15.6">
+    <row r="110" spans="1:5" ht="15.75">
       <c r="A110" s="34" t="s">
         <v>3149</v>
       </c>
@@ -39751,14 +39775,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E93"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="35.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -41363,14 +41387,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="24.7109375" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -42000,7 +42024,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
         <v>2485</v>
       </c>
@@ -43083,14 +43107,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -44822,13 +44846,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E101"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="49.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="49.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46566,14 +46590,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E112"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="32" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="54.5703125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="32" customWidth="1"/>
     <col min="3" max="3" width="21" style="32" customWidth="1"/>
-    <col min="4" max="4" width="36.5546875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="32"/>
+    <col min="4" max="4" width="36.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -46712,7 +46736,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="47.25">
       <c r="A9" s="30" t="s">
         <v>2822</v>
       </c>
@@ -46729,7 +46753,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46.8">
+    <row r="10" spans="1:5" ht="47.25">
       <c r="A10" s="34" t="s">
         <v>2825</v>
       </c>
@@ -46780,7 +46804,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="31.2">
+    <row r="13" spans="1:5" ht="31.5">
       <c r="A13" s="30" t="s">
         <v>2708</v>
       </c>
@@ -46848,7 +46872,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46.8">
+    <row r="17" spans="1:5" ht="47.25">
       <c r="A17" s="30" t="s">
         <v>1224</v>
       </c>
@@ -46899,7 +46923,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="31.2">
+    <row r="20" spans="1:5" ht="31.5">
       <c r="A20" s="34" t="s">
         <v>2845</v>
       </c>
@@ -46933,7 +46957,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="31.2">
+    <row r="22" spans="1:5" ht="31.5">
       <c r="A22" s="30" t="s">
         <v>2847</v>
       </c>
@@ -47154,7 +47178,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="62.4">
+    <row r="35" spans="1:5" ht="63">
       <c r="A35" s="31" t="s">
         <v>2867</v>
       </c>
@@ -47222,7 +47246,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.2">
+    <row r="39" spans="1:5" ht="31.5">
       <c r="A39" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47290,7 +47314,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="31.2">
+    <row r="43" spans="1:5" ht="31.5">
       <c r="A43" s="30" t="s">
         <v>2881</v>
       </c>
@@ -47494,7 +47518,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78">
+    <row r="55" spans="1:5" ht="78.75">
       <c r="A55" s="34" t="s">
         <v>2870</v>
       </c>
@@ -47732,7 +47756,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="31.2">
+    <row r="69" spans="1:5" ht="31.5">
       <c r="A69" s="30" t="s">
         <v>2870</v>
       </c>
@@ -47800,7 +47824,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="62.4">
+    <row r="73" spans="1:5" ht="63">
       <c r="A73" s="30" t="s">
         <v>2930</v>
       </c>
@@ -48046,7 +48070,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="31.2">
+    <row r="88" spans="1:5" ht="31.5">
       <c r="A88" s="34" t="s">
         <v>2881</v>
       </c>
@@ -48148,7 +48172,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="31.2">
+    <row r="94" spans="1:5" ht="31.5">
       <c r="A94" s="34" t="s">
         <v>2957</v>
       </c>
@@ -48165,7 +48189,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="31.2">
+    <row r="95" spans="1:5" ht="31.5">
       <c r="A95" s="34" t="s">
         <v>2960</v>
       </c>
@@ -48199,7 +48223,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="78">
+    <row r="97" spans="1:5" ht="78.75">
       <c r="A97" s="34" t="s">
         <v>2965</v>
       </c>
@@ -48216,7 +48240,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="31.2">
+    <row r="98" spans="1:5" ht="31.5">
       <c r="A98" s="30" t="s">
         <v>2967</v>
       </c>
@@ -48267,7 +48291,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="31.2">
+    <row r="101" spans="1:5" ht="31.5">
       <c r="A101" s="41" t="s">
         <v>2972</v>
       </c>
@@ -48386,7 +48410,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="62.4">
+    <row r="108" spans="1:5" ht="63">
       <c r="A108" s="34" t="s">
         <v>2984</v>
       </c>
@@ -48457,14 +48481,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E113"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="54.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="54.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -49708,7 +49732,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="28.8">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>2757</v>
       </c>
@@ -49997,7 +50021,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="43.2">
+    <row r="91" spans="1:5" ht="45">
       <c r="A91" s="4" t="s">
         <v>2774</v>
       </c>
@@ -50235,7 +50259,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="72">
+    <row r="105" spans="1:5" ht="75">
       <c r="A105" s="4" t="s">
         <v>2708</v>
       </c>
@@ -50252,7 +50276,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="28.8">
+    <row r="106" spans="1:5" ht="30">
       <c r="A106" s="4" t="s">
         <v>2799</v>
       </c>
@@ -50286,7 +50310,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="28.8">
+    <row r="108" spans="1:5" ht="30">
       <c r="A108" s="4" t="s">
         <v>2803</v>
       </c>
@@ -50407,14 +50431,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51164,14 +51188,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M50"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="43.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51565,7 +51589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="28.8">
+    <row r="24" spans="1:5" ht="30">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -51752,7 +51776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="4" t="s">
         <v>2564</v>
       </c>
@@ -52048,13 +52072,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E242"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="50.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -52142,7 +52166,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8">
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -52380,7 +52404,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="30">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -52703,7 +52727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28.8">
+    <row r="39" spans="1:5" ht="30">
       <c r="A39" s="4" t="s">
         <v>136</v>
       </c>
@@ -52720,7 +52744,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="4" t="s">
         <v>138</v>
       </c>
@@ -52737,7 +52761,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="28.8">
+    <row r="41" spans="1:5" ht="30">
       <c r="A41" s="4" t="s">
         <v>140</v>
       </c>
@@ -52754,7 +52778,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="28.8">
+    <row r="42" spans="1:5" ht="30">
       <c r="A42" s="4" t="s">
         <v>141</v>
       </c>
@@ -52788,7 +52812,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28.8">
+    <row r="44" spans="1:5" ht="30">
       <c r="A44" s="4" t="s">
         <v>144</v>
       </c>
@@ -53026,7 +53050,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
         <v>167</v>
       </c>
@@ -53043,7 +53067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="28.8">
+    <row r="59" spans="1:5" ht="30">
       <c r="A59" s="4" t="s">
         <v>169</v>
       </c>
@@ -53213,7 +53237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="28.8">
+    <row r="69" spans="1:5" ht="30">
       <c r="A69" s="4" t="s">
         <v>187</v>
       </c>
@@ -53298,7 +53322,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" ht="30">
       <c r="A74" s="4" t="s">
         <v>196</v>
       </c>
@@ -53451,7 +53475,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" ht="30">
       <c r="A83" s="4" t="s">
         <v>213</v>
       </c>
@@ -53638,7 +53662,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" ht="30">
       <c r="A94" s="4" t="s">
         <v>231</v>
       </c>
@@ -53740,7 +53764,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" ht="30">
       <c r="A100" s="4" t="s">
         <v>240</v>
       </c>
@@ -53757,7 +53781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="28.8">
+    <row r="101" spans="1:5" ht="30">
       <c r="A101" s="4" t="s">
         <v>242</v>
       </c>
@@ -53910,7 +53934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" ht="30">
       <c r="A110" s="4" t="s">
         <v>256</v>
       </c>
@@ -53927,7 +53951,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="28.8">
+    <row r="111" spans="1:5" ht="30">
       <c r="A111" s="4" t="s">
         <v>258</v>
       </c>
@@ -54012,7 +54036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" ht="30">
       <c r="A116" s="4" t="s">
         <v>267</v>
       </c>
@@ -54063,7 +54087,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="28.8">
+    <row r="119" spans="1:5" ht="30">
       <c r="A119" s="4">
         <v>1961</v>
       </c>
@@ -54335,7 +54359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" ht="30">
       <c r="A135" s="4" t="s">
         <v>298</v>
       </c>
@@ -54488,7 +54512,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="28.8">
+    <row r="144" spans="1:5" ht="30">
       <c r="A144" s="4" t="s">
         <v>311</v>
       </c>
@@ -54556,7 +54580,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="4" t="s">
         <v>298</v>
       </c>
@@ -54590,7 +54614,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="28.8">
+    <row r="150" spans="1:5" ht="30">
       <c r="A150" s="4" t="s">
         <v>317</v>
       </c>
@@ -54607,7 +54631,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" ht="30">
       <c r="A151" s="4" t="s">
         <v>318</v>
       </c>
@@ -54862,7 +54886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" ht="30">
       <c r="A166" s="4" t="s">
         <v>339</v>
       </c>
@@ -55032,7 +55056,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" ht="30">
       <c r="A176" s="4" t="s">
         <v>351</v>
       </c>
@@ -55083,7 +55107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" ht="28.8">
+    <row r="179" spans="1:5" ht="30">
       <c r="A179" s="4" t="s">
         <v>357</v>
       </c>
@@ -55168,7 +55192,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" ht="30">
       <c r="A184" s="4" t="s">
         <v>298</v>
       </c>
@@ -55253,7 +55277,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" ht="30">
       <c r="A189" s="4" t="s">
         <v>371</v>
       </c>
@@ -55831,7 +55855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" ht="30">
       <c r="A223" s="4" t="s">
         <v>422</v>
       </c>
@@ -56191,12 +56215,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E85"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -56335,7 +56359,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8">
+    <row r="9" spans="1:5" ht="30">
       <c r="A9" s="2" t="s">
         <v>462</v>
       </c>
@@ -56862,7 +56886,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="28.8">
+    <row r="40" spans="1:5" ht="30">
       <c r="A40" s="2" t="s">
         <v>496</v>
       </c>
@@ -57202,7 +57226,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="28.8">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="2" t="s">
         <v>496</v>
       </c>
@@ -57219,7 +57243,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="28.8">
+    <row r="61" spans="1:5" ht="30">
       <c r="A61" s="2" t="s">
         <v>496</v>
       </c>
@@ -57236,7 +57260,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="28.8">
+    <row r="62" spans="1:5" ht="30">
       <c r="A62" s="2" t="s">
         <v>526</v>
       </c>
@@ -57321,7 +57345,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="30">
       <c r="A67" s="2" t="s">
         <v>532</v>
       </c>
@@ -57474,7 +57498,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="28.8">
+    <row r="76" spans="1:5" ht="30">
       <c r="A76" s="2" t="s">
         <v>542</v>
       </c>
@@ -57491,7 +57515,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="28.8">
+    <row r="77" spans="1:5" ht="30">
       <c r="A77" s="2" t="s">
         <v>543</v>
       </c>
@@ -57542,7 +57566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="28.8">
+    <row r="80" spans="1:5" ht="30">
       <c r="A80" s="2" t="s">
         <v>545</v>
       </c>
@@ -57664,12 +57688,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -58148,7 +58172,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="30">
       <c r="A29" s="2" t="s">
         <v>581</v>
       </c>
@@ -58573,7 +58597,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="30">
       <c r="A54" s="2" t="s">
         <v>615</v>
       </c>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2613A98-5DFA-41A8-B280-2938AA589FA3}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B5226D-C155-4125-AFC6-492D4BEDE01F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7650" uniqueCount="3277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7654" uniqueCount="3278">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14272,6 +14272,9 @@
   </si>
   <si>
     <t>11/25/26  - 11/30/26</t>
+  </si>
+  <si>
+    <t>12/11/26 and 1/4/27</t>
   </si>
 </sst>
 </file>
@@ -17171,10 +17174,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17789,7 +17788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19463,6 +19462,23 @@
       </c>
       <c r="E98" s="48">
         <v>41</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="60" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B99" s="60" t="s">
+        <v>3066</v>
+      </c>
+      <c r="C99" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D99" s="50" t="s">
+        <v>3277</v>
+      </c>
+      <c r="E99" s="49">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -57671,7 +57687,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="40" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="16" fitToHeight="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>
@@ -59076,7 +59092,7 @@
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="20" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="15" fitToHeight="12" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"-,Bold"&amp;A</oddHeader>
     <oddFooter>Page &amp;P</oddFooter>

--- a/data/warn-scraper/cache/nj/source.xlsx
+++ b/data/warn-scraper/cache/nj/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sonj-my.sharepoint.com/personal/heather_bernhard_dol_nj_gov/Documents/Documents/Websites/WARN Notices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="151" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3B5226D-C155-4125-AFC6-492D4BEDE01F}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{83F69934-A376-4D4C-A95B-78C3BFCB4022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E536ABD9-EB31-4E9B-B5CF-8E452BFDD949}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7654" uniqueCount="3278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7658" uniqueCount="3280">
   <si>
     <t xml:space="preserve">Envision Physician Services, LLC </t>
   </si>
@@ -14275,6 +14275,12 @@
   </si>
   <si>
     <t>12/11/26 and 1/4/27</t>
+  </si>
+  <si>
+    <t>Educational Testing Service</t>
+  </si>
+  <si>
+    <t>11/9/26 and 12/31/26</t>
   </si>
 </sst>
 </file>
@@ -17174,6 +17180,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}" name="Table4232322" displayName="Table4232322" ref="A1:E110" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="A1:E110" xr:uid="{083CCC35-9798-44C7-9052-68D97851C304}"/>
@@ -17788,7 +17798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7C01F6-CAB7-4CB2-BC9F-F872F7E36B51}">
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="26.7109375" style="41" bestFit="1" customWidth="1"/>
@@ -19479,6 +19489,23 @@
       </c>
       <c r="E99" s="49">
         <v>54</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="31.5">
+      <c r="A100" s="60" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B100" s="60" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C100" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="D100" s="50" t="s">
+        <v>3279</v>
+      </c>
+      <c r="E100" s="49">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
